--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="角色组件" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="动画与状态" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="原型角色" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="角色中转记录" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="3D-角色" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="域变更日志" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色中转记录" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$36</definedName>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="I6" s="105" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>default / seated</t>
         </is>
       </c>
       <c r="J6" s="98" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="P6" s="105" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json</t>
         </is>
       </c>
       <c r="Q6" s="98" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="T6" s="105" t="inlineStr">
         <is>
-          <t>2802d5526c3eb7a8ab01a09bb9d2115c7dc531563442527460ddfd71870cbdec</t>
+          <t>d962a133c9f966e97e0471adf110eaddda7ade65c2ef3ec47b56dbf2f1c93af0</t>
         </is>
       </c>
       <c r="U6" s="98" t="inlineStr">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="V6" s="112" t="n">
-        <v>46264</v>
+        <v>46294</v>
       </c>
       <c r="W6" s="98" t="inlineStr">
         <is>
@@ -2762,7 +2762,9 @@
 2026-09-09：双Blend共享骨架 v009；新导出分件骨局部原点，八态Blender动作库接入；玩法层级/碰撞不变。
 2026-09-09：v010 腰胸/上下臂/指链/大小腿新骨架，模型未改；待机、移动、持枪待机、持枪移动重新制作并接入。用户要求跳过验收，未验证；其他状态沿用v009。
 2026-09-10：v011 +Y到Godot -Z统一朝向；原位直链绑定、腰胸归位、四基础动作无骨链拉伸。验收结果见中转JSON。
-2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。</t>
+2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。
+2026-09-29：v021 模型及原12动作保持不变；新增 v022 Blender 坐姿滑行循环 seated，Player3D 九态状态机与 99F 两把可驾驶椅接入；verify_pushable_base_chairs 通过。
+2026-09-29：v023 Blender 坐姿源将双脚向座面前方伸出；角色乘坐时可正常射击，相机补偿座面抬升，离座恢复世界碰撞。</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3497,7 @@
       </c>
       <c r="I13" s="116" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>default / seated / climbing</t>
         </is>
       </c>
       <c r="J13" s="116" t="inlineStr">
@@ -3530,7 +3532,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3548,7 +3550,7 @@
       </c>
       <c r="T13" s="116" t="inlineStr">
         <is>
-          <t>c571c093bab22f38361fabb0317d30602035d8e5187b7bf7279aec5b14a370ea</t>
+          <t>e9cac2738d9fa586eed9f2e97a93ff220cab52b60d89f53f4cd80e38ebc9b6c4</t>
         </is>
       </c>
       <c r="U13" s="116" t="inlineStr">
@@ -3557,7 +3559,7 @@
         </is>
       </c>
       <c r="V13" s="118" t="n">
-        <v>46264</v>
+        <v>46294</v>
       </c>
       <c r="W13" s="119" t="inlineStr">
         <is>
@@ -3580,7 +3582,10 @@
 2026-09-09：双Blend共享骨架 v009；新导出分件骨局部原点，八态Blender动作库接入；玩法层级/碰撞不变。
 2026-09-09：v010 腰胸/上下臂/指链/大小腿新骨架，模型未改；待机、移动、持枪待机、持枪移动重新制作并接入。用户要求跳过验收，未验证；其他状态沿用v009。
 2026-09-10：v011 +Y到Godot -Z统一朝向；原位直链绑定、腰胸归位、四基础动作无骨链拉伸。验收结果见中转JSON。
-2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。</t>
+2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。
+2026-09-29：v021 模型及原12动作保持不变；新增 v022 Blender 坐姿滑行循环 seated，Player3D 九态状态机与 99F 两把可驾驶椅接入；verify_pushable_base_chairs 通过。
+2026-09-29：v023 Blender 坐姿源将双脚向座面前方伸出；角色乘坐时可正常射击，相机补偿座面抬升，离座恢复世界碰撞。
+2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4975,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -7558,7 +7562,7 @@
     <row r="3" ht="73.5" customHeight="1" s="88">
       <c r="A3" s="126" t="inlineStr">
         <is>
-          <t>Player3D 八态状态机 × 组件表现（falling/landing为真实垂直物理顶层状态）</t>
+          <t>Player3D 九态状态机 × 组件表现（falling/landing为真实垂直物理顶层状态）</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7665,7 @@
       </c>
       <c r="E6" s="128" t="inlineStr">
         <is>
-          <t>moving,dashing,hurt,locked,falling,dead</t>
+          <t>moving,dashing,hurt,locked,falling,dead,seated</t>
         </is>
       </c>
       <c r="F6" s="128" t="inlineStr">
@@ -7723,7 +7727,7 @@
       </c>
       <c r="E7" s="130" t="inlineStr">
         <is>
-          <t>idle,dashing,hurt,locked,falling,dead</t>
+          <t>idle,dashing,hurt,locked,falling,dead,seated</t>
         </is>
       </c>
       <c r="F7" s="130" t="inlineStr">
@@ -8382,8 +8386,67 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="72" customHeight="1" s="88">
-      <c r="A18" s="133" t="n"/>
+    <row r="18" ht="22.35" customHeight="1" s="88">
+      <c r="A18" s="129" t="inlineStr">
+        <is>
+          <t>顶层</t>
+        </is>
+      </c>
+      <c r="B18" s="130" t="inlineStr">
+        <is>
+          <t>seated</t>
+        </is>
+      </c>
+      <c r="C18" s="129" t="inlineStr">
+        <is>
+          <t>座椅乘坐 / 滑行</t>
+        </is>
+      </c>
+      <c r="D18" s="129" t="inlineStr">
+        <is>
+          <t>idle/moving，经 E 交互且椅子空闲</t>
+        </is>
+      </c>
+      <c r="E18" s="129" t="inlineStr">
+        <is>
+          <t>idle,moving,locked,hurt,falling,dead；E 安全离座</t>
+        </is>
+      </c>
+      <c r="F18" s="130" t="inlineStr">
+        <is>
+          <t>v023：原始 Blender 动画源迭代 1.2 秒坐姿轻摆循环；双脚前伸，不驱动椅子位移。</t>
+        </is>
+      </c>
+      <c r="G18" s="129" t="inlineStr">
+        <is>
+          <t>头部随躯干微调，耳朵保持轻微呼吸。</t>
+        </is>
+      </c>
+      <c r="H18" s="129" t="inlineStr">
+        <is>
+          <t>双脚前伸；双手随坐姿与武器挂点，乘坐时仍可正常射击。</t>
+        </is>
+      </c>
+      <c r="I18" s="129" t="inlineStr">
+        <is>
+          <t>右手与 WeaponSocket 随坐姿；开火沿用既有射击/弹药判定。</t>
+        </is>
+      </c>
+      <c r="J18" s="129" t="inlineStr">
+        <is>
+          <t>随坐姿缓动</t>
+        </is>
+      </c>
+      <c r="K18" s="130" t="inlineStr">
+        <is>
+          <t>E 离座提示；世界碰撞离座恢复；镜头补偿座面升高</t>
+        </is>
+      </c>
+      <c r="L18" s="129" t="inlineStr">
+        <is>
+          <t>Player3DSeatedState 驱动；PushableSeat3D 刚体受方向输入施力，乘客跟随座点；退出前做地面与胶囊空间查询。</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="42" customHeight="1" s="88">
       <c r="A19" s="117" t="inlineStr">
@@ -9236,7 +9299,7 @@
     <row r="36" ht="33.75" customHeight="1" s="88">
       <c r="A36" s="116" t="inlineStr">
         <is>
-          <t>Player3D DIY 外观槽 × 动态继承（不影响八态/玩法）</t>
+          <t>Player3D DIY 外观槽 × 动态继承（不影响九态/玩法）</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9462,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44" ht="12.65" customHeight="1" s="88">
       <c r="A44" s="122" t="inlineStr">
         <is>
@@ -9663,7 +9725,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A41:L41"/>
     <mergeCell ref="A45:L45"/>
@@ -9673,7 +9735,6 @@
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A44:L44"/>
     <mergeCell ref="A40:L40"/>
-    <mergeCell ref="A18:L18"/>
     <mergeCell ref="A3:L3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -9716,7 +9777,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -10060,7 +10120,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="31.5" customHeight="1" s="88">
       <c r="A15" s="107" t="inlineStr">
         <is>
@@ -10271,7 +10330,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="88">
       <c r="A21" s="141" t="inlineStr">
         <is>
@@ -10279,7 +10337,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="88">
       <c r="A23" s="142" t="inlineStr">
         <is>
@@ -10308,7 +10365,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="33.75" customHeight="1" s="88">
       <c r="A28" s="145" t="inlineStr">
         <is>
@@ -10812,7 +10868,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="88">
       <c r="A4" s="153" t="inlineStr">
         <is>
@@ -11230,7 +11285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="87" min="1" max="1"/>
@@ -11331,6 +11386,154 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="105" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C7" s="98" t="inlineStr">
+        <is>
+          <t>玩家坐姿动作接入</t>
+        </is>
+      </c>
+      <c r="D7" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E7" s="98" t="inlineStr">
+        <is>
+          <t>v022 动画源新增 seated 循环，原 12 动作逐剪辑一致；玩法状态机新增 seated。</t>
+        </is>
+      </c>
+      <c r="F7" s="98" t="inlineStr">
+        <is>
+          <t>更新既有玩家与 Bunny 根资产的状态、源文件、备注和日期；模型/Prefab 路径不变，SHA 同步当前文件。</t>
+        </is>
+      </c>
+      <c r="G7" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.2</t>
+        </is>
+      </c>
+      <c r="B8" s="105" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C8" s="98" t="inlineStr">
+        <is>
+          <t>九态坐姿映射同步</t>
+        </is>
+      </c>
+      <c r="D8" s="98" t="inlineStr">
+        <is>
+          <t>角色 / 动画与状态</t>
+        </is>
+      </c>
+      <c r="E8" s="98" t="inlineStr">
+        <is>
+          <t>Player3D 八态扩为九态，补 seated 乘坐滑行状态的来源、去向、Blender v022 动作及安全离座契约。</t>
+        </is>
+      </c>
+      <c r="F8" s="98" t="inlineStr">
+        <is>
+          <t>仅改《动画与状态》专表和变更日志；资产主表内容不变，专表无损摘要同步更新。</t>
+        </is>
+      </c>
+      <c r="G8" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.3</t>
+        </is>
+      </c>
+      <c r="B9" s="105" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C9" s="98" t="inlineStr">
+        <is>
+          <t>坐姿动作与乘坐射击修正</t>
+        </is>
+      </c>
+      <c r="D9" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E9" s="98" t="inlineStr">
+        <is>
+          <t>v023 双脚前伸 Blender 动作；乘坐仍可开枪，相机与离座碰撞恢复。</t>
+        </is>
+      </c>
+      <c r="F9" s="98" t="inlineStr">
+        <is>
+          <t>更新既有资产记录与验收契约；保留 AssetID 和稳定 PackedScene 路径。</t>
+        </is>
+      </c>
+      <c r="G9" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.4</t>
+        </is>
+      </c>
+      <c r="B10" s="105" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C10" s="98" t="inlineStr">
+        <is>
+          <t>兔子角色攀爬状态与动作</t>
+        </is>
+      </c>
+      <c r="D10" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E10" s="98" t="inlineStr">
+        <is>
+          <t>v024 Blender动作母版与14剪辑库新增climbing；旧模型与其余动作保持。</t>
+        </is>
+      </c>
+      <c r="F10" s="98" t="inlineStr">
+        <is>
+          <t>更新资产主表与运行时事实源；既有历史资源保留。</t>
+        </is>
+      </c>
+      <c r="G10" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="88">
       <c r="A6" s="93">
-        <f>COUNTA('资产主表'!$A$6:$A$21)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$30)</f>
         <v/>
       </c>
       <c r="B6" s="91" t="n"/>
       <c r="C6" s="93">
-        <f>COUNTIF('资产主表'!$K$6:$K$21,"已完成")+COUNTIF('资产主表'!$K$6:$K$21,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$21,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$21,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$21,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$21,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$21,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$30,"已完成")+COUNTIF('资产主表'!$K$6:$K$30,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$30,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$30,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$30,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$30,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$30,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="91" t="n"/>
       <c r="E6" s="93">
-        <f>COUNTIF('资产主表'!$K$6:$K$21,"待制作")+COUNTIF('资产主表'!$K$6:$K$21,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$30,"待制作")+COUNTIF('资产主表'!$K$6:$K$30,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="91" t="n"/>
       <c r="G6" s="93">
-        <f>COUNTIF('资产主表'!$S$6:$S$21,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$30,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="91" t="n"/>
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="B10" s="98">
-        <f>COUNTIF('资产主表'!$C$6:$C$21,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$30,A10)</f>
         <v/>
       </c>
       <c r="C10" s="98">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$21=A10)*(('资产主表'!$K$6:$K$21="已完成")+('资产主表'!$K$6:$K$21="原型已接入")+('资产主表'!$K$6:$K$21="正式美术已接入")+('资产主表'!$K$6:$K$21="已优化并正式接入")+('资产主表'!$K$6:$K$21="Blender源已完成")+('资产主表'!$K$6:$K$21="已导入；优化完成")+('资产主表'!$K$6:$K$21="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$30=A10)*(('资产主表'!$K$6:$K$30="已完成")+('资产主表'!$K$6:$K$30="原型已接入")+('资产主表'!$K$6:$K$30="正式美术已接入")+('资产主表'!$K$6:$K$30="已优化并正式接入")+('资产主表'!$K$6:$K$30="Blender源已完成")+('资产主表'!$K$6:$K$30="已导入；优化完成")+('资产主表'!$K$6:$K$30="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="98" t="n"/>
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="B11" s="94">
-        <f>COUNTIF('资产主表'!$C$6:$C$21,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$30,A11)</f>
         <v/>
       </c>
       <c r="C11" s="94">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$21=A11)*(('资产主表'!$K$6:$K$21="已完成")+('资产主表'!$K$6:$K$21="原型已接入")+('资产主表'!$K$6:$K$21="正式美术已接入")+('资产主表'!$K$6:$K$21="已优化并正式接入")+('资产主表'!$K$6:$K$21="Blender源已完成")+('资产主表'!$K$6:$K$21="已导入；优化完成")+('资产主表'!$K$6:$K$21="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$30=A11)*(('资产主表'!$K$6:$K$30="已完成")+('资产主表'!$K$6:$K$30="原型已接入")+('资产主表'!$K$6:$K$30="正式美术已接入")+('资产主表'!$K$6:$K$30="已优化并正式接入")+('资产主表'!$K$6:$K$30="Blender源已完成")+('资产主表'!$K$6:$K$30="已导入；优化完成")+('资产主表'!$K$6:$K$30="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="94" t="n"/>
@@ -2123,6 +2123,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -2728,7 +2729,7 @@
         <v/>
       </c>
       <c r="S6" s="98">
-        <f>IF(COUNTIF($R$6:$R$21,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="105" t="inlineStr">
@@ -2851,7 +2852,7 @@
         <v/>
       </c>
       <c r="S7" s="99">
-        <f>IF(COUNTIF($R$6:$R$21,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="114" t="inlineStr">
@@ -2966,7 +2967,7 @@
         <v/>
       </c>
       <c r="S8" s="99">
-        <f>IF(COUNTIF($R$6:$R$21,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="114" t="inlineStr">
@@ -3081,7 +3082,7 @@
         <v/>
       </c>
       <c r="S9" s="99">
-        <f>IF(COUNTIF($R$6:$R$21,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="114" t="inlineStr">
@@ -3196,7 +3197,7 @@
         <v/>
       </c>
       <c r="S10" s="99">
-        <f>IF(COUNTIF($R$6:$R$21,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="114" t="inlineStr">
@@ -3311,7 +3312,7 @@
         <v/>
       </c>
       <c r="S11" s="99">
-        <f>IF(COUNTIF($R$6:$R$21,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="114" t="inlineStr">
@@ -3426,7 +3427,7 @@
         <v/>
       </c>
       <c r="S12" s="99">
-        <f>IF(COUNTIF($R$6:$R$21,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="99" t="n"/>
@@ -3545,7 +3546,7 @@
         <v/>
       </c>
       <c r="S13" s="117">
-        <f>IF(COUNTIF($R$6:$R$21,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="116" t="inlineStr">
@@ -3680,7 +3681,7 @@
         <v/>
       </c>
       <c r="S14" s="117">
-        <f>IF(COUNTIF($R$6:$R$21,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="116" t="inlineStr">
@@ -3808,7 +3809,7 @@
         <v/>
       </c>
       <c r="S15" s="117">
-        <f>IF(COUNTIF($R$6:$R$21,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="116" t="inlineStr">
@@ -3936,7 +3937,7 @@
         <v/>
       </c>
       <c r="S16" s="117">
-        <f>IF(COUNTIF($R$6:$R$21,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="116" t="inlineStr">
@@ -4064,7 +4065,7 @@
         <v/>
       </c>
       <c r="S17" s="117">
-        <f>IF(COUNTIF($R$6:$R$21,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="116" t="inlineStr">
@@ -4195,7 +4196,7 @@
         <v/>
       </c>
       <c r="S18" s="117">
-        <f>IF(COUNTIF($R$6:$R$21,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="116" t="inlineStr">
@@ -4323,7 +4324,7 @@
         <v/>
       </c>
       <c r="S19" s="117">
-        <f>IF(COUNTIF($R$6:$R$21,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="116" t="inlineStr">
@@ -4451,7 +4452,7 @@
         <v/>
       </c>
       <c r="S20" s="91">
-        <f>IF(COUNTIF($R$6:$R$21,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="120" t="inlineStr">
@@ -4576,7 +4577,7 @@
         <v/>
       </c>
       <c r="S21" s="87">
-        <f>IF(COUNTIF($R$6:$R$21,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$30,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="122" t="inlineStr">
@@ -4612,50 +4613,1128 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="88">
-      <c r="C22" s="87" t="n"/>
-      <c r="K22" s="87" t="n"/>
-      <c r="L22" s="122" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="88">
-      <c r="C23" s="87" t="n"/>
-      <c r="K23" s="87" t="n"/>
-      <c r="L23" s="122" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="88">
-      <c r="C24" s="87" t="n"/>
-      <c r="K24" s="87" t="n"/>
-      <c r="L24" s="122" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="88">
-      <c r="C25" s="87" t="n"/>
-      <c r="K25" s="87" t="n"/>
-      <c r="L25" s="122" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="88">
-      <c r="C26" s="87" t="n"/>
-      <c r="K26" s="87" t="n"/>
-      <c r="L26" s="122" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="88">
-      <c r="C27" s="87" t="n"/>
-      <c r="K27" s="87" t="n"/>
-      <c r="L27" s="122" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="88">
-      <c r="C28" s="87" t="n"/>
-      <c r="K28" s="87" t="n"/>
-      <c r="L28" s="122" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="88">
-      <c r="C29" s="87" t="n"/>
-      <c r="K29" s="87" t="n"/>
-      <c r="L29" s="122" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="88">
-      <c r="C30" s="87" t="n"/>
-      <c r="K30" s="87" t="n"/>
-      <c r="L30" s="122" t="n"/>
+    <row r="22" ht="1412.65" customHeight="1" s="88">
+      <c r="A22" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="B22" s="117" t="inlineStr">
+        <is>
+          <t>兔子主角黑色蓝光电子面具</t>
+        </is>
+      </c>
+      <c r="C22" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D22" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E22" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01</t>
+        </is>
+      </c>
+      <c r="F22" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G22" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-CAPSULE01-3D-BUNNY01</t>
+        </is>
+      </c>
+      <c r="H22" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I22" s="116" t="inlineStr">
+        <is>
+          <t>8种网格表情；mask_idle/blink/flicker；独立系统随机与状态事件调用</t>
+        </is>
+      </c>
+      <c r="J22" s="116" t="inlineStr">
+        <is>
+          <t>Bunny01面饰槽</t>
+        </is>
+      </c>
+      <c r="K22" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L22" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M22" s="116" t="inlineStr">
+        <is>
+          <t>v005</t>
+        </is>
+      </c>
+      <c r="N22" s="117" t="inlineStr">
+        <is>
+          <t>原黑色面具+8种独立方块网格；自发光1.25（降低75%）；情绪无嘴；眼睛/爱心/符号饱满加粗；11.8mm颗粒/14mm网格；生气红色；单位根/原head契约</t>
+        </is>
+      </c>
+      <c r="O22" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_root.tscn</t>
+        </is>
+      </c>
+      <c r="P22" s="116" t="inlineStr">
+        <is>
+          <t>src/player3d/PlayerAvatar3D.gd；docs/v0.1/16_技术施工_主页面与角色换装.md</t>
+        </is>
+      </c>
+      <c r="Q22" s="117" t="inlineStr">
+        <is>
+          <t>电子面具;黑色面罩;蓝光;方块眼睛;面饰;electronic_mask</t>
+        </is>
+      </c>
+      <c r="R22" s="116">
+        <f>LOWER(TRIM(C22)&amp;"|"&amp;TRIM(D22)&amp;"|"&amp;TRIM(E22)&amp;"|"&amp;TRIM(F22)&amp;"|"&amp;TRIM(H22)&amp;"|"&amp;TRIM(I22))</f>
+        <v/>
+      </c>
+      <c r="S22" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R22)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T22" s="116" t="inlineStr">
+        <is>
+          <t>3775f317b0abc0ea1bff93150221ba3d0a26bd851520c230c0773ced52155628</t>
+        </is>
+      </c>
+      <c r="U22" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V22" s="118" t="n">
+        <v>46296</v>
+      </c>
+      <c r="W22" s="117" t="inlineStr">
+        <is>
+          <t>用户参考图；项目既有头部曲面派生；代码制作蓝光颗粒</t>
+        </is>
+      </c>
+      <c r="X22" s="113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y22" s="116" t="inlineStr">
+        <is>
+          <t>v005同ID version_increment；独立CharacterExpressionSystem拥有选择/随机/保持，PlayerExpressionStateAdapter消费真实状态事件，面具只显示。8种表情自发光1.25；无嘴部且图案饱满；原11网格/骨架及v001–v004源保留；8种表情分别登记子资产。源、8种Forward+图、独立系统/实际状态调用和眨眼/闪烁/换装专项通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="1412.65" customHeight="1" s="88">
+      <c r="A23" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL</t>
+        </is>
+      </c>
+      <c r="B23" s="117" t="inlineStr">
+        <is>
+          <t>电子面具表情：平静</t>
+        </is>
+      </c>
+      <c r="C23" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D23" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E23" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01_expression_neutral</t>
+        </is>
+      </c>
+      <c r="F23" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G23" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="H23" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I23" s="116" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="J23" s="116" t="inlineStr">
+        <is>
+          <t>独立角色表情系统</t>
+        </is>
+      </c>
+      <c r="K23" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L23" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M23" s="116" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N23" s="117" t="inlineStr">
+        <is>
+          <t>180颗11.8mm方块/14mm网格；自发光1.25；情绪无嘴部；图案加粗放大；#21bfff；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="O23" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/runtime/chr_bunny01_expression_neutral_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P23" s="116" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/character_expression_system.md；src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="Q23" s="117" t="inlineStr">
+        <is>
+          <t>网格表情;情绪;符号;平静;neutral</t>
+        </is>
+      </c>
+      <c r="R23" s="116">
+        <f>LOWER(TRIM(C23)&amp;"|"&amp;TRIM(D23)&amp;"|"&amp;TRIM(E23)&amp;"|"&amp;TRIM(F23)&amp;"|"&amp;TRIM(H23)&amp;"|"&amp;TRIM(I23))</f>
+        <v/>
+      </c>
+      <c r="S23" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R23)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T23" s="116" t="inlineStr">
+        <is>
+          <t>91bf8992535d92214043b1f732fb9ef10f263f1507428fda2cd55282429b9fa2</t>
+        </is>
+      </c>
+      <c r="U23" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V23" s="118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="W23" s="117" t="inlineStr">
+        <is>
+          <t>用户要求；原创方块网格排布</t>
+        </is>
+      </c>
+      <c r="X23" s="113" t="inlineStr">
+        <is>
+          <t>01_部件/眼镜/眼镜__electronic_mask/表情__neutral</t>
+        </is>
+      </c>
+      <c r="Y23" s="116" t="inlineStr">
+        <is>
+          <t>version_increment；父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；共享v005模型/动作双母版与SKEL-BUNNY01-004签名；独立稳定GLB/Prefab；180颗方块，颜色#21bfff，符号不闭眼；随机可达/命令/实际状态事件/Forward+真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="1412.65" customHeight="1" s="88">
+      <c r="A24" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY</t>
+        </is>
+      </c>
+      <c r="B24" s="117" t="inlineStr">
+        <is>
+          <t>电子面具表情：开心</t>
+        </is>
+      </c>
+      <c r="C24" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D24" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E24" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01_expression_happy</t>
+        </is>
+      </c>
+      <c r="F24" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G24" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="H24" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I24" s="116" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="J24" s="116" t="inlineStr">
+        <is>
+          <t>独立角色表情系统</t>
+        </is>
+      </c>
+      <c r="K24" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L24" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M24" s="116" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N24" s="117" t="inlineStr">
+        <is>
+          <t>116颗11.8mm方块/14mm网格；自发光1.25；情绪无嘴部；图案加粗放大；#29e9ff；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="O24" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/runtime/chr_bunny01_expression_happy_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P24" s="116" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/character_expression_system.md；src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="Q24" s="117" t="inlineStr">
+        <is>
+          <t>网格表情;情绪;符号;开心;happy</t>
+        </is>
+      </c>
+      <c r="R24" s="116">
+        <f>LOWER(TRIM(C24)&amp;"|"&amp;TRIM(D24)&amp;"|"&amp;TRIM(E24)&amp;"|"&amp;TRIM(F24)&amp;"|"&amp;TRIM(H24)&amp;"|"&amp;TRIM(I24))</f>
+        <v/>
+      </c>
+      <c r="S24" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R24)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T24" s="116" t="inlineStr">
+        <is>
+          <t>6096540f49967a91f361561915c16f586ce6f32bf66548b4178ccf4b16e9cd4f</t>
+        </is>
+      </c>
+      <c r="U24" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V24" s="118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="W24" s="117" t="inlineStr">
+        <is>
+          <t>用户要求；原创方块网格排布</t>
+        </is>
+      </c>
+      <c r="X24" s="113" t="inlineStr">
+        <is>
+          <t>01_部件/眼镜/眼镜__electronic_mask/表情__happy</t>
+        </is>
+      </c>
+      <c r="Y24" s="116" t="inlineStr">
+        <is>
+          <t>version_increment；父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；共享v005模型/动作双母版与SKEL-BUNNY01-004签名；独立稳定GLB/Prefab；116颗方块，颜色#29e9ff，符号不闭眼；随机可达/命令/实际状态事件/Forward+真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="1412.65" customHeight="1" s="88">
+      <c r="A25" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD</t>
+        </is>
+      </c>
+      <c r="B25" s="117" t="inlineStr">
+        <is>
+          <t>电子面具表情：难过</t>
+        </is>
+      </c>
+      <c r="C25" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D25" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E25" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01_expression_sad</t>
+        </is>
+      </c>
+      <c r="F25" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G25" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="H25" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I25" s="116" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="J25" s="116" t="inlineStr">
+        <is>
+          <t>独立角色表情系统</t>
+        </is>
+      </c>
+      <c r="K25" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L25" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M25" s="116" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N25" s="117" t="inlineStr">
+        <is>
+          <t>102颗11.8mm方块/14mm网格；自发光1.25；情绪无嘴部；图案加粗放大；#777bff；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="O25" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/runtime/chr_bunny01_expression_sad_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P25" s="116" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/character_expression_system.md；src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="Q25" s="117" t="inlineStr">
+        <is>
+          <t>网格表情;情绪;符号;难过;sad</t>
+        </is>
+      </c>
+      <c r="R25" s="116">
+        <f>LOWER(TRIM(C25)&amp;"|"&amp;TRIM(D25)&amp;"|"&amp;TRIM(E25)&amp;"|"&amp;TRIM(F25)&amp;"|"&amp;TRIM(H25)&amp;"|"&amp;TRIM(I25))</f>
+        <v/>
+      </c>
+      <c r="S25" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R25)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T25" s="116" t="inlineStr">
+        <is>
+          <t>64b0b018248b0f2901755b51caf6af2246372424e246e0e2d2e52daa6c0db05e</t>
+        </is>
+      </c>
+      <c r="U25" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V25" s="118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="W25" s="117" t="inlineStr">
+        <is>
+          <t>用户要求；原创方块网格排布</t>
+        </is>
+      </c>
+      <c r="X25" s="113" t="inlineStr">
+        <is>
+          <t>01_部件/眼镜/眼镜__electronic_mask/表情__sad</t>
+        </is>
+      </c>
+      <c r="Y25" s="116" t="inlineStr">
+        <is>
+          <t>version_increment；父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；共享v005模型/动作双母版与SKEL-BUNNY01-004签名；独立稳定GLB/Prefab；102颗方块，颜色#777bff，符号不闭眼；随机可达/命令/实际状态事件/Forward+真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="1412.65" customHeight="1" s="88">
+      <c r="A26" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY</t>
+        </is>
+      </c>
+      <c r="B26" s="117" t="inlineStr">
+        <is>
+          <t>电子面具表情：生气</t>
+        </is>
+      </c>
+      <c r="C26" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D26" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E26" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01_expression_angry</t>
+        </is>
+      </c>
+      <c r="F26" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G26" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="H26" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I26" s="116" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="J26" s="116" t="inlineStr">
+        <is>
+          <t>独立角色表情系统</t>
+        </is>
+      </c>
+      <c r="K26" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L26" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M26" s="116" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N26" s="117" t="inlineStr">
+        <is>
+          <t>112颗11.8mm方块/14mm网格；自发光1.25；情绪无嘴部；图案加粗放大；#ff3028；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="O26" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/runtime/chr_bunny01_expression_angry_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P26" s="116" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/character_expression_system.md；src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="Q26" s="117" t="inlineStr">
+        <is>
+          <t>网格表情;情绪;符号;生气;angry</t>
+        </is>
+      </c>
+      <c r="R26" s="116">
+        <f>LOWER(TRIM(C26)&amp;"|"&amp;TRIM(D26)&amp;"|"&amp;TRIM(E26)&amp;"|"&amp;TRIM(F26)&amp;"|"&amp;TRIM(H26)&amp;"|"&amp;TRIM(I26))</f>
+        <v/>
+      </c>
+      <c r="S26" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R26)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T26" s="116" t="inlineStr">
+        <is>
+          <t>a7a713e8dfa53e0690b7dfa5957573d0cfd4551a85146b46de67eea1ee837eaa</t>
+        </is>
+      </c>
+      <c r="U26" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V26" s="118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="W26" s="117" t="inlineStr">
+        <is>
+          <t>用户要求；原创方块网格排布</t>
+        </is>
+      </c>
+      <c r="X26" s="113" t="inlineStr">
+        <is>
+          <t>01_部件/眼镜/眼镜__electronic_mask/表情__angry</t>
+        </is>
+      </c>
+      <c r="Y26" s="116" t="inlineStr">
+        <is>
+          <t>version_increment；父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；共享v005模型/动作双母版与SKEL-BUNNY01-004签名；独立稳定GLB/Prefab；112颗方块，颜色#ff3028，符号不闭眼；随机可达/命令/实际状态事件/Forward+真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="1412.65" customHeight="1" s="88">
+      <c r="A27" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED</t>
+        </is>
+      </c>
+      <c r="B27" s="117" t="inlineStr">
+        <is>
+          <t>电子面具表情：惊讶</t>
+        </is>
+      </c>
+      <c r="C27" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D27" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E27" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01_expression_surprised</t>
+        </is>
+      </c>
+      <c r="F27" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G27" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="H27" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I27" s="116" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="J27" s="116" t="inlineStr">
+        <is>
+          <t>独立角色表情系统</t>
+        </is>
+      </c>
+      <c r="K27" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L27" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M27" s="116" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N27" s="117" t="inlineStr">
+        <is>
+          <t>144颗11.8mm方块/14mm网格；自发光1.25；情绪无嘴部；图案加粗放大；#ffe45c；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="O27" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/runtime/chr_bunny01_expression_surprised_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P27" s="116" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/character_expression_system.md；src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="Q27" s="117" t="inlineStr">
+        <is>
+          <t>网格表情;情绪;符号;惊讶;surprised</t>
+        </is>
+      </c>
+      <c r="R27" s="116">
+        <f>LOWER(TRIM(C27)&amp;"|"&amp;TRIM(D27)&amp;"|"&amp;TRIM(E27)&amp;"|"&amp;TRIM(F27)&amp;"|"&amp;TRIM(H27)&amp;"|"&amp;TRIM(I27))</f>
+        <v/>
+      </c>
+      <c r="S27" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R27)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T27" s="116" t="inlineStr">
+        <is>
+          <t>fcf462e945994543ded0497e84dbfe44f33ff4d89d5422641fd93794a9747712</t>
+        </is>
+      </c>
+      <c r="U27" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V27" s="118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="W27" s="117" t="inlineStr">
+        <is>
+          <t>用户要求；原创方块网格排布</t>
+        </is>
+      </c>
+      <c r="X27" s="113" t="inlineStr">
+        <is>
+          <t>01_部件/眼镜/眼镜__electronic_mask/表情__surprised</t>
+        </is>
+      </c>
+      <c r="Y27" s="116" t="inlineStr">
+        <is>
+          <t>version_increment；父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；共享v005模型/动作双母版与SKEL-BUNNY01-004签名；独立稳定GLB/Prefab；144颗方块，颜色#ffe45c，符号不闭眼；随机可达/命令/实际状态事件/Forward+真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="1412.65" customHeight="1" s="88">
+      <c r="A28" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE</t>
+        </is>
+      </c>
+      <c r="B28" s="117" t="inlineStr">
+        <is>
+          <t>电子面具表情：爱心</t>
+        </is>
+      </c>
+      <c r="C28" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D28" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E28" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01_expression_love</t>
+        </is>
+      </c>
+      <c r="F28" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G28" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="H28" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I28" s="116" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="J28" s="116" t="inlineStr">
+        <is>
+          <t>独立角色表情系统</t>
+        </is>
+      </c>
+      <c r="K28" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L28" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M28" s="116" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N28" s="117" t="inlineStr">
+        <is>
+          <t>148颗11.8mm方块/14mm网格；自发光1.25；情绪无嘴部；图案加粗放大；#ff6abb；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="O28" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/runtime/chr_bunny01_expression_love_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P28" s="116" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/character_expression_system.md；src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="Q28" s="117" t="inlineStr">
+        <is>
+          <t>网格表情;情绪;符号;爱心;love</t>
+        </is>
+      </c>
+      <c r="R28" s="116">
+        <f>LOWER(TRIM(C28)&amp;"|"&amp;TRIM(D28)&amp;"|"&amp;TRIM(E28)&amp;"|"&amp;TRIM(F28)&amp;"|"&amp;TRIM(H28)&amp;"|"&amp;TRIM(I28))</f>
+        <v/>
+      </c>
+      <c r="S28" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R28)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T28" s="116" t="inlineStr">
+        <is>
+          <t>0c7c63c8bf72ba2dc21be59232dbfdebc982347d05eb13e1384646604229011d</t>
+        </is>
+      </c>
+      <c r="U28" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V28" s="118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="W28" s="117" t="inlineStr">
+        <is>
+          <t>用户要求；原创方块网格排布</t>
+        </is>
+      </c>
+      <c r="X28" s="113" t="inlineStr">
+        <is>
+          <t>01_部件/眼镜/眼镜__electronic_mask/表情__love</t>
+        </is>
+      </c>
+      <c r="Y28" s="116" t="inlineStr">
+        <is>
+          <t>version_increment；父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；共享v005模型/动作双母版与SKEL-BUNNY01-004签名；独立稳定GLB/Prefab；148颗方块，颜色#ff6abb，符号不闭眼；随机可达/命令/实际状态事件/Forward+真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="1412.65" customHeight="1" s="88">
+      <c r="A29" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION</t>
+        </is>
+      </c>
+      <c r="B29" s="117" t="inlineStr">
+        <is>
+          <t>电子面具表情：疑问</t>
+        </is>
+      </c>
+      <c r="C29" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D29" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E29" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01_expression_question</t>
+        </is>
+      </c>
+      <c r="F29" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G29" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="H29" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I29" s="116" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="J29" s="116" t="inlineStr">
+        <is>
+          <t>独立角色表情系统</t>
+        </is>
+      </c>
+      <c r="K29" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L29" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M29" s="116" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N29" s="117" t="inlineStr">
+        <is>
+          <t>112颗11.8mm方块/14mm网格；自发光1.25；情绪无嘴部；图案加粗放大；#ffd24a；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="O29" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/runtime/chr_bunny01_expression_question_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P29" s="116" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/character_expression_system.md；src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="Q29" s="117" t="inlineStr">
+        <is>
+          <t>网格表情;情绪;符号;疑问;question</t>
+        </is>
+      </c>
+      <c r="R29" s="116">
+        <f>LOWER(TRIM(C29)&amp;"|"&amp;TRIM(D29)&amp;"|"&amp;TRIM(E29)&amp;"|"&amp;TRIM(F29)&amp;"|"&amp;TRIM(H29)&amp;"|"&amp;TRIM(I29))</f>
+        <v/>
+      </c>
+      <c r="S29" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R29)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T29" s="116" t="inlineStr">
+        <is>
+          <t>9a682f546faf4a778a1db97d6c58e010b9db54814cf40cc91c3d4705603bd3c1</t>
+        </is>
+      </c>
+      <c r="U29" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V29" s="118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="W29" s="117" t="inlineStr">
+        <is>
+          <t>用户要求；原创方块网格排布</t>
+        </is>
+      </c>
+      <c r="X29" s="113" t="inlineStr">
+        <is>
+          <t>01_部件/眼镜/眼镜__electronic_mask/表情__question</t>
+        </is>
+      </c>
+      <c r="Y29" s="116" t="inlineStr">
+        <is>
+          <t>version_increment；父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；共享v005模型/动作双母版与SKEL-BUNNY01-004签名；独立稳定GLB/Prefab；112颗方块，颜色#ffd24a，符号不闭眼；随机可达/命令/实际状态事件/Forward+真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="1412.65" customHeight="1" s="88">
+      <c r="A30" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT</t>
+        </is>
+      </c>
+      <c r="B30" s="117" t="inlineStr">
+        <is>
+          <t>电子面具表情：警示</t>
+        </is>
+      </c>
+      <c r="C30" s="117" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="D30" s="116" t="inlineStr">
+        <is>
+          <t>player_accessory</t>
+        </is>
+      </c>
+      <c r="E30" s="116" t="inlineStr">
+        <is>
+          <t>player_capsule01_expression_alert</t>
+        </is>
+      </c>
+      <c r="F30" s="116" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="G30" s="116" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="H30" s="117" t="inlineStr">
+        <is>
+          <t>3D/正面+俯视</t>
+        </is>
+      </c>
+      <c r="I30" s="116" t="inlineStr">
+        <is>
+          <t>alert</t>
+        </is>
+      </c>
+      <c r="J30" s="116" t="inlineStr">
+        <is>
+          <t>独立角色表情系统</t>
+        </is>
+      </c>
+      <c r="K30" s="117" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L30" s="116" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M30" s="116" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N30" s="117" t="inlineStr">
+        <is>
+          <t>96颗11.8mm方块/14mm网格；自发光1.25；情绪无嘴部；图案加粗放大；#a1fff2；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="O30" s="116" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/runtime/chr_bunny01_expression_alert_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="P30" s="116" t="inlineStr">
+        <is>
+          <t>docs/v0.1/design/character_expression_system.md；src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="Q30" s="117" t="inlineStr">
+        <is>
+          <t>网格表情;情绪;符号;警示;alert</t>
+        </is>
+      </c>
+      <c r="R30" s="116">
+        <f>LOWER(TRIM(C30)&amp;"|"&amp;TRIM(D30)&amp;"|"&amp;TRIM(E30)&amp;"|"&amp;TRIM(F30)&amp;"|"&amp;TRIM(H30)&amp;"|"&amp;TRIM(I30))</f>
+        <v/>
+      </c>
+      <c r="S30" s="117">
+        <f>IF(COUNTIF($R$6:$R$30,R30)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T30" s="116" t="inlineStr">
+        <is>
+          <t>5c6f8b8035594d8c68e0159eda199b050f1261d22e648ae30738863ba5bcd3b3</t>
+        </is>
+      </c>
+      <c r="U30" s="116" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V30" s="118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="W30" s="117" t="inlineStr">
+        <is>
+          <t>用户要求；原创方块网格排布</t>
+        </is>
+      </c>
+      <c r="X30" s="113" t="inlineStr">
+        <is>
+          <t>01_部件/眼镜/眼镜__electronic_mask/表情__alert</t>
+        </is>
+      </c>
+      <c r="Y30" s="116" t="inlineStr">
+        <is>
+          <t>version_increment；父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；共享v005模型/动作双母版与SKEL-BUNNY01-004签名；独立稳定GLB/Prefab；96颗方块，颜色#a1fff2，符号不闭眼；随机可达/命令/实际状态事件/Forward+真实渲染通过。</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="88">
       <c r="C31" s="87" t="n"/>
@@ -4895,7 +5974,7 @@
     <row r="427" ht="84.75" customHeight="1" s="88"/>
     <row r="429" ht="120" customHeight="1" s="88"/>
   </sheetData>
-  <autoFilter ref="A5:X36"/>
+  <autoFilter ref="A5:Y30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -4942,7 +6021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="21.48" customWidth="1" style="87" min="1" max="1"/>
@@ -4975,6 +6054,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -7513,6 +8593,591 @@
       <c r="M43" s="122" t="inlineStr">
         <is>
           <t>presentation_only；无碰撞；不改变玩法；专项验证 verify_player3d_lower_body_socket_flow.tscn。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="88">
+      <c r="A44" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B44" s="122" t="inlineStr">
+        <is>
+          <t>glasses/electronic_mask</t>
+        </is>
+      </c>
+      <c r="C44" s="122" t="inlineStr">
+        <is>
+          <t>VisualRoot/BunnyRig/HeadJoint/FaceAccessorySocket/ElectronicMask</t>
+        </is>
+      </c>
+      <c r="D44" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E44" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_visual.glb</t>
+        </is>
+      </c>
+      <c r="F44" s="122" t="inlineStr">
+        <is>
+          <t>源0.630×0.479×0.257m；运行时继承玩家0.8表现倍率</t>
+        </is>
+      </c>
+      <c r="G44" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint局部原点；源曲面+Y前移0.009m</t>
+        </is>
+      </c>
+      <c r="H44" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I44" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" s="87" t="inlineStr">
+        <is>
+          <t>继承head姿态；局部Blink/闪烁；独立CharacterExpressionSystem选择8种网格，状态事件适配器调用</t>
+        </is>
+      </c>
+      <c r="K44" s="87" t="inlineStr">
+        <is>
+          <t>面饰槽，可独立替换/卸下</t>
+        </is>
+      </c>
+      <c r="L44" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M44" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；8种发光强度1.25；8个无嘴部表达子组件；11.8mm颗粒、加粗眼睛/爱心/符号；生气红色，?和!为符号；无玩法/碰撞权威。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="88">
+      <c r="A45" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B45" s="122" t="inlineStr">
+        <is>
+          <t>glasses/expression/neutral</t>
+        </is>
+      </c>
+      <c r="C45" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint/FaceAccessorySocket/ElectronicMask/Visual/ExpressionPixels</t>
+        </is>
+      </c>
+      <c r="D45" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E45" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/components/chr_bunny01_expression_neutral_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="F45" s="122" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；发光1.25；运行时继承角色比例</t>
+        </is>
+      </c>
+      <c r="G45" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint原点；原脸曲面前移9mm</t>
+        </is>
+      </c>
+      <c r="H45" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I45" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" s="87" t="inlineStr">
+        <is>
+          <t>无嘴部；加粗眼睛/爱心/符号；独立系统命令/随机/状态调用；共用Blender局部剪辑</t>
+        </is>
+      </c>
+      <c r="K45" s="87" t="inlineStr">
+        <is>
+          <t>只替换面具表情，不更换面饰配置</t>
+        </is>
+      </c>
+      <c r="L45" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M45" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL；平静；emotion；#21bfff；180颗；v003；共享父v005双母版</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="88">
+      <c r="A46" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B46" s="122" t="inlineStr">
+        <is>
+          <t>glasses/expression/happy</t>
+        </is>
+      </c>
+      <c r="C46" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint/FaceAccessorySocket/ElectronicMask/Visual/ExpressionPixels</t>
+        </is>
+      </c>
+      <c r="D46" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E46" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/components/chr_bunny01_expression_happy_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="F46" s="122" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；发光1.25；运行时继承角色比例</t>
+        </is>
+      </c>
+      <c r="G46" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint原点；原脸曲面前移9mm</t>
+        </is>
+      </c>
+      <c r="H46" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I46" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J46" s="87" t="inlineStr">
+        <is>
+          <t>无嘴部；加粗眼睛/爱心/符号；独立系统命令/随机/状态调用；共用Blender局部剪辑</t>
+        </is>
+      </c>
+      <c r="K46" s="87" t="inlineStr">
+        <is>
+          <t>只替换面具表情，不更换面饰配置</t>
+        </is>
+      </c>
+      <c r="L46" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M46" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY；开心；emotion；#29e9ff；116颗；v003；共享父v005双母版</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="88">
+      <c r="A47" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B47" s="122" t="inlineStr">
+        <is>
+          <t>glasses/expression/sad</t>
+        </is>
+      </c>
+      <c r="C47" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint/FaceAccessorySocket/ElectronicMask/Visual/ExpressionPixels</t>
+        </is>
+      </c>
+      <c r="D47" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E47" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/components/chr_bunny01_expression_sad_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="F47" s="122" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；发光1.25；运行时继承角色比例</t>
+        </is>
+      </c>
+      <c r="G47" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint原点；原脸曲面前移9mm</t>
+        </is>
+      </c>
+      <c r="H47" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I47" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" s="87" t="inlineStr">
+        <is>
+          <t>无嘴部；加粗眼睛/爱心/符号；独立系统命令/随机/状态调用；共用Blender局部剪辑</t>
+        </is>
+      </c>
+      <c r="K47" s="87" t="inlineStr">
+        <is>
+          <t>只替换面具表情，不更换面饰配置</t>
+        </is>
+      </c>
+      <c r="L47" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M47" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD；难过；emotion；#777bff；102颗；v003；共享父v005双母版</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="88">
+      <c r="A48" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B48" s="122" t="inlineStr">
+        <is>
+          <t>glasses/expression/angry</t>
+        </is>
+      </c>
+      <c r="C48" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint/FaceAccessorySocket/ElectronicMask/Visual/ExpressionPixels</t>
+        </is>
+      </c>
+      <c r="D48" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E48" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/components/chr_bunny01_expression_angry_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="F48" s="122" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；发光1.25；运行时继承角色比例</t>
+        </is>
+      </c>
+      <c r="G48" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint原点；原脸曲面前移9mm</t>
+        </is>
+      </c>
+      <c r="H48" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I48" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" s="87" t="inlineStr">
+        <is>
+          <t>无嘴部；加粗眼睛/爱心/符号；独立系统命令/随机/状态调用；共用Blender局部剪辑</t>
+        </is>
+      </c>
+      <c r="K48" s="87" t="inlineStr">
+        <is>
+          <t>只替换面具表情，不更换面饰配置</t>
+        </is>
+      </c>
+      <c r="L48" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M48" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY；生气；emotion；#ff3028；112颗；v003；共享父v005双母版</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="88">
+      <c r="A49" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B49" s="122" t="inlineStr">
+        <is>
+          <t>glasses/expression/surprised</t>
+        </is>
+      </c>
+      <c r="C49" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint/FaceAccessorySocket/ElectronicMask/Visual/ExpressionPixels</t>
+        </is>
+      </c>
+      <c r="D49" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E49" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/components/chr_bunny01_expression_surprised_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="F49" s="122" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；发光1.25；运行时继承角色比例</t>
+        </is>
+      </c>
+      <c r="G49" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint原点；原脸曲面前移9mm</t>
+        </is>
+      </c>
+      <c r="H49" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I49" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" s="87" t="inlineStr">
+        <is>
+          <t>无嘴部；加粗眼睛/爱心/符号；独立系统命令/随机/状态调用；共用Blender局部剪辑</t>
+        </is>
+      </c>
+      <c r="K49" s="87" t="inlineStr">
+        <is>
+          <t>只替换面具表情，不更换面饰配置</t>
+        </is>
+      </c>
+      <c r="L49" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M49" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED；惊讶；emotion；#ffe45c；144颗；v003；共享父v005双母版</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="88">
+      <c r="A50" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B50" s="122" t="inlineStr">
+        <is>
+          <t>glasses/expression/love</t>
+        </is>
+      </c>
+      <c r="C50" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint/FaceAccessorySocket/ElectronicMask/Visual/ExpressionPixels</t>
+        </is>
+      </c>
+      <c r="D50" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E50" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/components/chr_bunny01_expression_love_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="F50" s="122" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；发光1.25；运行时继承角色比例</t>
+        </is>
+      </c>
+      <c r="G50" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint原点；原脸曲面前移9mm</t>
+        </is>
+      </c>
+      <c r="H50" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I50" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" s="87" t="inlineStr">
+        <is>
+          <t>无嘴部；加粗眼睛/爱心/符号；独立系统命令/随机/状态调用；共用Blender局部剪辑</t>
+        </is>
+      </c>
+      <c r="K50" s="87" t="inlineStr">
+        <is>
+          <t>只替换面具表情，不更换面饰配置</t>
+        </is>
+      </c>
+      <c r="L50" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M50" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE；爱心；emotion；#ff6abb；148颗；v003；共享父v005双母版</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="88">
+      <c r="A51" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B51" s="122" t="inlineStr">
+        <is>
+          <t>glasses/expression/question</t>
+        </is>
+      </c>
+      <c r="C51" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint/FaceAccessorySocket/ElectronicMask/Visual/ExpressionPixels</t>
+        </is>
+      </c>
+      <c r="D51" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E51" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/components/chr_bunny01_expression_question_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="F51" s="122" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；发光1.25；运行时继承角色比例</t>
+        </is>
+      </c>
+      <c r="G51" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint原点；原脸曲面前移9mm</t>
+        </is>
+      </c>
+      <c r="H51" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I51" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" s="87" t="inlineStr">
+        <is>
+          <t>无嘴部；加粗眼睛/爱心/符号；独立系统命令/随机/状态调用；共用Blender局部剪辑</t>
+        </is>
+      </c>
+      <c r="K51" s="87" t="inlineStr">
+        <is>
+          <t>只替换面具表情，不更换面饰配置</t>
+        </is>
+      </c>
+      <c r="L51" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M51" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION；疑问；symbol；#ffd24a；112颗；v003；共享父v005双母版</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="88">
+      <c r="A52" s="122" t="inlineStr">
+        <is>
+          <t>player_capsule01_bunny01_3d</t>
+        </is>
+      </c>
+      <c r="B52" s="122" t="inlineStr">
+        <is>
+          <t>glasses/expression/alert</t>
+        </is>
+      </c>
+      <c r="C52" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint/FaceAccessorySocket/ElectronicMask/Visual/ExpressionPixels</t>
+        </is>
+      </c>
+      <c r="D52" s="122" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="E52" s="87" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/components/chr_bunny01_expression_alert_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="F52" s="122" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；发光1.25；运行时继承角色比例</t>
+        </is>
+      </c>
+      <c r="G52" s="122" t="inlineStr">
+        <is>
+          <t>HeadJoint原点；原脸曲面前移9mm</t>
+        </is>
+      </c>
+      <c r="H52" s="87" t="inlineStr">
+        <is>
+          <t>Blender +Y / Godot -Z；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="I52" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" s="87" t="inlineStr">
+        <is>
+          <t>无嘴部；加粗眼睛/爱心/符号；独立系统命令/随机/状态调用；共用Blender局部剪辑</t>
+        </is>
+      </c>
+      <c r="K52" s="87" t="inlineStr">
+        <is>
+          <t>只替换面具表情，不更换面饰配置</t>
+        </is>
+      </c>
+      <c r="L52" s="87" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M52" s="87" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT；警示；symbol；#a1fff2；96颗；v003；共享父v005双母版</t>
         </is>
       </c>
     </row>
@@ -7539,7 +9204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.94" customWidth="1" style="87" min="1" max="1"/>
@@ -9462,6 +11127,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44" ht="12.65" customHeight="1" s="88">
       <c r="A44" s="122" t="inlineStr">
         <is>
@@ -9721,6 +11387,688 @@
       <c r="L49" s="87" t="inlineStr">
         <is>
           <t>第三段结束强制复位；受伤/冲刺/坠落/锁定/死亡/换武器全部取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="57.75" customHeight="1" s="88">
+      <c r="A50" s="127" t="inlineStr">
+        <is>
+          <t>面饰局部剪辑（非玩家状态）</t>
+        </is>
+      </c>
+      <c r="B50" s="128" t="inlineStr">
+        <is>
+          <t>mask_idle</t>
+        </is>
+      </c>
+      <c r="C50" s="127" t="inlineStr">
+        <is>
+          <t>电子面具：2.8/7.2s眨眼；5.1/10.1s短闪；首尾张眼亮度1</t>
+        </is>
+      </c>
+      <c r="D50" s="128" t="inlineStr">
+        <is>
+          <t>ExpressionPlayer / Blender独立动作母版</t>
+        </is>
+      </c>
+      <c r="E50" s="128" t="inlineStr">
+        <is>
+          <t>局部剪辑结束恢复张眼/亮度1；不跳转玩家状态</t>
+        </is>
+      </c>
+      <c r="F50" s="128" t="inlineStr">
+        <is>
+          <t>保持原姿态</t>
+        </is>
+      </c>
+      <c r="G50" s="127" t="inlineStr">
+        <is>
+          <t>只对面具Blink与发光强度采样</t>
+        </is>
+      </c>
+      <c r="H50" s="127" t="inlineStr">
+        <is>
+          <t>不修改</t>
+        </is>
+      </c>
+      <c r="I50" s="127" t="inlineStr">
+        <is>
+          <t>不修改WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J50" s="127" t="inlineStr">
+        <is>
+          <t>不修改</t>
+        </is>
+      </c>
+      <c r="K50" s="128" t="inlineStr">
+        <is>
+          <t>12s；循环=True；glasses/electronic_mask</t>
+        </is>
+      </c>
+      <c r="L50" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；LINEAR；AnimationLibrary来自Blender曲线；verify_electronic_mask_flow通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="57.75" customHeight="1" s="88">
+      <c r="A51" s="127" t="inlineStr">
+        <is>
+          <t>面饰局部剪辑（非玩家状态）</t>
+        </is>
+      </c>
+      <c r="B51" s="128" t="inlineStr">
+        <is>
+          <t>mask_blink</t>
+        </is>
+      </c>
+      <c r="C51" s="127" t="inlineStr">
+        <is>
+          <t>电子面具：0.09s闭眼→0.16s结束保持→0.26s张眼</t>
+        </is>
+      </c>
+      <c r="D51" s="128" t="inlineStr">
+        <is>
+          <t>ExpressionPlayer / Blender独立动作母版</t>
+        </is>
+      </c>
+      <c r="E51" s="128" t="inlineStr">
+        <is>
+          <t>局部剪辑结束恢复张眼/亮度1；不跳转玩家状态</t>
+        </is>
+      </c>
+      <c r="F51" s="128" t="inlineStr">
+        <is>
+          <t>保持原姿态</t>
+        </is>
+      </c>
+      <c r="G51" s="127" t="inlineStr">
+        <is>
+          <t>只对面具Blink与发光强度采样</t>
+        </is>
+      </c>
+      <c r="H51" s="127" t="inlineStr">
+        <is>
+          <t>不修改</t>
+        </is>
+      </c>
+      <c r="I51" s="127" t="inlineStr">
+        <is>
+          <t>不修改WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J51" s="127" t="inlineStr">
+        <is>
+          <t>不修改</t>
+        </is>
+      </c>
+      <c r="K51" s="128" t="inlineStr">
+        <is>
+          <t>0.26s；循环=False；glasses/electronic_mask</t>
+        </is>
+      </c>
+      <c r="L51" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；LINEAR；AnimationLibrary来自Blender曲线；verify_electronic_mask_flow通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="57.75" customHeight="1" s="88">
+      <c r="A52" s="127" t="inlineStr">
+        <is>
+          <t>面饰局部剪辑（非玩家状态）</t>
+        </is>
+      </c>
+      <c r="B52" s="128" t="inlineStr">
+        <is>
+          <t>mask_flicker</t>
+        </is>
+      </c>
+      <c r="C52" s="127" t="inlineStr">
+        <is>
+          <t>电子面具：亮度1→0.18→1→0.35→1→0.55→1，0.42s回稳</t>
+        </is>
+      </c>
+      <c r="D52" s="128" t="inlineStr">
+        <is>
+          <t>ExpressionPlayer / Blender独立动作母版</t>
+        </is>
+      </c>
+      <c r="E52" s="128" t="inlineStr">
+        <is>
+          <t>局部剪辑结束恢复张眼/亮度1；不跳转玩家状态</t>
+        </is>
+      </c>
+      <c r="F52" s="128" t="inlineStr">
+        <is>
+          <t>保持原姿态</t>
+        </is>
+      </c>
+      <c r="G52" s="127" t="inlineStr">
+        <is>
+          <t>只对面具Blink与发光强度采样</t>
+        </is>
+      </c>
+      <c r="H52" s="127" t="inlineStr">
+        <is>
+          <t>不修改</t>
+        </is>
+      </c>
+      <c r="I52" s="127" t="inlineStr">
+        <is>
+          <t>不修改WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J52" s="127" t="inlineStr">
+        <is>
+          <t>不修改</t>
+        </is>
+      </c>
+      <c r="K52" s="128" t="inlineStr">
+        <is>
+          <t>0.42s；循环=False；glasses/electronic_mask</t>
+        </is>
+      </c>
+      <c r="L52" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；LINEAR；AnimationLibrary来自Blender曲线；verify_electronic_mask_flow通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="57.75" customHeight="1" s="88">
+      <c r="A53" s="127" t="inlineStr">
+        <is>
+          <t>面饰网格表情（非玩法状态）</t>
+        </is>
+      </c>
+      <c r="B53" s="128" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C53" s="127" t="inlineStr">
+        <is>
+          <t>平静</t>
+        </is>
+      </c>
+      <c r="D53" s="128" t="inlineStr">
+        <is>
+          <t>独立系统request_expression / 随机 / 状态适配命令</t>
+        </is>
+      </c>
+      <c r="E53" s="128" t="inlineStr">
+        <is>
+          <t>其他表情；保持结束恢复背景随机</t>
+        </is>
+      </c>
+      <c r="F53" s="128" t="inlineStr">
+        <is>
+          <t>保持原动作</t>
+        </is>
+      </c>
+      <c r="G53" s="127" t="inlineStr">
+        <is>
+          <t>只显示面具方块网格</t>
+        </is>
+      </c>
+      <c r="H53" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="I53" s="127" t="inlineStr">
+        <is>
+          <t>不改变武器</t>
+        </is>
+      </c>
+      <c r="J53" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="K53" s="128" t="inlineStr">
+        <is>
+          <t>#21bfff；emotion</t>
+        </is>
+      </c>
+      <c r="L53" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL；子v003/父v005；180颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="57.75" customHeight="1" s="88">
+      <c r="A54" s="127" t="inlineStr">
+        <is>
+          <t>面饰网格表情（非玩法状态）</t>
+        </is>
+      </c>
+      <c r="B54" s="128" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="C54" s="127" t="inlineStr">
+        <is>
+          <t>开心</t>
+        </is>
+      </c>
+      <c r="D54" s="128" t="inlineStr">
+        <is>
+          <t>独立系统request_expression / 随机 / 状态适配命令</t>
+        </is>
+      </c>
+      <c r="E54" s="128" t="inlineStr">
+        <is>
+          <t>其他表情；保持结束恢复背景随机</t>
+        </is>
+      </c>
+      <c r="F54" s="128" t="inlineStr">
+        <is>
+          <t>保持原动作</t>
+        </is>
+      </c>
+      <c r="G54" s="127" t="inlineStr">
+        <is>
+          <t>只显示面具方块网格</t>
+        </is>
+      </c>
+      <c r="H54" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="I54" s="127" t="inlineStr">
+        <is>
+          <t>不改变武器</t>
+        </is>
+      </c>
+      <c r="J54" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="K54" s="128" t="inlineStr">
+        <is>
+          <t>#29e9ff；emotion</t>
+        </is>
+      </c>
+      <c r="L54" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY；子v003/父v005；116颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="57.75" customHeight="1" s="88">
+      <c r="A55" s="127" t="inlineStr">
+        <is>
+          <t>面饰网格表情（非玩法状态）</t>
+        </is>
+      </c>
+      <c r="B55" s="128" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="C55" s="127" t="inlineStr">
+        <is>
+          <t>难过</t>
+        </is>
+      </c>
+      <c r="D55" s="128" t="inlineStr">
+        <is>
+          <t>独立系统request_expression / 随机 / 状态适配命令</t>
+        </is>
+      </c>
+      <c r="E55" s="128" t="inlineStr">
+        <is>
+          <t>其他表情；保持结束恢复背景随机</t>
+        </is>
+      </c>
+      <c r="F55" s="128" t="inlineStr">
+        <is>
+          <t>保持原动作</t>
+        </is>
+      </c>
+      <c r="G55" s="127" t="inlineStr">
+        <is>
+          <t>只显示面具方块网格</t>
+        </is>
+      </c>
+      <c r="H55" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="I55" s="127" t="inlineStr">
+        <is>
+          <t>不改变武器</t>
+        </is>
+      </c>
+      <c r="J55" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="K55" s="128" t="inlineStr">
+        <is>
+          <t>#777bff；emotion</t>
+        </is>
+      </c>
+      <c r="L55" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD；子v003/父v005；102颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="57.75" customHeight="1" s="88">
+      <c r="A56" s="127" t="inlineStr">
+        <is>
+          <t>面饰网格表情（非玩法状态）</t>
+        </is>
+      </c>
+      <c r="B56" s="128" t="inlineStr">
+        <is>
+          <t>angry</t>
+        </is>
+      </c>
+      <c r="C56" s="127" t="inlineStr">
+        <is>
+          <t>生气</t>
+        </is>
+      </c>
+      <c r="D56" s="128" t="inlineStr">
+        <is>
+          <t>独立系统request_expression / 随机 / 状态适配命令</t>
+        </is>
+      </c>
+      <c r="E56" s="128" t="inlineStr">
+        <is>
+          <t>其他表情；保持结束恢复背景随机</t>
+        </is>
+      </c>
+      <c r="F56" s="128" t="inlineStr">
+        <is>
+          <t>保持原动作</t>
+        </is>
+      </c>
+      <c r="G56" s="127" t="inlineStr">
+        <is>
+          <t>只显示面具方块网格</t>
+        </is>
+      </c>
+      <c r="H56" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="I56" s="127" t="inlineStr">
+        <is>
+          <t>不改变武器</t>
+        </is>
+      </c>
+      <c r="J56" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="K56" s="128" t="inlineStr">
+        <is>
+          <t>#ff3028；emotion</t>
+        </is>
+      </c>
+      <c r="L56" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY；子v003/父v005；112颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="57.75" customHeight="1" s="88">
+      <c r="A57" s="127" t="inlineStr">
+        <is>
+          <t>面饰网格表情（非玩法状态）</t>
+        </is>
+      </c>
+      <c r="B57" s="128" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="C57" s="127" t="inlineStr">
+        <is>
+          <t>惊讶</t>
+        </is>
+      </c>
+      <c r="D57" s="128" t="inlineStr">
+        <is>
+          <t>独立系统request_expression / 随机 / 状态适配命令</t>
+        </is>
+      </c>
+      <c r="E57" s="128" t="inlineStr">
+        <is>
+          <t>其他表情；保持结束恢复背景随机</t>
+        </is>
+      </c>
+      <c r="F57" s="128" t="inlineStr">
+        <is>
+          <t>保持原动作</t>
+        </is>
+      </c>
+      <c r="G57" s="127" t="inlineStr">
+        <is>
+          <t>只显示面具方块网格</t>
+        </is>
+      </c>
+      <c r="H57" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="I57" s="127" t="inlineStr">
+        <is>
+          <t>不改变武器</t>
+        </is>
+      </c>
+      <c r="J57" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="K57" s="128" t="inlineStr">
+        <is>
+          <t>#ffe45c；emotion</t>
+        </is>
+      </c>
+      <c r="L57" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED；子v003/父v005；144颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="57.75" customHeight="1" s="88">
+      <c r="A58" s="127" t="inlineStr">
+        <is>
+          <t>面饰网格表情（非玩法状态）</t>
+        </is>
+      </c>
+      <c r="B58" s="128" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="C58" s="127" t="inlineStr">
+        <is>
+          <t>爱心</t>
+        </is>
+      </c>
+      <c r="D58" s="128" t="inlineStr">
+        <is>
+          <t>独立系统request_expression / 随机 / 状态适配命令</t>
+        </is>
+      </c>
+      <c r="E58" s="128" t="inlineStr">
+        <is>
+          <t>其他表情；保持结束恢复背景随机</t>
+        </is>
+      </c>
+      <c r="F58" s="128" t="inlineStr">
+        <is>
+          <t>保持原动作</t>
+        </is>
+      </c>
+      <c r="G58" s="127" t="inlineStr">
+        <is>
+          <t>只显示面具方块网格</t>
+        </is>
+      </c>
+      <c r="H58" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="I58" s="127" t="inlineStr">
+        <is>
+          <t>不改变武器</t>
+        </is>
+      </c>
+      <c r="J58" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="K58" s="128" t="inlineStr">
+        <is>
+          <t>#ff6abb；emotion</t>
+        </is>
+      </c>
+      <c r="L58" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE；子v003/父v005；148颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="57.75" customHeight="1" s="88">
+      <c r="A59" s="127" t="inlineStr">
+        <is>
+          <t>面饰网格表情（非玩法状态）</t>
+        </is>
+      </c>
+      <c r="B59" s="128" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C59" s="127" t="inlineStr">
+        <is>
+          <t>疑问</t>
+        </is>
+      </c>
+      <c r="D59" s="128" t="inlineStr">
+        <is>
+          <t>独立系统request_expression / 随机 / 状态适配命令</t>
+        </is>
+      </c>
+      <c r="E59" s="128" t="inlineStr">
+        <is>
+          <t>其他表情；保持结束恢复背景随机</t>
+        </is>
+      </c>
+      <c r="F59" s="128" t="inlineStr">
+        <is>
+          <t>保持原动作</t>
+        </is>
+      </c>
+      <c r="G59" s="127" t="inlineStr">
+        <is>
+          <t>只显示面具方块网格</t>
+        </is>
+      </c>
+      <c r="H59" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="I59" s="127" t="inlineStr">
+        <is>
+          <t>不改变武器</t>
+        </is>
+      </c>
+      <c r="J59" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="K59" s="128" t="inlineStr">
+        <is>
+          <t>#ffd24a；symbol</t>
+        </is>
+      </c>
+      <c r="L59" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION；子v003/父v005；112颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="57.75" customHeight="1" s="88">
+      <c r="A60" s="127" t="inlineStr">
+        <is>
+          <t>面饰网格表情（非玩法状态）</t>
+        </is>
+      </c>
+      <c r="B60" s="128" t="inlineStr">
+        <is>
+          <t>alert</t>
+        </is>
+      </c>
+      <c r="C60" s="127" t="inlineStr">
+        <is>
+          <t>警示</t>
+        </is>
+      </c>
+      <c r="D60" s="128" t="inlineStr">
+        <is>
+          <t>独立系统request_expression / 随机 / 状态适配命令</t>
+        </is>
+      </c>
+      <c r="E60" s="128" t="inlineStr">
+        <is>
+          <t>其他表情；保持结束恢复背景随机</t>
+        </is>
+      </c>
+      <c r="F60" s="128" t="inlineStr">
+        <is>
+          <t>保持原动作</t>
+        </is>
+      </c>
+      <c r="G60" s="127" t="inlineStr">
+        <is>
+          <t>只显示面具方块网格</t>
+        </is>
+      </c>
+      <c r="H60" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="I60" s="127" t="inlineStr">
+        <is>
+          <t>不改变武器</t>
+        </is>
+      </c>
+      <c r="J60" s="127" t="inlineStr">
+        <is>
+          <t>不改变</t>
+        </is>
+      </c>
+      <c r="K60" s="128" t="inlineStr">
+        <is>
+          <t>#a1fff2；symbol</t>
+        </is>
+      </c>
+      <c r="L60" s="127" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT；子v003/父v005；96颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
         </is>
       </c>
     </row>
@@ -9777,6 +12125,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -10120,6 +12469,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="31.5" customHeight="1" s="88">
       <c r="A15" s="107" t="inlineStr">
         <is>
@@ -10330,6 +12680,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="88">
       <c r="A21" s="141" t="inlineStr">
         <is>
@@ -10337,6 +12688,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="88">
       <c r="A23" s="142" t="inlineStr">
         <is>
@@ -10365,6 +12717,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="33.75" customHeight="1" s="88">
       <c r="A28" s="145" t="inlineStr">
         <is>
@@ -10404,7 +12757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.1" customWidth="1" style="87" min="1" max="1"/>
@@ -10740,82 +13093,1764 @@
       </c>
     </row>
     <row r="18" ht="64.5" customHeight="1" s="88">
-      <c r="A18" s="91" t="n"/>
-      <c r="B18" s="91" t="n"/>
-      <c r="C18" s="91" t="n"/>
-      <c r="D18" s="91" t="n"/>
+      <c r="A18" s="91" t="inlineStr">
+        <is>
+          <t>电子面具v002/模型母版</t>
+        </is>
+      </c>
+      <c r="B18" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v002.blend</t>
+        </is>
+      </c>
+      <c r="C18" s="150" t="inlineStr">
+        <is>
+          <t>18b1a86a99602766a67d6a171763d6e896aacf7929165b318ce9be455dac639f</t>
+        </is>
+      </c>
+      <c r="D18" s="91" t="n">
+        <v>10736216</v>
+      </c>
     </row>
     <row r="19" ht="64.5" customHeight="1" s="88">
-      <c r="A19" s="91" t="n"/>
-      <c r="B19" s="91" t="n"/>
-      <c r="C19" s="91" t="n"/>
-      <c r="D19" s="91" t="n"/>
+      <c r="A19" s="91" t="inlineStr">
+        <is>
+          <t>电子面具v002/动作母版</t>
+        </is>
+      </c>
+      <c r="B19" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v002.blend</t>
+        </is>
+      </c>
+      <c r="C19" s="150" t="inlineStr">
+        <is>
+          <t>69ce39f9e65006b33e057e0e8c6234c8c39cbff0a9940fbc780f71cf92f98fc5</t>
+        </is>
+      </c>
+      <c r="D19" s="91" t="n">
+        <v>10749168</v>
+      </c>
     </row>
     <row r="20" ht="64.5" customHeight="1" s="88">
-      <c r="A20" s="91" t="n"/>
-      <c r="B20" s="91" t="n"/>
-      <c r="C20" s="91" t="n"/>
-      <c r="D20" s="91" t="n"/>
+      <c r="A20" s="91" t="inlineStr">
+        <is>
+          <t>电子面具v002/视觉与形态键</t>
+        </is>
+      </c>
+      <c r="B20" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_visual.glb</t>
+        </is>
+      </c>
+      <c r="C20" s="150" t="inlineStr">
+        <is>
+          <t>803aaa209e8cb3ca1a90e44be76bd39fb95dbdf24f574ea4f8baea68676d3033</t>
+        </is>
+      </c>
+      <c r="D20" s="91" t="n">
+        <v>357976</v>
+      </c>
     </row>
     <row r="21" ht="64.5" customHeight="1" s="88">
-      <c r="A21" s="91" t="n"/>
-      <c r="B21" s="91" t="n"/>
-      <c r="C21" s="91" t="n"/>
-      <c r="D21" s="91" t="n"/>
+      <c r="A21" s="91" t="inlineStr">
+        <is>
+          <t>电子面具v002/动画库</t>
+        </is>
+      </c>
+      <c r="B21" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_animations.tres</t>
+        </is>
+      </c>
+      <c r="C21" s="150" t="inlineStr">
+        <is>
+          <t>1661fd60ac07f06dc0b84ff8a3344fe310e1ecaeacb1b63891f3f3e96212f6ee</t>
+        </is>
+      </c>
+      <c r="D21" s="91" t="n">
+        <v>2815</v>
+      </c>
     </row>
     <row r="22" ht="64.5" customHeight="1" s="88">
-      <c r="A22" s="91" t="n"/>
-      <c r="B22" s="91" t="n"/>
-      <c r="C22" s="91" t="n"/>
-      <c r="D22" s="91" t="n"/>
+      <c r="A22" s="91" t="inlineStr">
+        <is>
+          <t>电子面具v002/曲线中转</t>
+        </is>
+      </c>
+      <c r="B22" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_expression_curves.json</t>
+        </is>
+      </c>
+      <c r="C22" s="150" t="inlineStr">
+        <is>
+          <t>c163daaeb8dccfb9d3a94509bd0d845330cc048b5a40a6e3d21b51bf05fbd30a</t>
+        </is>
+      </c>
+      <c r="D22" s="91" t="n">
+        <v>3318</v>
+      </c>
     </row>
     <row r="23" ht="64.5" customHeight="1" s="88">
-      <c r="A23" s="91" t="n"/>
-      <c r="B23" s="91" t="n"/>
-      <c r="C23" s="91" t="n"/>
-      <c r="D23" s="91" t="n"/>
+      <c r="A23" s="91" t="inlineStr">
+        <is>
+          <t>电子面具v002/运行包装</t>
+        </is>
+      </c>
+      <c r="B23" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_root.tscn</t>
+        </is>
+      </c>
+      <c r="C23" s="150" t="inlineStr">
+        <is>
+          <t>b7d9f1b45f58ec4fcbc295f5605e5050333cd7cb6c762ada53bf7aca74a19823</t>
+        </is>
+      </c>
+      <c r="D23" s="91" t="n">
+        <v>1136</v>
+      </c>
     </row>
     <row r="24" ht="64.5" customHeight="1" s="88">
-      <c r="A24" s="91" t="n"/>
-      <c r="B24" s="91" t="n"/>
-      <c r="C24" s="91" t="n"/>
-      <c r="D24" s="91" t="n"/>
+      <c r="A24" s="91" t="inlineStr">
+        <is>
+          <t>电子面具v002/局部表现适配器</t>
+        </is>
+      </c>
+      <c r="B24" s="150" t="inlineStr">
+        <is>
+          <t>src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="C24" s="150" t="inlineStr">
+        <is>
+          <t>ad3945897abf4ccf9c9671673d89a8f3984de7c76d87a18da0610fca13125a51</t>
+        </is>
+      </c>
+      <c r="D24" s="91" t="n">
+        <v>1010</v>
+      </c>
     </row>
     <row r="25" ht="64.5" customHeight="1" s="88">
-      <c r="A25" s="91" t="n"/>
-      <c r="B25" s="91" t="n"/>
-      <c r="C25" s="91" t="n"/>
-      <c r="D25" s="91" t="n"/>
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B25" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v003.blend</t>
+        </is>
+      </c>
+      <c r="C25" s="150" t="inlineStr">
+        <is>
+          <t>b65f35b46b15ce3099ea4d9a74837ccbffa5aa5ebb2258f59fc8f75b37ad32db</t>
+        </is>
+      </c>
+      <c r="D25" s="91" t="n">
+        <v>11562372</v>
+      </c>
     </row>
     <row r="26" ht="64.5" customHeight="1" s="88">
-      <c r="A26" s="91" t="n"/>
-      <c r="B26" s="91" t="n"/>
-      <c r="C26" s="91" t="n"/>
-      <c r="D26" s="91" t="n"/>
+      <c r="A26" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B26" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v003.blend</t>
+        </is>
+      </c>
+      <c r="C26" s="150" t="inlineStr">
+        <is>
+          <t>0276460eba4957a6927b7172ba89b4c09c592ef919ad7424c4ede477a1708eb1</t>
+        </is>
+      </c>
+      <c r="D26" s="91" t="n">
+        <v>11603653</v>
+      </c>
     </row>
     <row r="27" ht="64.5" customHeight="1" s="88">
-      <c r="A27" s="91" t="n"/>
-      <c r="B27" s="91" t="n"/>
-      <c r="C27" s="91" t="n"/>
-      <c r="D27" s="91" t="n"/>
+      <c r="A27" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B27" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_visual.glb</t>
+        </is>
+      </c>
+      <c r="C27" s="150" t="inlineStr">
+        <is>
+          <t>202720510b5b42693bd1da781d8e69fca63bf2f0e4153d413604a80c0da9537e</t>
+        </is>
+      </c>
+      <c r="D27" s="91" t="n">
+        <v>363900</v>
+      </c>
     </row>
     <row r="28" ht="64.5" customHeight="1" s="88">
-      <c r="A28" s="91" t="n"/>
-      <c r="B28" s="91" t="n"/>
-      <c r="C28" s="91" t="n"/>
-      <c r="D28" s="91" t="n"/>
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B28" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_animations.tres</t>
+        </is>
+      </c>
+      <c r="C28" s="150" t="inlineStr">
+        <is>
+          <t>1661fd60ac07f06dc0b84ff8a3344fe310e1ecaeacb1b63891f3f3e96212f6ee</t>
+        </is>
+      </c>
+      <c r="D28" s="91" t="n">
+        <v>2815</v>
+      </c>
     </row>
     <row r="29" ht="64.5" customHeight="1" s="88">
-      <c r="A29" s="91" t="n"/>
-      <c r="B29" s="91" t="n"/>
-      <c r="C29" s="91" t="n"/>
-      <c r="D29" s="91" t="n"/>
+      <c r="A29" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B29" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_expression_curves.json</t>
+        </is>
+      </c>
+      <c r="C29" s="150" t="inlineStr">
+        <is>
+          <t>c4516d1d2477b0fa66e7b641a2d138c8965e211c79577bdd3801b58ef966e79f</t>
+        </is>
+      </c>
+      <c r="D29" s="91" t="n">
+        <v>3318</v>
+      </c>
     </row>
     <row r="30" ht="64.5" customHeight="1" s="88">
-      <c r="A30" s="91" t="n"/>
-      <c r="B30" s="91" t="n"/>
-      <c r="C30" s="91" t="n"/>
-      <c r="D30" s="91" t="n"/>
+      <c r="A30" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B30" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_expression_catalog.json</t>
+        </is>
+      </c>
+      <c r="C30" s="150" t="inlineStr">
+        <is>
+          <t>582a214dc11f00828e0f523251bfc2bc4e6ebc881583867b9c36e2b38921e441</t>
+        </is>
+      </c>
+      <c r="D30" s="91" t="n">
+        <v>4086</v>
+      </c>
+    </row>
+    <row r="31" ht="64.5" customHeight="1" s="88">
+      <c r="A31" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B31" s="150" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionCatalog.gd</t>
+        </is>
+      </c>
+      <c r="C31" s="150" t="inlineStr">
+        <is>
+          <t>317238d4097979b0b400cb108c8123be52dc4f6a80148c215f729bc7282c3532</t>
+        </is>
+      </c>
+      <c r="D31" s="91" t="n">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="32" ht="64.5" customHeight="1" s="88">
+      <c r="A32" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B32" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_root.tscn</t>
+        </is>
+      </c>
+      <c r="C32" s="150" t="inlineStr">
+        <is>
+          <t>cb2ee2260277cfa752e4b4d5106577c17c8077df66b6838c9b5e6a6cfab390f5</t>
+        </is>
+      </c>
+      <c r="D32" s="91" t="n">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="33" ht="64.5" customHeight="1" s="88">
+      <c r="A33" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B33" s="150" t="inlineStr">
+        <is>
+          <t>src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="C33" s="150" t="inlineStr">
+        <is>
+          <t>28d3719c2a94638456ad5bd55ab8f0aecfe5d4537316b77d890e8e839cb69928</t>
+        </is>
+      </c>
+      <c r="D33" s="91" t="n">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="34" ht="64.5" customHeight="1" s="88">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B34" s="150" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="C34" s="150" t="inlineStr">
+        <is>
+          <t>2dc13da3dc63ee19001aa864f1a39ab1b742a2b3bebe782b74884edf0ec656b9</t>
+        </is>
+      </c>
+      <c r="D34" s="91" t="n">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="35" ht="64.5" customHeight="1" s="88">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v003</t>
+        </is>
+      </c>
+      <c r="B35" s="150" t="inlineStr">
+        <is>
+          <t>src/player3d/PlayerExpressionStateAdapter.gd</t>
+        </is>
+      </c>
+      <c r="C35" s="150" t="inlineStr">
+        <is>
+          <t>5ff3c07ac210eb22e99e7dc3ac22672ac24767ddd8aff1b8450ebfadd15d067a</t>
+        </is>
+      </c>
+      <c r="D35" s="91" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="36" ht="64.5" customHeight="1" s="88">
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL v001</t>
+        </is>
+      </c>
+      <c r="B36" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/components/chr_bunny01_expression_neutral_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C36" s="150" t="inlineStr">
+        <is>
+          <t>12077bb9e475d69790e680aed4f8a6c77581ff1090bb76fdfbd625488d77cc6e</t>
+        </is>
+      </c>
+      <c r="D36" s="91" t="n">
+        <v>211016</v>
+      </c>
+    </row>
+    <row r="37" ht="64.5" customHeight="1" s="88">
+      <c r="A37" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL v001</t>
+        </is>
+      </c>
+      <c r="B37" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/runtime/chr_bunny01_expression_neutral_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C37" s="150" t="inlineStr">
+        <is>
+          <t>91b3651370db63bdf2fdc4fdb6ecea1b4f7029cf3c783db93236e167d1875a3c</t>
+        </is>
+      </c>
+      <c r="D37" s="91" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="38" ht="64.5" customHeight="1" s="88">
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY v001</t>
+        </is>
+      </c>
+      <c r="B38" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/components/chr_bunny01_expression_happy_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C38" s="150" t="inlineStr">
+        <is>
+          <t>ca9ad2f734889f05dd1bfb7df7606b943bc1cffc4ff1cf06a7eecf61f4706ea7</t>
+        </is>
+      </c>
+      <c r="D38" s="91" t="n">
+        <v>82432</v>
+      </c>
+    </row>
+    <row r="39" ht="64.5" customHeight="1" s="88">
+      <c r="A39" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY v001</t>
+        </is>
+      </c>
+      <c r="B39" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/runtime/chr_bunny01_expression_happy_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C39" s="150" t="inlineStr">
+        <is>
+          <t>ce9c4707990891e7bdc3be61c5feee44697744511db5b5766f99888dbbc5b174</t>
+        </is>
+      </c>
+      <c r="D39" s="91" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="40" ht="64.5" customHeight="1" s="88">
+      <c r="A40" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD v001</t>
+        </is>
+      </c>
+      <c r="B40" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/components/chr_bunny01_expression_sad_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C40" s="150" t="inlineStr">
+        <is>
+          <t>0384111e3089f04ac8eda3db5705db67271fb75d03072af24c147a7434c6d1e9</t>
+        </is>
+      </c>
+      <c r="D40" s="91" t="n">
+        <v>105680</v>
+      </c>
+    </row>
+    <row r="41" ht="64.5" customHeight="1" s="88">
+      <c r="A41" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD v001</t>
+        </is>
+      </c>
+      <c r="B41" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/runtime/chr_bunny01_expression_sad_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C41" s="150" t="inlineStr">
+        <is>
+          <t>c1d0deeb2343d5f1fefa01b66a83f22b429691f53f0afbf62444ed62ff258d56</t>
+        </is>
+      </c>
+      <c r="D41" s="91" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="42" ht="64.5" customHeight="1" s="88">
+      <c r="A42" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY v001</t>
+        </is>
+      </c>
+      <c r="B42" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/components/chr_bunny01_expression_angry_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C42" s="150" t="inlineStr">
+        <is>
+          <t>92c73e23d1968f01d9db45035cdd9c29510bffe7cad29a8e9df7bb5bd38cbb32</t>
+        </is>
+      </c>
+      <c r="D42" s="91" t="n">
+        <v>120928</v>
+      </c>
+    </row>
+    <row r="43" ht="64.5" customHeight="1" s="88">
+      <c r="A43" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY v001</t>
+        </is>
+      </c>
+      <c r="B43" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/runtime/chr_bunny01_expression_angry_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C43" s="150" t="inlineStr">
+        <is>
+          <t>ad72d2042529794a2ee8a82cf9df5e5dc29cd10fc7e2cee3c11466d9fb46ba03</t>
+        </is>
+      </c>
+      <c r="D43" s="91" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="44" ht="64.5" customHeight="1" s="88">
+      <c r="A44" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED v001</t>
+        </is>
+      </c>
+      <c r="B44" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/components/chr_bunny01_expression_surprised_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C44" s="150" t="inlineStr">
+        <is>
+          <t>2bacbebfc50f1dc2b777a2e6b2a7409c7852647e19288fd69f7f634c1245d674</t>
+        </is>
+      </c>
+      <c r="D44" s="91" t="n">
+        <v>119648</v>
+      </c>
+    </row>
+    <row r="45" ht="64.5" customHeight="1" s="88">
+      <c r="A45" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED v001</t>
+        </is>
+      </c>
+      <c r="B45" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/runtime/chr_bunny01_expression_surprised_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C45" s="150" t="inlineStr">
+        <is>
+          <t>44722cf9090a68981d9dc39172178171242b4df738e211bbd5691b1747f7c662</t>
+        </is>
+      </c>
+      <c r="D45" s="91" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="46" ht="64.5" customHeight="1" s="88">
+      <c r="A46" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE v001</t>
+        </is>
+      </c>
+      <c r="B46" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/components/chr_bunny01_expression_love_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C46" s="150" t="inlineStr">
+        <is>
+          <t>f6546ffaa46abdf145c07cdaf7ad5e1a0c35b3f84ce373aa5a2220a6f2b3d44b</t>
+        </is>
+      </c>
+      <c r="D46" s="91" t="n">
+        <v>122984</v>
+      </c>
+    </row>
+    <row r="47" ht="64.5" customHeight="1" s="88">
+      <c r="A47" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE v001</t>
+        </is>
+      </c>
+      <c r="B47" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/runtime/chr_bunny01_expression_love_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C47" s="150" t="inlineStr">
+        <is>
+          <t>55c5ed2427692689d420d661f1f14f9804ac8d16eaa9986fe95f603e03f03646</t>
+        </is>
+      </c>
+      <c r="D47" s="91" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="48" ht="64.5" customHeight="1" s="88">
+      <c r="A48" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION v001</t>
+        </is>
+      </c>
+      <c r="B48" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/components/chr_bunny01_expression_question_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C48" s="150" t="inlineStr">
+        <is>
+          <t>4740fdd4fcc8dcede0e95f27b7df2b695ac0d14e3f7e244e64f233b1e4e30bb1</t>
+        </is>
+      </c>
+      <c r="D48" s="91" t="n">
+        <v>80452</v>
+      </c>
+    </row>
+    <row r="49" ht="64.5" customHeight="1" s="88">
+      <c r="A49" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION v001</t>
+        </is>
+      </c>
+      <c r="B49" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/runtime/chr_bunny01_expression_question_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C49" s="150" t="inlineStr">
+        <is>
+          <t>75e43fbd73f8ca06937b03393cae4ba6e2761b4dc3849941a8caef78627ef6e6</t>
+        </is>
+      </c>
+      <c r="D49" s="91" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="50" ht="64.5" customHeight="1" s="88">
+      <c r="A50" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT v001</t>
+        </is>
+      </c>
+      <c r="B50" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/components/chr_bunny01_expression_alert_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C50" s="150" t="inlineStr">
+        <is>
+          <t>d8fae0b6ae1fbc853f3fa641f69e1cd95dc79167bf28f1cf2d48a1ba183aa65c</t>
+        </is>
+      </c>
+      <c r="D50" s="91" t="n">
+        <v>75932</v>
+      </c>
+    </row>
+    <row r="51" ht="64.5" customHeight="1" s="88">
+      <c r="A51" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT v001</t>
+        </is>
+      </c>
+      <c r="B51" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/runtime/chr_bunny01_expression_alert_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C51" s="150" t="inlineStr">
+        <is>
+          <t>10c462da39e05fc35b7ecc2e78c3d951ac654eaec30ce055a36c60fd08f14b84</t>
+        </is>
+      </c>
+      <c r="D51" s="91" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="52" ht="64.5" customHeight="1" s="88">
+      <c r="A52" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B52" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v004.blend</t>
+        </is>
+      </c>
+      <c r="C52" s="150" t="inlineStr">
+        <is>
+          <t>dc23858aac2735070abb92406aba67e5ae864a62b96a62d57fad428d05ab72fb</t>
+        </is>
+      </c>
+      <c r="D52" s="91" t="n">
+        <v>12045566</v>
+      </c>
+    </row>
+    <row r="53" ht="64.5" customHeight="1" s="88">
+      <c r="A53" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B53" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v004.blend</t>
+        </is>
+      </c>
+      <c r="C53" s="150" t="inlineStr">
+        <is>
+          <t>b97f0cd58582e2caea43aed770567f44479b266248f09a9bfece7dca724c3fb5</t>
+        </is>
+      </c>
+      <c r="D53" s="91" t="n">
+        <v>12086847</v>
+      </c>
+    </row>
+    <row r="54" ht="64.5" customHeight="1" s="88">
+      <c r="A54" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B54" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_visual.glb</t>
+        </is>
+      </c>
+      <c r="C54" s="150" t="inlineStr">
+        <is>
+          <t>61ec14bbf394070bc84ee949e928b512ff71ac706b16071fee2a75ec176fb29e</t>
+        </is>
+      </c>
+      <c r="D54" s="91" t="n">
+        <v>424156</v>
+      </c>
+    </row>
+    <row r="55" ht="64.5" customHeight="1" s="88">
+      <c r="A55" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B55" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_animations.tres</t>
+        </is>
+      </c>
+      <c r="C55" s="150" t="inlineStr">
+        <is>
+          <t>1661fd60ac07f06dc0b84ff8a3344fe310e1ecaeacb1b63891f3f3e96212f6ee</t>
+        </is>
+      </c>
+      <c r="D55" s="91" t="n">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="56" ht="64.5" customHeight="1" s="88">
+      <c r="A56" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B56" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_expression_curves.json</t>
+        </is>
+      </c>
+      <c r="C56" s="150" t="inlineStr">
+        <is>
+          <t>1445c148bf6b0f6fd8eb0f736cf55b5cc6016fa5109579d854172000933a97d0</t>
+        </is>
+      </c>
+      <c r="D56" s="91" t="n">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="57" ht="64.5" customHeight="1" s="88">
+      <c r="A57" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B57" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_expression_catalog.json</t>
+        </is>
+      </c>
+      <c r="C57" s="150" t="inlineStr">
+        <is>
+          <t>04734b7cf54634a6c87985b9b922467d38a67faf5154c14a5b49879b072ff458</t>
+        </is>
+      </c>
+      <c r="D57" s="91" t="n">
+        <v>4092</v>
+      </c>
+    </row>
+    <row r="58" ht="64.5" customHeight="1" s="88">
+      <c r="A58" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B58" s="150" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionCatalog.gd</t>
+        </is>
+      </c>
+      <c r="C58" s="150" t="inlineStr">
+        <is>
+          <t>317238d4097979b0b400cb108c8123be52dc4f6a80148c215f729bc7282c3532</t>
+        </is>
+      </c>
+      <c r="D58" s="91" t="n">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="59" ht="64.5" customHeight="1" s="88">
+      <c r="A59" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B59" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_root.tscn</t>
+        </is>
+      </c>
+      <c r="C59" s="150" t="inlineStr">
+        <is>
+          <t>b183779cd666cbb42cf60b0a61ca8b70b9ef9597000fa240dc5754ec27f9a64b</t>
+        </is>
+      </c>
+      <c r="D59" s="91" t="n">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="60" ht="64.5" customHeight="1" s="88">
+      <c r="A60" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B60" s="150" t="inlineStr">
+        <is>
+          <t>src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="C60" s="150" t="inlineStr">
+        <is>
+          <t>28d3719c2a94638456ad5bd55ab8f0aecfe5d4537316b77d890e8e839cb69928</t>
+        </is>
+      </c>
+      <c r="D60" s="91" t="n">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="61" ht="64.5" customHeight="1" s="88">
+      <c r="A61" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B61" s="150" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="C61" s="150" t="inlineStr">
+        <is>
+          <t>2dc13da3dc63ee19001aa864f1a39ab1b742a2b3bebe782b74884edf0ec656b9</t>
+        </is>
+      </c>
+      <c r="D61" s="91" t="n">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="62" ht="64.5" customHeight="1" s="88">
+      <c r="A62" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v004</t>
+        </is>
+      </c>
+      <c r="B62" s="150" t="inlineStr">
+        <is>
+          <t>src/player3d/PlayerExpressionStateAdapter.gd</t>
+        </is>
+      </c>
+      <c r="C62" s="150" t="inlineStr">
+        <is>
+          <t>5ff3c07ac210eb22e99e7dc3ac22672ac24767ddd8aff1b8450ebfadd15d067a</t>
+        </is>
+      </c>
+      <c r="D62" s="91" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="63" ht="64.5" customHeight="1" s="88">
+      <c r="A63" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL v002</t>
+        </is>
+      </c>
+      <c r="B63" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/components/chr_bunny01_expression_neutral_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C63" s="150" t="inlineStr">
+        <is>
+          <t>9d600684c9245a8d252f336cd1ea2da5f99ab0d39035e5acc99d8382da2940bb</t>
+        </is>
+      </c>
+      <c r="D63" s="91" t="n">
+        <v>271272</v>
+      </c>
+    </row>
+    <row r="64" ht="64.5" customHeight="1" s="88">
+      <c r="A64" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL v002</t>
+        </is>
+      </c>
+      <c r="B64" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/runtime/chr_bunny01_expression_neutral_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C64" s="150" t="inlineStr">
+        <is>
+          <t>9b60ab404d7d11beeda731ed9341f96c7d5490166c42c89f2ad9369952d97f12</t>
+        </is>
+      </c>
+      <c r="D64" s="91" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="65" ht="64.5" customHeight="1" s="88">
+      <c r="A65" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY v002</t>
+        </is>
+      </c>
+      <c r="B65" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/components/chr_bunny01_expression_happy_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C65" s="150" t="inlineStr">
+        <is>
+          <t>0c72911712b2f631a4770d4f6605f53d38e29dcbd9112825360818edf5edfb7f</t>
+        </is>
+      </c>
+      <c r="D65" s="91" t="n">
+        <v>180636</v>
+      </c>
+    </row>
+    <row r="66" ht="64.5" customHeight="1" s="88">
+      <c r="A66" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY v002</t>
+        </is>
+      </c>
+      <c r="B66" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/runtime/chr_bunny01_expression_happy_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C66" s="150" t="inlineStr">
+        <is>
+          <t>eee2a1f0ffd5e535edf6475862cd05a25e3424f55c64b9e81d74058d42c6dddb</t>
+        </is>
+      </c>
+      <c r="D66" s="91" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="67" ht="64.5" customHeight="1" s="88">
+      <c r="A67" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD v002</t>
+        </is>
+      </c>
+      <c r="B67" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/components/chr_bunny01_expression_sad_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C67" s="150" t="inlineStr">
+        <is>
+          <t>07a781454ed45b972b4b6167b40ae212e09a9224687d7ae3e33032e3e2686653</t>
+        </is>
+      </c>
+      <c r="D67" s="91" t="n">
+        <v>160804</v>
+      </c>
+    </row>
+    <row r="68" ht="64.5" customHeight="1" s="88">
+      <c r="A68" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD v002</t>
+        </is>
+      </c>
+      <c r="B68" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/runtime/chr_bunny01_expression_sad_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C68" s="150" t="inlineStr">
+        <is>
+          <t>7fac906a032fbaa5dba2fefc76abc8f5bff3e7d5f6c0b7d69675029e3f9ef6c5</t>
+        </is>
+      </c>
+      <c r="D68" s="91" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="69" ht="64.5" customHeight="1" s="88">
+      <c r="A69" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY v002</t>
+        </is>
+      </c>
+      <c r="B69" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/components/chr_bunny01_expression_angry_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C69" s="150" t="inlineStr">
+        <is>
+          <t>ea64a70cff0a47cebebda6e3eb848c6ac61d0703d2fd49a2cb88e748fc93e103</t>
+        </is>
+      </c>
+      <c r="D69" s="91" t="n">
+        <v>174972</v>
+      </c>
+    </row>
+    <row r="70" ht="64.5" customHeight="1" s="88">
+      <c r="A70" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY v002</t>
+        </is>
+      </c>
+      <c r="B70" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/runtime/chr_bunny01_expression_angry_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C70" s="150" t="inlineStr">
+        <is>
+          <t>b54be2e086421b2fba7300e5c8401d1bb24976a977d76f33311bafbcb31dfe57</t>
+        </is>
+      </c>
+      <c r="D70" s="91" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="71" ht="64.5" customHeight="1" s="88">
+      <c r="A71" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED v002</t>
+        </is>
+      </c>
+      <c r="B71" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/components/chr_bunny01_expression_surprised_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C71" s="150" t="inlineStr">
+        <is>
+          <t>ca6c85c194155c799363a39c3a1330a8318ad69b850db9f3758f3a81f65fdc8b</t>
+        </is>
+      </c>
+      <c r="D71" s="91" t="n">
+        <v>220292</v>
+      </c>
+    </row>
+    <row r="72" ht="64.5" customHeight="1" s="88">
+      <c r="A72" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED v002</t>
+        </is>
+      </c>
+      <c r="B72" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/runtime/chr_bunny01_expression_surprised_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C72" s="150" t="inlineStr">
+        <is>
+          <t>afbfa5f12e7390d561d8f99b7094c849d45e605b29dbbaddbf1cbc44988694d0</t>
+        </is>
+      </c>
+      <c r="D72" s="91" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="73" ht="64.5" customHeight="1" s="88">
+      <c r="A73" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE v002</t>
+        </is>
+      </c>
+      <c r="B73" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/components/chr_bunny01_expression_love_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C73" s="150" t="inlineStr">
+        <is>
+          <t>eb053ee8cc8dc110705e187d4e433885214aeed835b156b4a208b80e82da8d53</t>
+        </is>
+      </c>
+      <c r="D73" s="91" t="n">
+        <v>225944</v>
+      </c>
+    </row>
+    <row r="74" ht="64.5" customHeight="1" s="88">
+      <c r="A74" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE v002</t>
+        </is>
+      </c>
+      <c r="B74" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/runtime/chr_bunny01_expression_love_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C74" s="150" t="inlineStr">
+        <is>
+          <t>775c85672c9b18316ab5d1439a9b1661b21cd68ec97239d45d0878b4d9831c2e</t>
+        </is>
+      </c>
+      <c r="D74" s="91" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="75" ht="64.5" customHeight="1" s="88">
+      <c r="A75" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION v002</t>
+        </is>
+      </c>
+      <c r="B75" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/components/chr_bunny01_expression_question_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C75" s="150" t="inlineStr">
+        <is>
+          <t>05d0c354aeba2eaabdbf20ed4c71adedcbfbaf8e6d6441962cad2d91f1472875</t>
+        </is>
+      </c>
+      <c r="D75" s="91" t="n">
+        <v>142728</v>
+      </c>
+    </row>
+    <row r="76" ht="64.5" customHeight="1" s="88">
+      <c r="A76" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION v002</t>
+        </is>
+      </c>
+      <c r="B76" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/runtime/chr_bunny01_expression_question_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C76" s="150" t="inlineStr">
+        <is>
+          <t>dbc11dca53dd480f46228b9b14fb9824348fb17c20285664cd4abc09a7650ef2</t>
+        </is>
+      </c>
+      <c r="D76" s="91" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="77" ht="64.5" customHeight="1" s="88">
+      <c r="A77" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT v002</t>
+        </is>
+      </c>
+      <c r="B77" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/components/chr_bunny01_expression_alert_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C77" s="150" t="inlineStr">
+        <is>
+          <t>9a1b7056f7264c0866d322a7e746be6e42cc2cfb8a500acb587a67226d6da233</t>
+        </is>
+      </c>
+      <c r="D77" s="91" t="n">
+        <v>124668</v>
+      </c>
+    </row>
+    <row r="78" ht="64.5" customHeight="1" s="88">
+      <c r="A78" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT v002</t>
+        </is>
+      </c>
+      <c r="B78" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/runtime/chr_bunny01_expression_alert_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C78" s="150" t="inlineStr">
+        <is>
+          <t>d705c3e454f6c53a680db5da41e5829eced0b3c8a106a5d68ee0e2e912282afd</t>
+        </is>
+      </c>
+      <c r="D78" s="91" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="79" ht="64.5" customHeight="1" s="88">
+      <c r="A79" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B79" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="C79" s="150" t="inlineStr">
+        <is>
+          <t>4d70a9e65658a8e8617ad042b42a475b28dc12ec196d4b5fdb8443b93e98a288</t>
+        </is>
+      </c>
+      <c r="D79" s="91" t="n">
+        <v>12045588</v>
+      </c>
+    </row>
+    <row r="80" ht="64.5" customHeight="1" s="88">
+      <c r="A80" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B80" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v005.blend</t>
+        </is>
+      </c>
+      <c r="C80" s="150" t="inlineStr">
+        <is>
+          <t>3862ecf93b49e6722b70f55446c5737b5fd9492c9f652945438884a5c022b8ca</t>
+        </is>
+      </c>
+      <c r="D80" s="91" t="n">
+        <v>12086869</v>
+      </c>
+    </row>
+    <row r="81" ht="64.5" customHeight="1" s="88">
+      <c r="A81" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B81" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_visual.glb</t>
+        </is>
+      </c>
+      <c r="C81" s="150" t="inlineStr">
+        <is>
+          <t>2d9120571cb55e2ceed0d2748cec9c99bee6e4cb44fa6c8a20ff2ea8860c8625</t>
+        </is>
+      </c>
+      <c r="D81" s="91" t="n">
+        <v>424180</v>
+      </c>
+    </row>
+    <row r="82" ht="64.5" customHeight="1" s="88">
+      <c r="A82" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B82" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_animations.tres</t>
+        </is>
+      </c>
+      <c r="C82" s="150" t="inlineStr">
+        <is>
+          <t>1661fd60ac07f06dc0b84ff8a3344fe310e1ecaeacb1b63891f3f3e96212f6ee</t>
+        </is>
+      </c>
+      <c r="D82" s="91" t="n">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="83" ht="64.5" customHeight="1" s="88">
+      <c r="A83" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B83" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_expression_curves.json</t>
+        </is>
+      </c>
+      <c r="C83" s="150" t="inlineStr">
+        <is>
+          <t>591af5d8ad9cca3eda51051edc25d7d201d7a6a9f3bfe7151c873b171f188648</t>
+        </is>
+      </c>
+      <c r="D83" s="91" t="n">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="84" ht="64.5" customHeight="1" s="88">
+      <c r="A84" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B84" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_expression_catalog.json</t>
+        </is>
+      </c>
+      <c r="C84" s="150" t="inlineStr">
+        <is>
+          <t>66d06bce1b97501bfe670882e5080d2fa40519b3a58df5377b4c5cf0547ef0bd</t>
+        </is>
+      </c>
+      <c r="D84" s="91" t="n">
+        <v>4092</v>
+      </c>
+    </row>
+    <row r="85" ht="64.5" customHeight="1" s="88">
+      <c r="A85" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B85" s="150" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionCatalog.gd</t>
+        </is>
+      </c>
+      <c r="C85" s="150" t="inlineStr">
+        <is>
+          <t>317238d4097979b0b400cb108c8123be52dc4f6a80148c215f729bc7282c3532</t>
+        </is>
+      </c>
+      <c r="D85" s="91" t="n">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="86" ht="64.5" customHeight="1" s="88">
+      <c r="A86" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B86" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_root.tscn</t>
+        </is>
+      </c>
+      <c r="C86" s="150" t="inlineStr">
+        <is>
+          <t>3775f317b0abc0ea1bff93150221ba3d0a26bd851520c230c0773ced52155628</t>
+        </is>
+      </c>
+      <c r="D86" s="91" t="n">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="87" ht="64.5" customHeight="1" s="88">
+      <c r="A87" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B87" s="150" t="inlineStr">
+        <is>
+          <t>src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="C87" s="150" t="inlineStr">
+        <is>
+          <t>28d3719c2a94638456ad5bd55ab8f0aecfe5d4537316b77d890e8e839cb69928</t>
+        </is>
+      </c>
+      <c r="D87" s="91" t="n">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="88" ht="64.5" customHeight="1" s="88">
+      <c r="A88" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B88" s="150" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd</t>
+        </is>
+      </c>
+      <c r="C88" s="150" t="inlineStr">
+        <is>
+          <t>2dc13da3dc63ee19001aa864f1a39ab1b742a2b3bebe782b74884edf0ec656b9</t>
+        </is>
+      </c>
+      <c r="D88" s="91" t="n">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="89" ht="64.5" customHeight="1" s="88">
+      <c r="A89" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005</t>
+        </is>
+      </c>
+      <c r="B89" s="150" t="inlineStr">
+        <is>
+          <t>src/player3d/PlayerExpressionStateAdapter.gd</t>
+        </is>
+      </c>
+      <c r="C89" s="150" t="inlineStr">
+        <is>
+          <t>5ff3c07ac210eb22e99e7dc3ac22672ac24767ddd8aff1b8450ebfadd15d067a</t>
+        </is>
+      </c>
+      <c r="D89" s="91" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="90" ht="64.5" customHeight="1" s="88">
+      <c r="A90" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL v003</t>
+        </is>
+      </c>
+      <c r="B90" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/components/chr_bunny01_expression_neutral_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C90" s="150" t="inlineStr">
+        <is>
+          <t>7fb6b4130317bf52d09c1e6f6b2d64b4004cf1dd431141ef1f0d9dec55fdce69</t>
+        </is>
+      </c>
+      <c r="D90" s="91" t="n">
+        <v>271296</v>
+      </c>
+    </row>
+    <row r="91" ht="64.5" customHeight="1" s="88">
+      <c r="A91" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL v003</t>
+        </is>
+      </c>
+      <c r="B91" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/runtime/chr_bunny01_expression_neutral_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C91" s="150" t="inlineStr">
+        <is>
+          <t>91bf8992535d92214043b1f732fb9ef10f263f1507428fda2cd55282429b9fa2</t>
+        </is>
+      </c>
+      <c r="D91" s="91" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="92" ht="64.5" customHeight="1" s="88">
+      <c r="A92" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY v003</t>
+        </is>
+      </c>
+      <c r="B92" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/components/chr_bunny01_expression_happy_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C92" s="150" t="inlineStr">
+        <is>
+          <t>e784ed42bbb919c6863b58f9d4ba863358f301a74d408c97bcfa417dc49beb76</t>
+        </is>
+      </c>
+      <c r="D92" s="91" t="n">
+        <v>180664</v>
+      </c>
+    </row>
+    <row r="93" ht="64.5" customHeight="1" s="88">
+      <c r="A93" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY v003</t>
+        </is>
+      </c>
+      <c r="B93" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/runtime/chr_bunny01_expression_happy_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C93" s="150" t="inlineStr">
+        <is>
+          <t>6096540f49967a91f361561915c16f586ce6f32bf66548b4178ccf4b16e9cd4f</t>
+        </is>
+      </c>
+      <c r="D93" s="91" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="94" ht="64.5" customHeight="1" s="88">
+      <c r="A94" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD v003</t>
+        </is>
+      </c>
+      <c r="B94" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/components/chr_bunny01_expression_sad_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C94" s="150" t="inlineStr">
+        <is>
+          <t>3c4335d9b23a16fc774cbed2343e4b5909d7310d36d9e58edbccc1bf6a17361c</t>
+        </is>
+      </c>
+      <c r="D94" s="91" t="n">
+        <v>160828</v>
+      </c>
+    </row>
+    <row r="95" ht="64.5" customHeight="1" s="88">
+      <c r="A95" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD v003</t>
+        </is>
+      </c>
+      <c r="B95" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/runtime/chr_bunny01_expression_sad_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C95" s="150" t="inlineStr">
+        <is>
+          <t>64b0b018248b0f2901755b51caf6af2246372424e246e0e2d2e52daa6c0db05e</t>
+        </is>
+      </c>
+      <c r="D95" s="91" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="96" ht="64.5" customHeight="1" s="88">
+      <c r="A96" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY v003</t>
+        </is>
+      </c>
+      <c r="B96" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/components/chr_bunny01_expression_angry_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C96" s="150" t="inlineStr">
+        <is>
+          <t>6e7ed4ae31b74a3cf8e4640532691862865b9ab5217c47bc597534506f37b384</t>
+        </is>
+      </c>
+      <c r="D96" s="91" t="n">
+        <v>174996</v>
+      </c>
+    </row>
+    <row r="97" ht="64.5" customHeight="1" s="88">
+      <c r="A97" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY v003</t>
+        </is>
+      </c>
+      <c r="B97" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/runtime/chr_bunny01_expression_angry_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C97" s="150" t="inlineStr">
+        <is>
+          <t>a7a713e8dfa53e0690b7dfa5957573d0cfd4551a85146b46de67eea1ee837eaa</t>
+        </is>
+      </c>
+      <c r="D97" s="91" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="98" ht="64.5" customHeight="1" s="88">
+      <c r="A98" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED v003</t>
+        </is>
+      </c>
+      <c r="B98" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/components/chr_bunny01_expression_surprised_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C98" s="150" t="inlineStr">
+        <is>
+          <t>adba7fc4b390c4da1594ecad346accf99facd1683a00f4ce718d3f145c5eeb2c</t>
+        </is>
+      </c>
+      <c r="D98" s="91" t="n">
+        <v>220316</v>
+      </c>
+    </row>
+    <row r="99" ht="64.5" customHeight="1" s="88">
+      <c r="A99" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED v003</t>
+        </is>
+      </c>
+      <c r="B99" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/runtime/chr_bunny01_expression_surprised_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C99" s="150" t="inlineStr">
+        <is>
+          <t>fcf462e945994543ded0497e84dbfe44f33ff4d89d5422641fd93794a9747712</t>
+        </is>
+      </c>
+      <c r="D99" s="91" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="100" ht="64.5" customHeight="1" s="88">
+      <c r="A100" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE v003</t>
+        </is>
+      </c>
+      <c r="B100" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/components/chr_bunny01_expression_love_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C100" s="150" t="inlineStr">
+        <is>
+          <t>5abaf55dd6797527ce7546ca97c93d7eb906ae8119a9cf66a9374124e1410186</t>
+        </is>
+      </c>
+      <c r="D100" s="91" t="n">
+        <v>225968</v>
+      </c>
+    </row>
+    <row r="101" ht="64.5" customHeight="1" s="88">
+      <c r="A101" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE v003</t>
+        </is>
+      </c>
+      <c r="B101" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/runtime/chr_bunny01_expression_love_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C101" s="150" t="inlineStr">
+        <is>
+          <t>0c7c63c8bf72ba2dc21be59232dbfdebc982347d05eb13e1384646604229011d</t>
+        </is>
+      </c>
+      <c r="D101" s="91" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="102" ht="64.5" customHeight="1" s="88">
+      <c r="A102" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION v003</t>
+        </is>
+      </c>
+      <c r="B102" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/components/chr_bunny01_expression_question_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C102" s="150" t="inlineStr">
+        <is>
+          <t>366ad4fa73cbfacedeaeb982bceb292ec67818e2eccd354b3be920c8b46a666d</t>
+        </is>
+      </c>
+      <c r="D102" s="91" t="n">
+        <v>142752</v>
+      </c>
+    </row>
+    <row r="103" ht="64.5" customHeight="1" s="88">
+      <c r="A103" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION v003</t>
+        </is>
+      </c>
+      <c r="B103" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/runtime/chr_bunny01_expression_question_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C103" s="150" t="inlineStr">
+        <is>
+          <t>9a682f546faf4a778a1db97d6c58e010b9db54814cf40cc91c3d4705603bd3c1</t>
+        </is>
+      </c>
+      <c r="D103" s="91" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="104" ht="64.5" customHeight="1" s="88">
+      <c r="A104" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT v003</t>
+        </is>
+      </c>
+      <c r="B104" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/components/chr_bunny01_expression_alert_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="C104" s="150" t="inlineStr">
+        <is>
+          <t>7865e933c5fbae490e8e3af98a1e75a918c3b24621caf6003430f0da4029d34f</t>
+        </is>
+      </c>
+      <c r="D104" s="91" t="n">
+        <v>124696</v>
+      </c>
+    </row>
+    <row r="105" ht="64.5" customHeight="1" s="88">
+      <c r="A105" s="91" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT v003</t>
+        </is>
+      </c>
+      <c r="B105" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/runtime/chr_bunny01_expression_alert_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="C105" s="150" t="inlineStr">
+        <is>
+          <t>5c6f8b8035594d8c68e0159eda199b050f1261d22e648ae30738863ba5bcd3b3</t>
+        </is>
+      </c>
+      <c r="D105" s="91" t="n">
+        <v>566</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10834,7 +14869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="35.81" customWidth="1" style="87" min="1" max="1"/>
@@ -10864,10 +14899,11 @@
     <row r="2" ht="33.75" customHeight="1" s="88">
       <c r="A2" s="152" t="inlineStr">
         <is>
-          <t>玩家、NPC与角色表现/玩法根及制作母版；当前 4 个登记项。</t>
-        </is>
-      </c>
-    </row>
+          <t>玩家、NPC、角色表现/玩法根、制作母版与独立表情组件；表情逐项登记。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="88">
       <c r="A4" s="153" t="inlineStr">
         <is>
@@ -11251,6 +15287,744 @@
       <c r="P8" s="120" t="inlineStr">
         <is>
           <t>7槽位/9挂点；角色玩法碰撞仍由scenes/Player3D.tscn拥有</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1" s="88">
+      <c r="A9" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK</t>
+        </is>
+      </c>
+      <c r="B9" s="158" t="inlineStr">
+        <is>
+          <t>兔子主角黑色蓝光电子面具</t>
+        </is>
+      </c>
+      <c r="C9" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/runtime/chr_bunny01_electronic_mask_root.tscn</t>
+        </is>
+      </c>
+      <c r="D9" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/components/chr_bunny01_electronic_mask_visual.glb</t>
+        </is>
+      </c>
+      <c r="E9" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F9" s="158" t="inlineStr">
+        <is>
+          <t>可替换电子面饰组件；新角色默认款；实际换装/读档沿用glasses槽</t>
+        </is>
+      </c>
+      <c r="G9" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/PlayerExpressionStateAdapter.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H9" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I9" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J9" s="158" t="inlineStr">
+        <is>
+          <t>纯视觉配件不定义碰撞</t>
+        </is>
+      </c>
+      <c r="K9" s="159" t="inlineStr">
+        <is>
+          <t>源0.630×0.479×0.257m；独立根缩放1</t>
+        </is>
+      </c>
+      <c r="L9" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部原点；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M9" s="159" t="inlineStr">
+        <is>
+          <t>正式Bunny01玩家、衣柜面饰与3D预览</t>
+        </is>
+      </c>
+      <c r="N9" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O9" s="159" t="inlineStr">
+        <is>
+          <t>v005</t>
+        </is>
+      </c>
+      <c r="P9" s="160" t="inlineStr">
+        <is>
+          <t>原头部/骨架/动作不变；8独立表达子Prefab/GLB，选择/随机/保持由独立系统拥有，真实状态事件只发命令；显示共用Blink/亮度剪辑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1" s="88">
+      <c r="A10" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-NEUTRAL</t>
+        </is>
+      </c>
+      <c r="B10" s="158" t="inlineStr">
+        <is>
+          <t>电子面具表情：平静</t>
+        </is>
+      </c>
+      <c r="C10" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/runtime/chr_bunny01_expression_neutral_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D10" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_neutral/components/chr_bunny01_expression_neutral_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E10" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F10" s="158" t="inlineStr">
+        <is>
+          <t>独立无嘴部方块网格表达组件</t>
+        </is>
+      </c>
+      <c r="G10" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H10" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I10" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J10" s="158" t="inlineStr">
+        <is>
+          <t>不增加任何玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K10" s="159" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；根缩放1</t>
+        </is>
+      </c>
+      <c r="L10" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M10" s="159" t="inlineStr">
+        <is>
+          <t>独立角色表情系统；可移植到其他显示端</t>
+        </is>
+      </c>
+      <c r="N10" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O10" s="159" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P10" s="160" t="inlineStr">
+        <is>
+          <t>父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；emotion；#21bfff；180颗；发光1.25；8种随机可达与Forward+独立渲染通过；依赖父v005双母版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1" s="88">
+      <c r="A11" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-HAPPY</t>
+        </is>
+      </c>
+      <c r="B11" s="158" t="inlineStr">
+        <is>
+          <t>电子面具表情：开心</t>
+        </is>
+      </c>
+      <c r="C11" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/runtime/chr_bunny01_expression_happy_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D11" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_happy/components/chr_bunny01_expression_happy_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E11" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F11" s="158" t="inlineStr">
+        <is>
+          <t>独立无嘴部方块网格表达组件</t>
+        </is>
+      </c>
+      <c r="G11" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H11" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I11" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J11" s="158" t="inlineStr">
+        <is>
+          <t>不增加任何玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K11" s="159" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；根缩放1</t>
+        </is>
+      </c>
+      <c r="L11" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M11" s="159" t="inlineStr">
+        <is>
+          <t>独立角色表情系统；可移植到其他显示端</t>
+        </is>
+      </c>
+      <c r="N11" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O11" s="159" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P11" s="160" t="inlineStr">
+        <is>
+          <t>父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；emotion；#29e9ff；116颗；发光1.25；8种随机可达与Forward+独立渲染通过；依赖父v005双母版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1" s="88">
+      <c r="A12" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SAD</t>
+        </is>
+      </c>
+      <c r="B12" s="158" t="inlineStr">
+        <is>
+          <t>电子面具表情：难过</t>
+        </is>
+      </c>
+      <c r="C12" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/runtime/chr_bunny01_expression_sad_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D12" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_sad/components/chr_bunny01_expression_sad_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E12" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F12" s="158" t="inlineStr">
+        <is>
+          <t>独立无嘴部方块网格表达组件</t>
+        </is>
+      </c>
+      <c r="G12" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H12" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I12" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J12" s="158" t="inlineStr">
+        <is>
+          <t>不增加任何玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K12" s="159" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；根缩放1</t>
+        </is>
+      </c>
+      <c r="L12" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M12" s="159" t="inlineStr">
+        <is>
+          <t>独立角色表情系统；可移植到其他显示端</t>
+        </is>
+      </c>
+      <c r="N12" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O12" s="159" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P12" s="160" t="inlineStr">
+        <is>
+          <t>父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；emotion；#777bff；102颗；发光1.25；8种随机可达与Forward+独立渲染通过；依赖父v005双母版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1" s="88">
+      <c r="A13" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ANGRY</t>
+        </is>
+      </c>
+      <c r="B13" s="158" t="inlineStr">
+        <is>
+          <t>电子面具表情：生气</t>
+        </is>
+      </c>
+      <c r="C13" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/runtime/chr_bunny01_expression_angry_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D13" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_angry/components/chr_bunny01_expression_angry_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E13" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F13" s="158" t="inlineStr">
+        <is>
+          <t>独立无嘴部方块网格表达组件</t>
+        </is>
+      </c>
+      <c r="G13" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H13" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I13" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J13" s="158" t="inlineStr">
+        <is>
+          <t>不增加任何玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K13" s="159" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；根缩放1</t>
+        </is>
+      </c>
+      <c r="L13" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M13" s="159" t="inlineStr">
+        <is>
+          <t>独立角色表情系统；可移植到其他显示端</t>
+        </is>
+      </c>
+      <c r="N13" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O13" s="159" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P13" s="160" t="inlineStr">
+        <is>
+          <t>父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；emotion；#ff3028；112颗；发光1.25；8种随机可达与Forward+独立渲染通过；依赖父v005双母版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1" s="88">
+      <c r="A14" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-SURPRISED</t>
+        </is>
+      </c>
+      <c r="B14" s="158" t="inlineStr">
+        <is>
+          <t>电子面具表情：惊讶</t>
+        </is>
+      </c>
+      <c r="C14" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/runtime/chr_bunny01_expression_surprised_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D14" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_surprised/components/chr_bunny01_expression_surprised_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E14" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F14" s="158" t="inlineStr">
+        <is>
+          <t>独立无嘴部方块网格表达组件</t>
+        </is>
+      </c>
+      <c r="G14" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H14" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I14" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J14" s="158" t="inlineStr">
+        <is>
+          <t>不增加任何玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K14" s="159" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；根缩放1</t>
+        </is>
+      </c>
+      <c r="L14" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M14" s="159" t="inlineStr">
+        <is>
+          <t>独立角色表情系统；可移植到其他显示端</t>
+        </is>
+      </c>
+      <c r="N14" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O14" s="159" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P14" s="160" t="inlineStr">
+        <is>
+          <t>父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；emotion；#ffe45c；144颗；发光1.25；8种随机可达与Forward+独立渲染通过；依赖父v005双母版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1" s="88">
+      <c r="A15" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-LOVE</t>
+        </is>
+      </c>
+      <c r="B15" s="158" t="inlineStr">
+        <is>
+          <t>电子面具表情：爱心</t>
+        </is>
+      </c>
+      <c r="C15" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/runtime/chr_bunny01_expression_love_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D15" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_love/components/chr_bunny01_expression_love_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E15" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F15" s="158" t="inlineStr">
+        <is>
+          <t>独立无嘴部方块网格表达组件</t>
+        </is>
+      </c>
+      <c r="G15" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H15" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I15" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J15" s="158" t="inlineStr">
+        <is>
+          <t>不增加任何玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K15" s="159" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；根缩放1</t>
+        </is>
+      </c>
+      <c r="L15" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M15" s="159" t="inlineStr">
+        <is>
+          <t>独立角色表情系统；可移植到其他显示端</t>
+        </is>
+      </c>
+      <c r="N15" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O15" s="159" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P15" s="160" t="inlineStr">
+        <is>
+          <t>父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；emotion；#ff6abb；148颗；发光1.25；8种随机可达与Forward+独立渲染通过；依赖父v005双母版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1" s="88">
+      <c r="A16" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-QUESTION</t>
+        </is>
+      </c>
+      <c r="B16" s="158" t="inlineStr">
+        <is>
+          <t>电子面具表情：疑问</t>
+        </is>
+      </c>
+      <c r="C16" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/runtime/chr_bunny01_expression_question_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D16" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_question/components/chr_bunny01_expression_question_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E16" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F16" s="158" t="inlineStr">
+        <is>
+          <t>独立无嘴部方块网格表达组件</t>
+        </is>
+      </c>
+      <c r="G16" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H16" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I16" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J16" s="158" t="inlineStr">
+        <is>
+          <t>不增加任何玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K16" s="159" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；根缩放1</t>
+        </is>
+      </c>
+      <c r="L16" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M16" s="159" t="inlineStr">
+        <is>
+          <t>独立角色表情系统；可移植到其他显示端</t>
+        </is>
+      </c>
+      <c r="N16" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O16" s="159" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P16" s="160" t="inlineStr">
+        <is>
+          <t>父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；symbol；#ffd24a；112颗；发光1.25；8种随机可达与Forward+独立渲染通过；依赖父v005双母版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1" s="88">
+      <c r="A17" s="157" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-EXPR-ALERT</t>
+        </is>
+      </c>
+      <c r="B17" s="158" t="inlineStr">
+        <is>
+          <t>电子面具表情：警示</t>
+        </is>
+      </c>
+      <c r="C17" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/runtime/chr_bunny01_expression_alert_root_top3d.tscn</t>
+        </is>
+      </c>
+      <c r="D17" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/expressions/chr_bunny01_expression_alert/components/chr_bunny01_expression_alert_visual_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E17" s="159" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+        </is>
+      </c>
+      <c r="F17" s="158" t="inlineStr">
+        <is>
+          <t>独立无嘴部方块网格表达组件</t>
+        </is>
+      </c>
+      <c r="G17" s="159" t="inlineStr">
+        <is>
+          <t>src/presentation/expressions/CharacterExpressionSystem.gd；src/player3d/customization/ElectronicMaskExpression3D.gd</t>
+        </is>
+      </c>
+      <c r="H17" s="158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I17" s="158" t="inlineStr">
+        <is>
+          <t>Player3D玩法根</t>
+        </is>
+      </c>
+      <c r="J17" s="158" t="inlineStr">
+        <is>
+          <t>不增加任何玩法碰撞</t>
+        </is>
+      </c>
+      <c r="K17" s="159" t="inlineStr">
+        <is>
+          <t>14mm网格/11.8mm颗粒；根缩放1</t>
+        </is>
+      </c>
+      <c r="L17" s="158" t="inlineStr">
+        <is>
+          <t>HeadJoint局部；Blender +Y / Godot -Z</t>
+        </is>
+      </c>
+      <c r="M17" s="159" t="inlineStr">
+        <is>
+          <t>独立角色表情系统；可移植到其他显示端</t>
+        </is>
+      </c>
+      <c r="N17" s="158" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O17" s="159" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P17" s="160" t="inlineStr">
+        <is>
+          <t>父CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK v005；symbol；#a1fff2；96颗；发光1.25；8种随机可达与Forward+独立渲染通过；依赖父v005双母版。</t>
         </is>
       </c>
     </row>
@@ -11285,7 +16059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="87" min="1" max="1"/>
@@ -11312,6 +16086,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -11497,7 +16272,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" s="88">
       <c r="A10" s="105" t="inlineStr">
         <is>
           <t>v0.1.4</t>
@@ -11529,6 +16304,191 @@
         </is>
       </c>
       <c r="G10" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" s="88">
+      <c r="A11" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.5</t>
+        </is>
+      </c>
+      <c r="B11" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C11" s="98" t="inlineStr">
+        <is>
+          <t>新增默认电子面具</t>
+        </is>
+      </c>
+      <c r="D11" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01 / glasses</t>
+        </is>
+      </c>
+      <c r="E11" s="98" t="inlineStr">
+        <is>
+          <t>新增CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK；独立面饰默认佩戴、可换装和保存；原角色模型保留。</t>
+        </is>
+      </c>
+      <c r="F11" s="98" t="inlineStr">
+        <is>
+          <t>只新增一条资产，历史内容与其他资产指纹保持；查重与统计公式扩至新行。</t>
+        </is>
+      </c>
+      <c r="G11" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" s="88">
+      <c r="A12" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.6</t>
+        </is>
+      </c>
+      <c r="B12" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C12" s="98" t="inlineStr">
+        <is>
+          <t>电子面具眼睛放大与局部动画</t>
+        </is>
+      </c>
+      <c r="D12" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01 / glasses</t>
+        </is>
+      </c>
+      <c r="E12" s="98" t="inlineStr">
+        <is>
+          <t>CHR-PLY-BUNNY01-FACE-ELECTRONIC-MASK升级v002；140颗大方块，眨眼与间歇闪烁；原角色/旧源保留。</t>
+        </is>
+      </c>
+      <c r="F12" s="98" t="inlineStr">
+        <is>
+          <t>同ID同稳定运行路径升级；只修改本资产行与指纹，专表另事务登记。</t>
+        </is>
+      </c>
+      <c r="G12" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="88">
+      <c r="A13" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.7</t>
+        </is>
+      </c>
+      <c r="B13" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C13" s="98" t="inlineStr">
+        <is>
+          <t>8种网格情绪/符号与独立系统</t>
+        </is>
+      </c>
+      <c r="D13" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01 / 面饰</t>
+        </is>
+      </c>
+      <c r="E13" s="98" t="inlineStr">
+        <is>
+          <t>八个子资产逐项登记；父面具升级v003；真实状态事件调用独立随机表情系统。</t>
+        </is>
+      </c>
+      <c r="F13" s="98" t="inlineStr">
+        <is>
+          <t>保留其余资产指纹；父/八子主行与组件/动画/3D/中转专表分事务更新。</t>
+        </is>
+      </c>
+      <c r="G13" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" s="88">
+      <c r="A14" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.8</t>
+        </is>
+      </c>
+      <c r="B14" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C14" s="98" t="inlineStr">
+        <is>
+          <t>去除嘴部并深化8种网格表情</t>
+        </is>
+      </c>
+      <c r="D14" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01 / 面饰</t>
+        </is>
+      </c>
+      <c r="E14" s="98" t="inlineStr">
+        <is>
+          <t>父面具升级v004，八个既有表情子资产升级v002；情绪无嘴部，眼睛/爱心/符号加粗放大，11.8mm颗粒；保留独立系统、随机和状态调用。</t>
+        </is>
+      </c>
+      <c r="F14" s="98" t="inlineStr">
+        <is>
+          <t>保留其余资产指纹；父/八子主行与组件/动画/3D/中转专表分事务更新。</t>
+        </is>
+      </c>
+      <c r="G14" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" s="88">
+      <c r="A15" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="B15" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C15" s="98" t="inlineStr">
+        <is>
+          <t>降低8种表情自发光与光晕</t>
+        </is>
+      </c>
+      <c r="D15" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01 / 面饰</t>
+        </is>
+      </c>
+      <c r="E15" s="98" t="inlineStr">
+        <is>
+          <t>父面具升级v005，八个既有表情子资产升级v003；八种材质自发光5→1.25，降低75%；保持无嘴部、饱满网格、11.8mm颗粒及眨眼/闪烁、独立系统和状态调用。</t>
+        </is>
+      </c>
+      <c r="F15" s="98" t="inlineStr">
+        <is>
+          <t>保留其余资产指纹；父/八子主行与组件/动画/3D/中转专表分事务更新。</t>
+        </is>
+      </c>
+      <c r="G15" s="98" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -2123,7 +2123,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -3533,7 +3532,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3560,7 +3559,7 @@
         </is>
       </c>
       <c r="V13" s="118" t="n">
-        <v>46294</v>
+        <v>46302</v>
       </c>
       <c r="W13" s="119" t="inlineStr">
         <is>
@@ -3586,7 +3585,7 @@
 2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。
 2026-09-29：v021 模型及原12动作保持不变；新增 v022 Blender 坐姿滑行循环 seated，Player3D 九态状态机与 99F 两把可驾驶椅接入；verify_pushable_base_chairs 通过。
 2026-09-29：v023 Blender 坐姿源将双脚向座面前方伸出；角色乘坐时可正常射击，相机补偿座面抬升，离座恢复世界碰撞。
-2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。</t>
+2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6053,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -9204,7 +9202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.94" customWidth="1" style="87" min="1" max="1"/>
@@ -12069,6 +12067,192 @@
       <c r="L60" s="127" t="inlineStr">
         <is>
           <t>CHR-PLY-BUNNY01-EXPR-ALERT；子v003/父v005；96颗11.8mm方块；无嘴部且图案加粗；独立Prefab；随机不重复；保持/拒绝/状态调用/真实渲染通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1" s="88">
+      <c r="A61" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B61" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_idle</t>
+        </is>
+      </c>
+      <c r="C61" s="127" t="inlineStr">
+        <is>
+          <t>短枪站立待机</t>
+        </is>
+      </c>
+      <c r="D61" s="128" t="inlineStr">
+        <is>
+          <t>idle + weapon_family=sidearm</t>
+        </is>
+      </c>
+      <c r="E61" s="128" t="inlineStr">
+        <is>
+          <t>由原状态机决定</t>
+        </is>
+      </c>
+      <c r="F61" s="128" t="inlineStr">
+        <is>
+          <t>3.2秒循环；双脚站稳，根不移，独立呼吸曲线</t>
+        </is>
+      </c>
+      <c r="G61" s="127" t="inlineStr">
+        <is>
+          <t>轻微呼吸跟随及耳部滞后</t>
+        </is>
+      </c>
+      <c r="H61" s="127" t="inlineStr">
+        <is>
+          <t>左手自然放松</t>
+        </is>
+      </c>
+      <c r="I61" s="127" t="inlineStr">
+        <is>
+          <t>右手单手握枪，枪口朝上，位于脸侧外方</t>
+        </is>
+      </c>
+      <c r="J61" s="127" t="inlineStr">
+        <is>
+          <t>保持现有组件契约</t>
+        </is>
+      </c>
+      <c r="K61" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX/UI</t>
+        </is>
+      </c>
+      <c r="L61" s="127" t="inlineStr">
+        <is>
+          <t>v025源已完成/authored；保存重开、四分之一帧骨链/双握点/循环检查通过。未导入Godot；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1" s="88">
+      <c r="A62" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B62" s="128" t="inlineStr">
+        <is>
+          <t>longgun_idle</t>
+        </is>
+      </c>
+      <c r="C62" s="127" t="inlineStr">
+        <is>
+          <t>长枪站立待机</t>
+        </is>
+      </c>
+      <c r="D62" s="128" t="inlineStr">
+        <is>
+          <t>idle + weapon_family=longgun</t>
+        </is>
+      </c>
+      <c r="E62" s="128" t="inlineStr">
+        <is>
+          <t>由原状态机决定</t>
+        </is>
+      </c>
+      <c r="F62" s="128" t="inlineStr">
+        <is>
+          <t>3.6秒循环；双脚站稳，根不移，独立呼吸曲线</t>
+        </is>
+      </c>
+      <c r="G62" s="127" t="inlineStr">
+        <is>
+          <t>轻微呼吸跟随及耳部滞后</t>
+        </is>
+      </c>
+      <c r="H62" s="127" t="inlineStr">
+        <is>
+          <t>左手托SupportHandSocket</t>
+        </is>
+      </c>
+      <c r="I62" s="127" t="inlineStr">
+        <is>
+          <t>右手主握，步枪斜持胸前，枪托不贴腮</t>
+        </is>
+      </c>
+      <c r="J62" s="127" t="inlineStr">
+        <is>
+          <t>保持现有组件契约</t>
+        </is>
+      </c>
+      <c r="K62" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX/UI</t>
+        </is>
+      </c>
+      <c r="L62" s="127" t="inlineStr">
+        <is>
+          <t>v025源已完成/authored；保存重开、四分之一帧骨链/双握点/循环检查通过。未导入Godot；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1" s="88">
+      <c r="A63" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B63" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_idle</t>
+        </is>
+      </c>
+      <c r="C63" s="127" t="inlineStr">
+        <is>
+          <t>机枪站立待机</t>
+        </is>
+      </c>
+      <c r="D63" s="128" t="inlineStr">
+        <is>
+          <t>idle + weapon_family=machinegun</t>
+        </is>
+      </c>
+      <c r="E63" s="128" t="inlineStr">
+        <is>
+          <t>由原状态机决定</t>
+        </is>
+      </c>
+      <c r="F63" s="128" t="inlineStr">
+        <is>
+          <t>4.0秒循环；双脚站稳，根不移，独立呼吸曲线</t>
+        </is>
+      </c>
+      <c r="G63" s="127" t="inlineStr">
+        <is>
+          <t>轻微呼吸跟随及耳部滞后</t>
+        </is>
+      </c>
+      <c r="H63" s="127" t="inlineStr">
+        <is>
+          <t>左手托SupportHandSocket承重</t>
+        </is>
+      </c>
+      <c r="I63" s="127" t="inlineStr">
+        <is>
+          <t>右手主握，双手低位承重，枪口略朝下</t>
+        </is>
+      </c>
+      <c r="J63" s="127" t="inlineStr">
+        <is>
+          <t>保持现有组件契约</t>
+        </is>
+      </c>
+      <c r="K63" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX/UI</t>
+        </is>
+      </c>
+      <c r="L63" s="127" t="inlineStr">
+        <is>
+          <t>v025源已完成/authored；保存重开、四分之一帧骨链/双握点/循环检查通过。未导入Godot；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12309,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -12469,7 +12652,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="31.5" customHeight="1" s="88">
       <c r="A15" s="107" t="inlineStr">
         <is>
@@ -12680,7 +12862,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="88">
       <c r="A21" s="141" t="inlineStr">
         <is>
@@ -12688,7 +12869,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="88">
       <c r="A23" s="142" t="inlineStr">
         <is>
@@ -12717,7 +12897,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="33.75" customHeight="1" s="88">
       <c r="A28" s="145" t="inlineStr">
         <is>
@@ -12757,7 +12936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.1" customWidth="1" style="87" min="1" max="1"/>
@@ -14850,6 +15029,46 @@
       </c>
       <c r="D105" s="91" t="n">
         <v>566</v>
+      </c>
+    </row>
+    <row r="106" ht="64.5" customHeight="1" s="88">
+      <c r="A106" s="91" t="inlineStr">
+        <is>
+          <t>v025动作母版（authored，未接线）</t>
+        </is>
+      </c>
+      <c r="B106" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
+        </is>
+      </c>
+      <c r="C106" s="150" t="inlineStr">
+        <is>
+          <t>53a7951a00c6fed8f22ceef335a5817b4a55580ef38b315b2b56f9464065a8ad</t>
+        </is>
+      </c>
+      <c r="D106" s="91" t="n">
+        <v>58259133</v>
+      </c>
+    </row>
+    <row r="107" ht="64.5" customHeight="1" s="88">
+      <c r="A107" s="91" t="inlineStr">
+        <is>
+          <t>v025源级中转记录（待导出）</t>
+        </is>
+      </c>
+      <c r="B107" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json</t>
+        </is>
+      </c>
+      <c r="C107" s="150" t="inlineStr">
+        <is>
+          <t>2b1fb42e24197664c19a8b59ae53e40feecabaf2e94d5b4f6d54042b0c771c43</t>
+        </is>
+      </c>
+      <c r="D107" s="91" t="n">
+        <v>3586</v>
       </c>
     </row>
   </sheetData>
@@ -14903,7 +15122,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="88">
       <c r="A4" s="153" t="inlineStr">
         <is>
@@ -16059,7 +16277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="87" min="1" max="1"/>
@@ -16086,7 +16304,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -16489,6 +16706,43 @@
         </is>
       </c>
       <c r="G15" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" s="88">
+      <c r="A16" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.10</t>
+        </is>
+      </c>
+      <c r="B16" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C16" s="98" t="inlineStr">
+        <is>
+          <t>三类站立持枪待机源动画</t>
+        </is>
+      </c>
+      <c r="D16" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01 / 动画</t>
+        </is>
+      </c>
+      <c r="E16" s="98" t="inlineStr">
+        <is>
+          <t>短枪单手朝上3.2秒；长枪胸前斜持3.6秒；机枪低位承重4秒。现有AssetID增加v025源，原14动作保留。</t>
+        </is>
+      </c>
+      <c r="F16" s="98" t="inlineStr">
+        <is>
+          <t>仅源级authored，未导出/导入/改接线；活动版本与Prefab不变，主表与动作专表分事务登记。</t>
+        </is>
+      </c>
+      <c r="G16" s="98" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I13" s="116" t="inlineStr">
         <is>
-          <t>default / seated / climbing</t>
+          <t>10 existing states / unarmed swing / stow-draw upper-body overlay</t>
         </is>
       </c>
       <c r="J13" s="116" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K13" s="117" t="inlineStr">
         <is>
-          <t>原型已接入</t>
+          <t>active</t>
         </is>
       </c>
       <c r="L13" s="116" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="M13" s="116" t="inlineStr">
         <is>
-          <t>v021</t>
+          <t>v032</t>
         </is>
       </c>
       <c r="N13" s="117" t="inlineStr">
         <is>
-          <t>创作高1.5m；运行可见高1.05m；碰撞由Player3D拥有，不随美术骨架修改。</t>
+          <t>创作高1.5m；默认运行倍率0.8/静止高1.2m；碰撞仍由Player3D拥有。</t>
         </is>
       </c>
       <c r="O13" s="116" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T13" s="116" t="inlineStr">
         <is>
-          <t>e9cac2738d9fa586eed9f2e97a93ff220cab52b60d89f53f4cd80e38ebc9b6c4</t>
+          <t>ca9d03d23c08dcdb2313171a4ce74e51f47aa8db371103ea8c80e7920d7754ff</t>
         </is>
       </c>
       <c r="U13" s="116" t="inlineStr">
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="V13" s="118" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="W13" s="119" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
 2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。
 2026-09-29：v021 模型及原12动作保持不变；新增 v022 Blender 坐姿滑行循环 seated，Player3D 九态状态机与 99F 两把可驾驶椅接入；verify_pushable_base_chairs 通过。
 2026-09-29：v023 Blender 坐姿源将双脚向座面前方伸出；角色乘坐时可正常射击，相机补偿座面抬升，离座恢复世界碰撞。
-2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。</t>
+2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.94" customWidth="1" style="87" min="1" max="1"/>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="L61" s="127" t="inlineStr">
         <is>
-          <t>v025源已完成/authored；保存重开、四分之一帧骨链/双握点/循环检查通过。未导入Godot；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
+          <t>v032 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="L62" s="127" t="inlineStr">
         <is>
-          <t>v025源已完成/authored；保存重开、四分之一帧骨链/双握点/循环检查通过。未导入Godot；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
+          <t>v032 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,4409 @@
       </c>
       <c r="L63" s="127" t="inlineStr">
         <is>
-          <t>v025源已完成/authored；保存重开、四分之一帧骨链/双握点/循环检查通过。未导入Godot；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
+          <t>v032 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1" s="88">
+      <c r="A64" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B64" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="C64" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="D64" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E64" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F64" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G64" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H64" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I64" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J64" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K64" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L64" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1" s="88">
+      <c r="A65" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B65" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="C65" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="D65" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E65" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F65" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G65" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H65" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I65" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J65" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K65" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L65" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1" s="88">
+      <c r="A66" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B66" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_walking_backward</t>
+        </is>
+      </c>
+      <c r="C66" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_walking_backward</t>
+        </is>
+      </c>
+      <c r="D66" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E66" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F66" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G66" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H66" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I66" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J66" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K66" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L66" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1" s="88">
+      <c r="A67" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B67" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="C67" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="D67" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E67" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F67" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G67" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H67" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I67" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J67" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K67" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L67" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1" s="88">
+      <c r="A68" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B68" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="C68" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="D68" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E68" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F68" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G68" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H68" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I68" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J68" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K68" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L68" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1" s="88">
+      <c r="A69" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B69" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_moving_backward</t>
+        </is>
+      </c>
+      <c r="C69" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_moving_backward</t>
+        </is>
+      </c>
+      <c r="D69" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E69" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F69" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G69" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H69" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I69" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J69" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K69" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L69" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1" s="88">
+      <c r="A70" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B70" s="128" t="inlineStr">
+        <is>
+          <t>longgun_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="C70" s="127" t="inlineStr">
+        <is>
+          <t>longgun_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="D70" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E70" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F70" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G70" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H70" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I70" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J70" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K70" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L70" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1" s="88">
+      <c r="A71" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B71" s="128" t="inlineStr">
+        <is>
+          <t>longgun_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="C71" s="127" t="inlineStr">
+        <is>
+          <t>longgun_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="D71" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E71" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F71" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G71" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H71" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I71" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J71" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K71" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L71" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1" s="88">
+      <c r="A72" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B72" s="128" t="inlineStr">
+        <is>
+          <t>longgun_walking_backward</t>
+        </is>
+      </c>
+      <c r="C72" s="127" t="inlineStr">
+        <is>
+          <t>longgun_walking_backward</t>
+        </is>
+      </c>
+      <c r="D72" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E72" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F72" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G72" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H72" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I72" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J72" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K72" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L72" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1" s="88">
+      <c r="A73" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B73" s="128" t="inlineStr">
+        <is>
+          <t>longgun_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="C73" s="127" t="inlineStr">
+        <is>
+          <t>longgun_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="D73" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E73" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F73" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G73" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H73" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I73" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J73" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K73" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L73" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1" s="88">
+      <c r="A74" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B74" s="128" t="inlineStr">
+        <is>
+          <t>longgun_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="C74" s="127" t="inlineStr">
+        <is>
+          <t>longgun_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="D74" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E74" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F74" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G74" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H74" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I74" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J74" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K74" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L74" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1" s="88">
+      <c r="A75" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B75" s="128" t="inlineStr">
+        <is>
+          <t>longgun_moving_backward</t>
+        </is>
+      </c>
+      <c r="C75" s="127" t="inlineStr">
+        <is>
+          <t>longgun_moving_backward</t>
+        </is>
+      </c>
+      <c r="D75" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E75" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F75" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G75" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H75" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I75" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J75" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K75" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L75" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1" s="88">
+      <c r="A76" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B76" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="C76" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="D76" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E76" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F76" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G76" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H76" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I76" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J76" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K76" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L76" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="60" customHeight="1" s="88">
+      <c r="A77" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B77" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="C77" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="D77" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E77" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F77" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G77" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H77" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I77" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J77" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K77" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L77" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="60" customHeight="1" s="88">
+      <c r="A78" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B78" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_walking_backward</t>
+        </is>
+      </c>
+      <c r="C78" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_walking_backward</t>
+        </is>
+      </c>
+      <c r="D78" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E78" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F78" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G78" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H78" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I78" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J78" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K78" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L78" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1" s="88">
+      <c r="A79" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B79" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="C79" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="D79" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E79" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F79" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G79" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H79" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I79" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J79" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K79" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L79" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1" s="88">
+      <c r="A80" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B80" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="C80" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="D80" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E80" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F80" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G80" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H80" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I80" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J80" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K80" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L80" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1" s="88">
+      <c r="A81" s="127" t="inlineStr">
+        <is>
+          <t>表现移动变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B81" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_moving_backward</t>
+        </is>
+      </c>
+      <c r="C81" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_moving_backward</t>
+        </is>
+      </c>
+      <c r="D81" s="128" t="inlineStr">
+        <is>
+          <t>moving + 类型/速度/局部方向</t>
+        </is>
+      </c>
+      <c r="E81" s="128" t="inlineStr">
+        <is>
+          <t>由玩法状态机决定</t>
+        </is>
+      </c>
+      <c r="F81" s="128" t="inlineStr">
+        <is>
+          <t>重心轻摆，面朝向保持</t>
+        </is>
+      </c>
+      <c r="G81" s="127" t="inlineStr">
+        <is>
+          <t>v028耳朵反移动方向飘动，错相回弹，耳根固定</t>
+        </is>
+      </c>
+      <c r="H81" s="127" t="inlineStr">
+        <is>
+          <t>跟随枪型握持关系</t>
+        </is>
+      </c>
+      <c r="I81" s="127" t="inlineStr">
+        <is>
+          <t>v026主握与枪体朝向保持</t>
+        </is>
+      </c>
+      <c r="J81" s="127" t="inlineStr">
+        <is>
+          <t>不新增</t>
+        </is>
+      </c>
+      <c r="K81" s="128" t="inlineStr">
+        <is>
+          <t>无新增</t>
+        </is>
+      </c>
+      <c r="L81" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="60" customHeight="1" s="88">
+      <c r="A82" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B82" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_walking_forward</t>
+        </is>
+      </c>
+      <c r="C82" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_walking_forward</t>
+        </is>
+      </c>
+      <c r="D82" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E82" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F82" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G82" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H82" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I82" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J82" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K82" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L82" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="60" customHeight="1" s="88">
+      <c r="A83" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B83" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_moving_forward</t>
+        </is>
+      </c>
+      <c r="C83" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_moving_forward</t>
+        </is>
+      </c>
+      <c r="D83" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E83" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F83" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G83" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H83" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I83" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J83" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K83" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L83" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="60" customHeight="1" s="88">
+      <c r="A84" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B84" s="128" t="inlineStr">
+        <is>
+          <t>longgun_walking_forward</t>
+        </is>
+      </c>
+      <c r="C84" s="127" t="inlineStr">
+        <is>
+          <t>longgun_walking_forward</t>
+        </is>
+      </c>
+      <c r="D84" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E84" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F84" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G84" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H84" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I84" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J84" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K84" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L84" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1" s="88">
+      <c r="A85" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B85" s="128" t="inlineStr">
+        <is>
+          <t>longgun_moving_forward</t>
+        </is>
+      </c>
+      <c r="C85" s="127" t="inlineStr">
+        <is>
+          <t>longgun_moving_forward</t>
+        </is>
+      </c>
+      <c r="D85" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E85" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F85" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G85" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H85" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I85" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J85" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K85" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L85" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="60" customHeight="1" s="88">
+      <c r="A86" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B86" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_walking_forward</t>
+        </is>
+      </c>
+      <c r="C86" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_walking_forward</t>
+        </is>
+      </c>
+      <c r="D86" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E86" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F86" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G86" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H86" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I86" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J86" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K86" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L86" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="60" customHeight="1" s="88">
+      <c r="A87" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B87" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_moving_forward</t>
+        </is>
+      </c>
+      <c r="C87" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_moving_forward</t>
+        </is>
+      </c>
+      <c r="D87" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E87" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F87" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G87" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H87" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I87" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J87" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K87" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L87" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1" s="88">
+      <c r="A88" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B88" s="128" t="inlineStr">
+        <is>
+          <t>unarmed_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="C88" s="127" t="inlineStr">
+        <is>
+          <t>unarmed_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="D88" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E88" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F88" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G88" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H88" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I88" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J88" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K88" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L88" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1" s="88">
+      <c r="A89" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B89" s="128" t="inlineStr">
+        <is>
+          <t>unarmed_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="C89" s="127" t="inlineStr">
+        <is>
+          <t>unarmed_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="D89" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E89" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F89" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G89" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H89" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I89" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J89" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K89" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L89" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="60" customHeight="1" s="88">
+      <c r="A90" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B90" s="128" t="inlineStr">
+        <is>
+          <t>unarmed_walking_backward</t>
+        </is>
+      </c>
+      <c r="C90" s="127" t="inlineStr">
+        <is>
+          <t>unarmed_walking_backward</t>
+        </is>
+      </c>
+      <c r="D90" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E90" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F90" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G90" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H90" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I90" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J90" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K90" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L90" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="60" customHeight="1" s="88">
+      <c r="A91" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B91" s="128" t="inlineStr">
+        <is>
+          <t>unarmed_walking_forward</t>
+        </is>
+      </c>
+      <c r="C91" s="127" t="inlineStr">
+        <is>
+          <t>unarmed_walking_forward</t>
+        </is>
+      </c>
+      <c r="D91" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E91" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F91" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G91" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H91" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I91" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J91" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K91" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L91" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1" s="88">
+      <c r="A92" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B92" s="128" t="inlineStr">
+        <is>
+          <t>unarmed_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="C92" s="127" t="inlineStr">
+        <is>
+          <t>unarmed_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="D92" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E92" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F92" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G92" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H92" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I92" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J92" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K92" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L92" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1" s="88">
+      <c r="A93" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B93" s="128" t="inlineStr">
+        <is>
+          <t>unarmed_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="C93" s="127" t="inlineStr">
+        <is>
+          <t>unarmed_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="D93" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E93" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F93" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G93" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H93" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I93" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J93" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K93" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L93" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="60" customHeight="1" s="88">
+      <c r="A94" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B94" s="128" t="inlineStr">
+        <is>
+          <t>unarmed_moving_backward</t>
+        </is>
+      </c>
+      <c r="C94" s="127" t="inlineStr">
+        <is>
+          <t>unarmed_moving_backward</t>
+        </is>
+      </c>
+      <c r="D94" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E94" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F94" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G94" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H94" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I94" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J94" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K94" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L94" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1" s="88">
+      <c r="A95" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B95" s="128" t="inlineStr">
+        <is>
+          <t>unarmed_moving_forward</t>
+        </is>
+      </c>
+      <c r="C95" s="127" t="inlineStr">
+        <is>
+          <t>unarmed_moving_forward</t>
+        </is>
+      </c>
+      <c r="D95" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E95" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F95" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G95" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H95" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I95" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J95" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K95" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L95" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="60" customHeight="1" s="88">
+      <c r="A96" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B96" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_idle</t>
+        </is>
+      </c>
+      <c r="C96" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_idle</t>
+        </is>
+      </c>
+      <c r="D96" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E96" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F96" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G96" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H96" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I96" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J96" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K96" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L96" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="60" customHeight="1" s="88">
+      <c r="A97" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B97" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_idle</t>
+        </is>
+      </c>
+      <c r="C97" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_idle</t>
+        </is>
+      </c>
+      <c r="D97" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E97" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F97" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G97" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H97" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I97" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J97" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K97" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L97" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="60" customHeight="1" s="88">
+      <c r="A98" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B98" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_idle</t>
+        </is>
+      </c>
+      <c r="C98" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_idle</t>
+        </is>
+      </c>
+      <c r="D98" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E98" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F98" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G98" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H98" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I98" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J98" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K98" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L98" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1" s="88">
+      <c r="A99" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B99" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="C99" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="D99" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E99" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F99" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G99" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H99" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I99" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J99" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K99" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L99" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="60" customHeight="1" s="88">
+      <c r="A100" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B100" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="C100" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="D100" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E100" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F100" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G100" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H100" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I100" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J100" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K100" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L100" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="60" customHeight="1" s="88">
+      <c r="A101" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B101" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_walking_backward</t>
+        </is>
+      </c>
+      <c r="C101" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_walking_backward</t>
+        </is>
+      </c>
+      <c r="D101" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E101" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F101" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G101" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H101" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I101" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J101" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K101" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L101" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="60" customHeight="1" s="88">
+      <c r="A102" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B102" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="C102" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="D102" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E102" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F102" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G102" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H102" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I102" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J102" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K102" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L102" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="60" customHeight="1" s="88">
+      <c r="A103" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B103" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="C103" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="D103" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E103" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F103" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G103" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H103" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I103" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J103" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K103" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L103" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="60" customHeight="1" s="88">
+      <c r="A104" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B104" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_moving_backward</t>
+        </is>
+      </c>
+      <c r="C104" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_moving_backward</t>
+        </is>
+      </c>
+      <c r="D104" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E104" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F104" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G104" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H104" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I104" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J104" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K104" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L104" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="60" customHeight="1" s="88">
+      <c r="A105" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B105" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="C105" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="D105" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E105" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F105" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G105" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H105" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I105" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J105" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K105" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L105" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="60" customHeight="1" s="88">
+      <c r="A106" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B106" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="C106" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="D106" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E106" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F106" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G106" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H106" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I106" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J106" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K106" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L106" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="60" customHeight="1" s="88">
+      <c r="A107" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B107" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_walking_backward</t>
+        </is>
+      </c>
+      <c r="C107" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_walking_backward</t>
+        </is>
+      </c>
+      <c r="D107" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E107" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F107" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G107" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H107" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I107" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J107" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K107" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L107" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="60" customHeight="1" s="88">
+      <c r="A108" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B108" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="C108" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="D108" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E108" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F108" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G108" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H108" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I108" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J108" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K108" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L108" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="60" customHeight="1" s="88">
+      <c r="A109" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B109" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="C109" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="D109" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E109" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F109" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G109" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H109" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I109" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J109" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K109" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L109" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="60" customHeight="1" s="88">
+      <c r="A110" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B110" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_moving_backward</t>
+        </is>
+      </c>
+      <c r="C110" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_moving_backward</t>
+        </is>
+      </c>
+      <c r="D110" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E110" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F110" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G110" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H110" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I110" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J110" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K110" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L110" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="60" customHeight="1" s="88">
+      <c r="A111" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B111" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="C111" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_walking_strafe_left</t>
+        </is>
+      </c>
+      <c r="D111" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E111" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F111" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G111" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H111" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I111" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J111" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K111" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L111" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="60" customHeight="1" s="88">
+      <c r="A112" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B112" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="C112" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_walking_strafe_right</t>
+        </is>
+      </c>
+      <c r="D112" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E112" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F112" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G112" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H112" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I112" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J112" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K112" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L112" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="60" customHeight="1" s="88">
+      <c r="A113" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B113" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_walking_backward</t>
+        </is>
+      </c>
+      <c r="C113" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_walking_backward</t>
+        </is>
+      </c>
+      <c r="D113" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E113" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F113" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G113" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H113" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I113" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J113" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K113" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L113" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="60" customHeight="1" s="88">
+      <c r="A114" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B114" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="C114" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_moving_strafe_left</t>
+        </is>
+      </c>
+      <c r="D114" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E114" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F114" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G114" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H114" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I114" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J114" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K114" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L114" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="60" customHeight="1" s="88">
+      <c r="A115" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B115" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="C115" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_moving_strafe_right</t>
+        </is>
+      </c>
+      <c r="D115" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E115" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F115" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G115" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H115" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I115" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J115" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K115" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L115" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="60" customHeight="1" s="88">
+      <c r="A116" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B116" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_moving_backward</t>
+        </is>
+      </c>
+      <c r="C116" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_moving_backward</t>
+        </is>
+      </c>
+      <c r="D116" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E116" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F116" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G116" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H116" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I116" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J116" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K116" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L116" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="60" customHeight="1" s="88">
+      <c r="A117" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B117" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_walking_forward</t>
+        </is>
+      </c>
+      <c r="C117" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_walking_forward</t>
+        </is>
+      </c>
+      <c r="D117" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E117" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F117" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G117" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H117" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I117" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J117" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K117" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L117" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="60" customHeight="1" s="88">
+      <c r="A118" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B118" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_fire_moving_forward</t>
+        </is>
+      </c>
+      <c r="C118" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_fire_moving_forward</t>
+        </is>
+      </c>
+      <c r="D118" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E118" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F118" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G118" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H118" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I118" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J118" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K118" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L118" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="60" customHeight="1" s="88">
+      <c r="A119" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B119" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_walking_forward</t>
+        </is>
+      </c>
+      <c r="C119" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_walking_forward</t>
+        </is>
+      </c>
+      <c r="D119" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E119" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F119" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G119" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H119" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I119" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J119" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K119" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L119" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="60" customHeight="1" s="88">
+      <c r="A120" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B120" s="128" t="inlineStr">
+        <is>
+          <t>longgun_fire_moving_forward</t>
+        </is>
+      </c>
+      <c r="C120" s="127" t="inlineStr">
+        <is>
+          <t>longgun_fire_moving_forward</t>
+        </is>
+      </c>
+      <c r="D120" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E120" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F120" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G120" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H120" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I120" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J120" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K120" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L120" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="60" customHeight="1" s="88">
+      <c r="A121" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B121" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_walking_forward</t>
+        </is>
+      </c>
+      <c r="C121" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_walking_forward</t>
+        </is>
+      </c>
+      <c r="D121" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E121" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F121" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G121" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H121" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I121" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J121" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K121" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L121" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="60" customHeight="1" s="88">
+      <c r="A122" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B122" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_fire_moving_forward</t>
+        </is>
+      </c>
+      <c r="C122" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_fire_moving_forward</t>
+        </is>
+      </c>
+      <c r="D122" s="128" t="inlineStr">
+        <is>
+          <t>moving + family/speed/local direction</t>
+        </is>
+      </c>
+      <c r="E122" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F122" s="128" t="inlineStr">
+        <is>
+          <t>独立原地脚步；无根运动</t>
+        </is>
+      </c>
+      <c r="G122" s="127" t="inlineStr">
+        <is>
+          <t>反移动方向拖曳/错相回弹</t>
+        </is>
+      </c>
+      <c r="H122" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I122" s="127" t="inlineStr">
+        <is>
+          <t>主掌心跟随；双手类别公开支撑误差</t>
+        </is>
+      </c>
+      <c r="J122" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K122" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L122" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="60" customHeight="1" s="88">
+      <c r="A123" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B123" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_stow_slot0</t>
+        </is>
+      </c>
+      <c r="C123" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_stow_slot0</t>
+        </is>
+      </c>
+      <c r="D123" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E123" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F123" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G123" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H123" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I123" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J123" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K123" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L123" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="60" customHeight="1" s="88">
+      <c r="A124" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B124" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_draw_slot0</t>
+        </is>
+      </c>
+      <c r="C124" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_draw_slot0</t>
+        </is>
+      </c>
+      <c r="D124" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E124" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F124" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G124" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H124" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I124" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J124" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K124" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L124" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="60" customHeight="1" s="88">
+      <c r="A125" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B125" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_stow_slot1</t>
+        </is>
+      </c>
+      <c r="C125" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_stow_slot1</t>
+        </is>
+      </c>
+      <c r="D125" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E125" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F125" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G125" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H125" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I125" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J125" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K125" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L125" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="60" customHeight="1" s="88">
+      <c r="A126" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B126" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_draw_slot1</t>
+        </is>
+      </c>
+      <c r="C126" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_draw_slot1</t>
+        </is>
+      </c>
+      <c r="D126" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E126" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F126" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G126" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H126" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I126" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J126" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K126" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L126" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="60" customHeight="1" s="88">
+      <c r="A127" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B127" s="128" t="inlineStr">
+        <is>
+          <t>longgun_stow_slot0</t>
+        </is>
+      </c>
+      <c r="C127" s="127" t="inlineStr">
+        <is>
+          <t>longgun_stow_slot0</t>
+        </is>
+      </c>
+      <c r="D127" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E127" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F127" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G127" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H127" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I127" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J127" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K127" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L127" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="60" customHeight="1" s="88">
+      <c r="A128" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B128" s="128" t="inlineStr">
+        <is>
+          <t>longgun_draw_slot0</t>
+        </is>
+      </c>
+      <c r="C128" s="127" t="inlineStr">
+        <is>
+          <t>longgun_draw_slot0</t>
+        </is>
+      </c>
+      <c r="D128" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E128" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F128" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G128" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H128" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I128" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J128" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K128" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L128" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="60" customHeight="1" s="88">
+      <c r="A129" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B129" s="128" t="inlineStr">
+        <is>
+          <t>longgun_stow_slot1</t>
+        </is>
+      </c>
+      <c r="C129" s="127" t="inlineStr">
+        <is>
+          <t>longgun_stow_slot1</t>
+        </is>
+      </c>
+      <c r="D129" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E129" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F129" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G129" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H129" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I129" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J129" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K129" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L129" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="60" customHeight="1" s="88">
+      <c r="A130" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B130" s="128" t="inlineStr">
+        <is>
+          <t>longgun_draw_slot1</t>
+        </is>
+      </c>
+      <c r="C130" s="127" t="inlineStr">
+        <is>
+          <t>longgun_draw_slot1</t>
+        </is>
+      </c>
+      <c r="D130" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E130" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F130" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G130" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H130" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I130" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J130" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K130" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L130" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="60" customHeight="1" s="88">
+      <c r="A131" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B131" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_stow_slot0</t>
+        </is>
+      </c>
+      <c r="C131" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_stow_slot0</t>
+        </is>
+      </c>
+      <c r="D131" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E131" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F131" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G131" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H131" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I131" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J131" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K131" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L131" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="60" customHeight="1" s="88">
+      <c r="A132" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B132" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_draw_slot0</t>
+        </is>
+      </c>
+      <c r="C132" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_draw_slot0</t>
+        </is>
+      </c>
+      <c r="D132" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E132" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F132" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G132" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H132" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I132" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J132" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K132" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L132" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="60" customHeight="1" s="88">
+      <c r="A133" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B133" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_stow_slot1</t>
+        </is>
+      </c>
+      <c r="C133" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_stow_slot1</t>
+        </is>
+      </c>
+      <c r="D133" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E133" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F133" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G133" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H133" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I133" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J133" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K133" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L133" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="60" customHeight="1" s="88">
+      <c r="A134" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B134" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_draw_slot1</t>
+        </is>
+      </c>
+      <c r="C134" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_draw_slot1</t>
+        </is>
+      </c>
+      <c r="D134" s="128" t="inlineStr">
+        <is>
+          <t>weapon_transition.phase/progress + family/slot</t>
+        </is>
+      </c>
+      <c r="E134" s="128" t="inlineStr">
+        <is>
+          <t>Player3D状态所有者</t>
+        </is>
+      </c>
+      <c r="F134" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G134" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H134" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I134" s="127" t="inlineStr">
+        <is>
+          <t>右掌握点跟随；背槽端点对齐</t>
+        </is>
+      </c>
+      <c r="J134" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K134" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L134" s="127" t="inlineStr">
+        <is>
+          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12936,7 +17338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.1" customWidth="1" style="87" min="1" max="1"/>
@@ -15069,6 +19471,446 @@
       </c>
       <c r="D107" s="91" t="n">
         <v>3586</v>
+      </c>
+    </row>
+    <row r="108" ht="64.5" customHeight="1" s="88">
+      <c r="A108" s="91" t="inlineStr">
+        <is>
+          <t>v026动作母版（authored，未接线）</t>
+        </is>
+      </c>
+      <c r="B108" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend</t>
+        </is>
+      </c>
+      <c r="C108" s="150" t="inlineStr">
+        <is>
+          <t>0081e249b36db0ce1cbd3aff5e4111980c31c0920921c3c4123b9d13eee33edc</t>
+        </is>
+      </c>
+      <c r="D108" s="91" t="n">
+        <v>73063284</v>
+      </c>
+    </row>
+    <row r="109" ht="64.5" customHeight="1" s="88">
+      <c r="A109" s="91" t="inlineStr">
+        <is>
+          <t>v026源级中转（待导出）</t>
+        </is>
+      </c>
+      <c r="B109" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json</t>
+        </is>
+      </c>
+      <c r="C109" s="150" t="inlineStr">
+        <is>
+          <t>f7c5f6b77362831c9ba2e4a091f5554f5cdaa2d841191ca035debe39ffe41638</t>
+        </is>
+      </c>
+      <c r="D109" s="91" t="n">
+        <v>10741</v>
+      </c>
+    </row>
+    <row r="110" ht="64.5" customHeight="1" s="88">
+      <c r="A110" s="91" t="inlineStr">
+        <is>
+          <t>v027三方向动作母版（authored）</t>
+        </is>
+      </c>
+      <c r="B110" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend</t>
+        </is>
+      </c>
+      <c r="C110" s="150" t="inlineStr">
+        <is>
+          <t>3558a0eb983bfdc965164dc7d6a9030f5ec10525199155847f7cd22e71c11490</t>
+        </is>
+      </c>
+      <c r="D110" s="91" t="n">
+        <v>98958981</v>
+      </c>
+    </row>
+    <row r="111" ht="64.5" customHeight="1" s="88">
+      <c r="A111" s="91" t="inlineStr">
+        <is>
+          <t>v027源级中转（待导出）</t>
+        </is>
+      </c>
+      <c r="B111" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json</t>
+        </is>
+      </c>
+      <c r="C111" s="150" t="inlineStr">
+        <is>
+          <t>1e489c6634dad643bcfe70da05186afa60c3c63bdb45b04fb041245b56c93a2f</t>
+        </is>
+      </c>
+      <c r="D111" s="91" t="n">
+        <v>12520</v>
+      </c>
+    </row>
+    <row r="112" ht="64.5" customHeight="1" s="88">
+      <c r="A112" s="91" t="inlineStr">
+        <is>
+          <t>v028耳朵跟随动作母版（authored）</t>
+        </is>
+      </c>
+      <c r="B112" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend</t>
+        </is>
+      </c>
+      <c r="C112" s="150" t="inlineStr">
+        <is>
+          <t>d646646d5c5380edd9d571cb5d8c793eda78e73bb50e112e189312643af66b51</t>
+        </is>
+      </c>
+      <c r="D112" s="91" t="n">
+        <v>122760213</v>
+      </c>
+    </row>
+    <row r="113" ht="64.5" customHeight="1" s="88">
+      <c r="A113" s="91" t="inlineStr">
+        <is>
+          <t>v028源级中转（待导出）</t>
+        </is>
+      </c>
+      <c r="B113" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json</t>
+        </is>
+      </c>
+      <c r="C113" s="150" t="inlineStr">
+        <is>
+          <t>0d9aef4303349b3adb8dba614113a1ff96898d77cd5d69983c2d5f273fcdb0c9</t>
+        </is>
+      </c>
+      <c r="D113" s="91" t="n">
+        <v>20235</v>
+      </c>
+    </row>
+    <row r="114" ht="64.5" customHeight="1" s="88">
+      <c r="A114" s="91" t="inlineStr">
+        <is>
+          <t>v029动作源</t>
+        </is>
+      </c>
+      <c r="B114" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend</t>
+        </is>
+      </c>
+      <c r="C114" s="150" t="inlineStr">
+        <is>
+          <t>9abec2bb0d155acc36b82701e065a9fba64906247dcb06888ee4528abadd5fca</t>
+        </is>
+      </c>
+      <c r="D114" s="91" t="n">
+        <v>142501746</v>
+      </c>
+    </row>
+    <row r="115" ht="64.5" customHeight="1" s="88">
+      <c r="A115" s="91" t="inlineStr">
+        <is>
+          <t>v029正式中转</t>
+        </is>
+      </c>
+      <c r="B115" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C115" s="150" t="inlineStr">
+        <is>
+          <t>6122c60d33b4cfff12d1f142679476b79fe86b46efb8c784c655f251b713e6cc</t>
+        </is>
+      </c>
+      <c r="D115" s="91" t="n">
+        <v>11551</v>
+      </c>
+    </row>
+    <row r="116" ht="64.5" customHeight="1" s="88">
+      <c r="A116" s="91" t="inlineStr">
+        <is>
+          <t>v029运行采样库</t>
+        </is>
+      </c>
+      <c r="B116" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C116" s="150" t="inlineStr">
+        <is>
+          <t>ee3f1f368f64efa00cfe0de47e25d199c334dabbf6e49af8dc6b1a50c940e38b</t>
+        </is>
+      </c>
+      <c r="D116" s="91" t="n">
+        <v>6430468</v>
+      </c>
+    </row>
+    <row r="117" ht="64.5" customHeight="1" s="88">
+      <c r="A117" s="91" t="inlineStr">
+        <is>
+          <t>v029标准GLB</t>
+        </is>
+      </c>
+      <c r="B117" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C117" s="150" t="inlineStr">
+        <is>
+          <t>20fa768a52de8db7abf140d9a412a61ce01c343f9c0091e9968a80c4ab2461ce</t>
+        </is>
+      </c>
+      <c r="D117" s="91" t="n">
+        <v>958896</v>
+      </c>
+    </row>
+    <row r="118" ht="64.5" customHeight="1" s="88">
+      <c r="A118" s="91" t="inlineStr">
+        <is>
+          <t>v030动作源</t>
+        </is>
+      </c>
+      <c r="B118" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend</t>
+        </is>
+      </c>
+      <c r="C118" s="150" t="inlineStr">
+        <is>
+          <t>2cfb06c94b4e9361a9036a085e136199ad002bfa88f160224cf80f2906d4a3e5</t>
+        </is>
+      </c>
+      <c r="D118" s="91" t="n">
+        <v>191962400</v>
+      </c>
+    </row>
+    <row r="119" ht="64.5" customHeight="1" s="88">
+      <c r="A119" s="91" t="inlineStr">
+        <is>
+          <t>v030正式中转</t>
+        </is>
+      </c>
+      <c r="B119" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C119" s="150" t="inlineStr">
+        <is>
+          <t>bf63482b53e30ad9341a2e8a054073b80ebe5d765d9dc38e86146eaf37da8b0e</t>
+        </is>
+      </c>
+      <c r="D119" s="91" t="n">
+        <v>15563</v>
+      </c>
+    </row>
+    <row r="120" ht="64.5" customHeight="1" s="88">
+      <c r="A120" s="91" t="inlineStr">
+        <is>
+          <t>v030运行采样库</t>
+        </is>
+      </c>
+      <c r="B120" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C120" s="150" t="inlineStr">
+        <is>
+          <t>45d9be8289ffc2aca56cc9890242fcbbf3b03b9554e23f999a8b254668c141dc</t>
+        </is>
+      </c>
+      <c r="D120" s="91" t="n">
+        <v>10082661</v>
+      </c>
+    </row>
+    <row r="121" ht="64.5" customHeight="1" s="88">
+      <c r="A121" s="91" t="inlineStr">
+        <is>
+          <t>v030标准GLB</t>
+        </is>
+      </c>
+      <c r="B121" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C121" s="150" t="inlineStr">
+        <is>
+          <t>8ffc72435993b83e8bcba6dc0611d34f08a6c76eced30e9c92df790920677c04</t>
+        </is>
+      </c>
+      <c r="D121" s="91" t="n">
+        <v>1679952</v>
+      </c>
+    </row>
+    <row r="122" ht="64.5" customHeight="1" s="88">
+      <c r="A122" s="91" t="inlineStr">
+        <is>
+          <t>v031动作源</t>
+        </is>
+      </c>
+      <c r="B122" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend</t>
+        </is>
+      </c>
+      <c r="C122" s="150" t="inlineStr">
+        <is>
+          <t>faabced8621a80139e33a6652a36deaa02b815d5c1ff44046454630ac6f903ff</t>
+        </is>
+      </c>
+      <c r="D122" s="91" t="n">
+        <v>224032944</v>
+      </c>
+    </row>
+    <row r="123" ht="64.5" customHeight="1" s="88">
+      <c r="A123" s="91" t="inlineStr">
+        <is>
+          <t>v031正式中转</t>
+        </is>
+      </c>
+      <c r="B123" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C123" s="150" t="inlineStr">
+        <is>
+          <t>c89eb481335dc4750b381a2b27d781c95aedc27dba12b81d25f39f009af71e73</t>
+        </is>
+      </c>
+      <c r="D123" s="91" t="n">
+        <v>15568</v>
+      </c>
+    </row>
+    <row r="124" ht="64.5" customHeight="1" s="88">
+      <c r="A124" s="91" t="inlineStr">
+        <is>
+          <t>v031运行采样库</t>
+        </is>
+      </c>
+      <c r="B124" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C124" s="150" t="inlineStr">
+        <is>
+          <t>b413287a7b5e607b491dc5c2ec5253975b85b8eccddfcec72cbef097dfec775a</t>
+        </is>
+      </c>
+      <c r="D124" s="91" t="n">
+        <v>10089425</v>
+      </c>
+    </row>
+    <row r="125" ht="64.5" customHeight="1" s="88">
+      <c r="A125" s="91" t="inlineStr">
+        <is>
+          <t>v031标准GLB</t>
+        </is>
+      </c>
+      <c r="B125" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C125" s="150" t="inlineStr">
+        <is>
+          <t>21ceaacb64cfb00e2d3313fc34940125106d0dd63474ccd29e2510355c84f2b3</t>
+        </is>
+      </c>
+      <c r="D125" s="91" t="n">
+        <v>1436492</v>
+      </c>
+    </row>
+    <row r="126" ht="64.5" customHeight="1" s="88">
+      <c r="A126" s="91" t="inlineStr">
+        <is>
+          <t>v032动作源</t>
+        </is>
+      </c>
+      <c r="B126" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend</t>
+        </is>
+      </c>
+      <c r="C126" s="150" t="inlineStr">
+        <is>
+          <t>0fa3767ec1a7c57c8c686f97eb809aa65100bb6725e664cacab624059069ea9d</t>
+        </is>
+      </c>
+      <c r="D126" s="91" t="n">
+        <v>260138212</v>
+      </c>
+    </row>
+    <row r="127" ht="64.5" customHeight="1" s="88">
+      <c r="A127" s="91" t="inlineStr">
+        <is>
+          <t>v032正式中转</t>
+        </is>
+      </c>
+      <c r="B127" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C127" s="150" t="inlineStr">
+        <is>
+          <t>f2cd88ede77c391ac38f3781b69e4ac00da1abae3f4fd2d197c7ec7b9af24360</t>
+        </is>
+      </c>
+      <c r="D127" s="91" t="n">
+        <v>18052</v>
+      </c>
+    </row>
+    <row r="128" ht="64.5" customHeight="1" s="88">
+      <c r="A128" s="91" t="inlineStr">
+        <is>
+          <t>v032运行采样库</t>
+        </is>
+      </c>
+      <c r="B128" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C128" s="150" t="inlineStr">
+        <is>
+          <t>081525c870cfe3954d21056da6ae44542e18a1ba218ff2ff7af0be01fbcb6b0b</t>
+        </is>
+      </c>
+      <c r="D128" s="91" t="n">
+        <v>12479676</v>
+      </c>
+    </row>
+    <row r="129" ht="64.5" customHeight="1" s="88">
+      <c r="A129" s="91" t="inlineStr">
+        <is>
+          <t>v032标准GLB</t>
+        </is>
+      </c>
+      <c r="B129" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C129" s="150" t="inlineStr">
+        <is>
+          <t>439081827701d079ef91d9fbcee0f86d62d8daf2f00ccd65a3c54f3f84f43d0b</t>
+        </is>
+      </c>
+      <c r="D129" s="91" t="n">
+        <v>1685548</v>
       </c>
     </row>
   </sheetData>
@@ -15122,6 +19964,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="88">
       <c r="A4" s="153" t="inlineStr">
         <is>
@@ -15301,7 +20144,7 @@
       </c>
       <c r="E6" s="162" t="inlineStr">
         <is>
-          <t>模型、动作双母版：完整路径见「角色中转记录」</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；模型保持v021</t>
         </is>
       </c>
       <c r="F6" s="162" t="inlineStr">
@@ -15311,7 +20154,7 @@
       </c>
       <c r="G6" s="163" t="inlineStr">
         <is>
-          <t>src/player3d/PlayerAvatar3D.gd</t>
+          <t>src/player3d/PlayerAvatar3D.gd; src/player3d/CharacterMotionLibrary3D.gd</t>
         </is>
       </c>
       <c r="H6" s="162" t="inlineStr">
@@ -15331,7 +20174,7 @@
       </c>
       <c r="K6" s="162" t="inlineStr">
         <is>
-          <t>可见边界 0.724×1.050×0.452m（含耳）；玩法碰撞由 Player3D 的 1.5m CapsuleShape3D 独占</t>
+          <t>源高1.5m，默认倍率0.8/高1.2m；Player3D碰撞不变</t>
         </is>
       </c>
       <c r="L6" s="162" t="inlineStr">
@@ -15346,17 +20189,17 @@
       </c>
       <c r="N6" s="162" t="inlineStr">
         <is>
-          <t>原型已接入</t>
+          <t>active</t>
         </is>
       </c>
       <c r="O6" s="163" t="inlineStr">
         <is>
-          <t>v021</t>
+          <t>v032</t>
         </is>
       </c>
       <c r="P6" s="164" t="inlineStr">
         <is>
-          <t>双文件共享骨架；状态 active；中转 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>模型装配v021；动作v032；专项通过；其他长枪支撑差异、脚底锁地、换弹蓄力近战待完善。assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
         </is>
       </c>
     </row>
@@ -16277,7 +21120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="87" min="1" max="1"/>
@@ -16748,6 +21591,265 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="60" customHeight="1" s="88">
+      <c r="A17" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.11</t>
+        </is>
+      </c>
+      <c r="B17" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C17" s="98" t="inlineStr">
+        <is>
+          <t>持枪站立待机位置修订</t>
+        </is>
+      </c>
+      <c r="D17" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E17" s="98" t="inlineStr">
+        <is>
+          <t>v026短枪参考位置、长枪机枪前移，三枪头部/躯干相交采样检查；旧源保留。</t>
+        </is>
+      </c>
+      <c r="F17" s="98" t="inlineStr">
+        <is>
+          <t>authored；运行路径、状态和版本保持。</t>
+        </is>
+      </c>
+      <c r="G17" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" s="88">
+      <c r="A18" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.12</t>
+        </is>
+      </c>
+      <c r="B18" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C18" s="98" t="inlineStr">
+        <is>
+          <t>18条持枪三方向移动循环</t>
+        </is>
+      </c>
+      <c r="D18" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E18" s="98" t="inlineStr">
+        <is>
+          <t>v027，保留v026姿态与旧动作；各方向独立步态，根不移动。</t>
+        </is>
+      </c>
+      <c r="F18" s="98" t="inlineStr">
+        <is>
+          <t>源级authored；运行版本与Prefab不变。</t>
+        </is>
+      </c>
+      <c r="G18" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" s="88">
+      <c r="A19" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.13</t>
+        </is>
+      </c>
+      <c r="B19" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C19" s="98" t="inlineStr">
+        <is>
+          <t>18条移动循环耳朵跟随</t>
+        </is>
+      </c>
+      <c r="D19" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E19" s="98" t="inlineStr">
+        <is>
+          <t>v028仅补耳朵旋转；保留v027旧动作、持枪和脚步。</t>
+        </is>
+      </c>
+      <c r="F19" s="98" t="inlineStr">
+        <is>
+          <t>源级authored；运行版本和Prefab不变。</t>
+        </is>
+      </c>
+      <c r="G19" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" s="88">
+      <c r="A20" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.14</t>
+        </is>
+      </c>
+      <c r="B20" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C20" s="98" t="inlineStr">
+        <is>
+          <t>四方向持枪动作正式接入</t>
+        </is>
+      </c>
+      <c r="D20" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E20" s="98" t="inlineStr">
+        <is>
+          <t>v029动作库49条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F20" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；战斗动作/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G20" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" s="88">
+      <c r="A21" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.15</t>
+        </is>
+      </c>
+      <c r="B21" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C21" s="98" t="inlineStr">
+        <is>
+          <t>三类枪举枪射击修复</t>
+        </is>
+      </c>
+      <c r="D21" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E21" s="98" t="inlineStr">
+        <is>
+          <t>v030动作库76条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F21" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；换弹蓄力近战/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G21" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1" s="88">
+      <c r="A22" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.16</t>
+        </is>
+      </c>
+      <c r="B22" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C22" s="98" t="inlineStr">
+        <is>
+          <t>长枪机枪斜持与机枪收近</t>
+        </is>
+      </c>
+      <c r="D22" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E22" s="98" t="inlineStr">
+        <is>
+          <t>v031动作库76条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F22" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；换弹蓄力近战/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G22" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1" s="88">
+      <c r="A23" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.17</t>
+        </is>
+      </c>
+      <c r="B23" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C23" s="98" t="inlineStr">
+        <is>
+          <t>无枪摆臂与双槽收取枪</t>
+        </is>
+      </c>
+      <c r="D23" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E23" s="98" t="inlineStr">
+        <is>
+          <t>v032动作库88条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F23" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；换弹蓄力近战/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G23" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I13" s="116" t="inlineStr">
         <is>
-          <t>10 existing states / unarmed swing / stow-draw upper-body overlay</t>
+          <t>10 existing states / 3 family reload overlays / gameplay progress sampling</t>
         </is>
       </c>
       <c r="J13" s="116" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M13" s="116" t="inlineStr">
         <is>
-          <t>v032</t>
+          <t>v033</t>
         </is>
       </c>
       <c r="N13" s="117" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T13" s="116" t="inlineStr">
         <is>
-          <t>ca9d03d23c08dcdb2313171a4ce74e51f47aa8db371103ea8c80e7920d7754ff</t>
+          <t>c991ad2f8a65e796184684344b898672c2a67d4509d0a1cac37644ebe7987535</t>
         </is>
       </c>
       <c r="U13" s="116" t="inlineStr">
@@ -3585,7 +3585,7 @@
 2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。
 2026-09-29：v021 模型及原12动作保持不变；新增 v022 Blender 坐姿滑行循环 seated，Player3D 九态状态机与 99F 两把可驾驶椅接入；verify_pushable_base_chairs 通过。
 2026-09-29：v023 Blender 坐姿源将双脚向座面前方伸出；角色乘坐时可正常射击，相机补偿座面抬升，离座恢复世界碰撞。
-2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。</t>
+2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。；v033新增三类独立换弹，按WeaponModel3D真实progress同步播放；保留88条原剪辑。0.4/1.5/4秒、移动/取消/换槽打断专项174检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v033.md。</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.94" customWidth="1" style="87" min="1" max="1"/>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="L61" s="127" t="inlineStr">
         <is>
-          <t>v032 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="L62" s="127" t="inlineStr">
         <is>
-          <t>v032 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="L63" s="127" t="inlineStr">
         <is>
-          <t>v032 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="L64" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="L65" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="L66" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="L67" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="L68" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="L69" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="L70" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="L71" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L72" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="L73" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="L74" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="L75" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="L76" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="L77" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="L78" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="L79" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="L80" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13368,7 +13368,7 @@
       </c>
       <c r="L81" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="L82" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="L83" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="L84" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="L85" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13678,7 @@
       </c>
       <c r="L86" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="L87" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="L88" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="L89" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="L90" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="L91" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="L92" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="L93" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="L94" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="L95" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="L96" s="127" t="inlineStr">
         <is>
-          <t>v032 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="L97" s="127" t="inlineStr">
         <is>
-          <t>v032 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="L98" s="127" t="inlineStr">
         <is>
-          <t>v032 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="L99" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="L100" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14608,7 +14608,7 @@
       </c>
       <c r="L101" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="L102" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
       </c>
       <c r="L103" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="L104" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="L105" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="L106" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="L107" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="L108" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="L109" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="L110" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="L111" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="L112" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="L113" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="L114" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="L115" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="L116" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="L117" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="L118" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="L119" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="L120" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="L121" s="127" t="inlineStr">
         <is>
-          <t>v032 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="L122" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="L123" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="L124" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="L125" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="L126" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="L127" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="L128" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="L129" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="L130" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="L131" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="L132" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="L133" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16654,7 +16654,193 @@
       </c>
       <c r="L134" s="127" t="inlineStr">
         <is>
-          <t>v032 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；换弹蓄力近战/锁地待完善。</t>
+          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="60" customHeight="1" s="88">
+      <c r="A135" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B135" s="128" t="inlineStr">
+        <is>
+          <t>longgun_reload</t>
+        </is>
+      </c>
+      <c r="C135" s="127" t="inlineStr">
+        <is>
+          <t>longgun_reload</t>
+        </is>
+      </c>
+      <c r="D135" s="128" t="inlineStr">
+        <is>
+          <t>get_reload_snapshot.progress + weapon family</t>
+        </is>
+      </c>
+      <c r="E135" s="128" t="inlineStr">
+        <is>
+          <t>WeaponModel3D换弹计时所有者</t>
+        </is>
+      </c>
+      <c r="F135" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G135" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H135" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I135" s="127" t="inlineStr">
+        <is>
+          <t>右掌主握；左手取弹装入回位</t>
+        </is>
+      </c>
+      <c r="J135" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K135" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L135" s="127" t="inlineStr">
+        <is>
+          <t>v033 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="60" customHeight="1" s="88">
+      <c r="A136" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B136" s="128" t="inlineStr">
+        <is>
+          <t>machinegun_reload</t>
+        </is>
+      </c>
+      <c r="C136" s="127" t="inlineStr">
+        <is>
+          <t>machinegun_reload</t>
+        </is>
+      </c>
+      <c r="D136" s="128" t="inlineStr">
+        <is>
+          <t>get_reload_snapshot.progress + weapon family</t>
+        </is>
+      </c>
+      <c r="E136" s="128" t="inlineStr">
+        <is>
+          <t>WeaponModel3D换弹计时所有者</t>
+        </is>
+      </c>
+      <c r="F136" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G136" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H136" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I136" s="127" t="inlineStr">
+        <is>
+          <t>右掌主握；左手取弹装入回位</t>
+        </is>
+      </c>
+      <c r="J136" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K136" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L136" s="127" t="inlineStr">
+        <is>
+          <t>v033 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="60" customHeight="1" s="88">
+      <c r="A137" s="127" t="inlineStr">
+        <is>
+          <t>表现动作变体（非顶层状态）</t>
+        </is>
+      </c>
+      <c r="B137" s="128" t="inlineStr">
+        <is>
+          <t>sidearm_reload</t>
+        </is>
+      </c>
+      <c r="C137" s="127" t="inlineStr">
+        <is>
+          <t>sidearm_reload</t>
+        </is>
+      </c>
+      <c r="D137" s="128" t="inlineStr">
+        <is>
+          <t>get_reload_snapshot.progress + weapon family</t>
+        </is>
+      </c>
+      <c r="E137" s="128" t="inlineStr">
+        <is>
+          <t>WeaponModel3D换弹计时所有者</t>
+        </is>
+      </c>
+      <c r="F137" s="128" t="inlineStr">
+        <is>
+          <t>上半身叠加；下肢沿用移动循环</t>
+        </is>
+      </c>
+      <c r="G137" s="127" t="inlineStr">
+        <is>
+          <t>耳朵沿用基础动作</t>
+        </is>
+      </c>
+      <c r="H137" s="127" t="inlineStr">
+        <is>
+          <t>源动作采样，不用IK</t>
+        </is>
+      </c>
+      <c r="I137" s="127" t="inlineStr">
+        <is>
+          <t>右掌主握；左手取弹装入回位</t>
+        </is>
+      </c>
+      <c r="J137" s="127" t="inlineStr">
+        <is>
+          <t>无碰撞修改</t>
+        </is>
+      </c>
+      <c r="K137" s="128" t="inlineStr">
+        <is>
+          <t>无新增VFX</t>
+        </is>
+      </c>
+      <c r="L137" s="127" t="inlineStr">
+        <is>
+          <t>v033 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -17338,7 +17524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.1" customWidth="1" style="87" min="1" max="1"/>
@@ -19911,6 +20097,86 @@
       </c>
       <c r="D129" s="91" t="n">
         <v>1685548</v>
+      </c>
+    </row>
+    <row r="130" ht="64.5" customHeight="1" s="88">
+      <c r="A130" s="91" t="inlineStr">
+        <is>
+          <t>v033动作源</t>
+        </is>
+      </c>
+      <c r="B130" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend</t>
+        </is>
+      </c>
+      <c r="C130" s="150" t="inlineStr">
+        <is>
+          <t>1e690ad4479915a0c173a6eeb411c3bbf6a83e97971e6eb8879c749c6096ab94</t>
+        </is>
+      </c>
+      <c r="D130" s="91" t="n">
+        <v>276603632</v>
+      </c>
+    </row>
+    <row r="131" ht="64.5" customHeight="1" s="88">
+      <c r="A131" s="91" t="inlineStr">
+        <is>
+          <t>v033正式中转</t>
+        </is>
+      </c>
+      <c r="B131" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C131" s="150" t="inlineStr">
+        <is>
+          <t>109902defd29913cb5630c5956a4610e3ef2ad8f9440b144a1ebfa266bfa2f77</t>
+        </is>
+      </c>
+      <c r="D131" s="91" t="n">
+        <v>17797</v>
+      </c>
+    </row>
+    <row r="132" ht="64.5" customHeight="1" s="88">
+      <c r="A132" s="91" t="inlineStr">
+        <is>
+          <t>v033运行采样库</t>
+        </is>
+      </c>
+      <c r="B132" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C132" s="150" t="inlineStr">
+        <is>
+          <t>d99434f852e64111a0b8da9acd316d9b33fdd7a06b0280d342b59fda2be72d93</t>
+        </is>
+      </c>
+      <c r="D132" s="91" t="n">
+        <v>13799260</v>
+      </c>
+    </row>
+    <row r="133" ht="64.5" customHeight="1" s="88">
+      <c r="A133" s="91" t="inlineStr">
+        <is>
+          <t>v033标准GLB</t>
+        </is>
+      </c>
+      <c r="B133" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C133" s="150" t="inlineStr">
+        <is>
+          <t>a32b3bc97825b9b0ff48bb3c67bd3affb148c123f815bf3eef0ac62c25429fb9</t>
+        </is>
+      </c>
+      <c r="D133" s="91" t="n">
+        <v>1769716</v>
       </c>
     </row>
   </sheetData>
@@ -20144,7 +20410,7 @@
       </c>
       <c r="E6" s="162" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend；模型保持v021</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；模型保持v021</t>
         </is>
       </c>
       <c r="F6" s="162" t="inlineStr">
@@ -20194,12 +20460,12 @@
       </c>
       <c r="O6" s="163" t="inlineStr">
         <is>
-          <t>v032</t>
+          <t>v033</t>
         </is>
       </c>
       <c r="P6" s="164" t="inlineStr">
         <is>
-          <t>模型装配v021；动作v032；专项通过；其他长枪支撑差异、脚底锁地、换弹蓄力近战待完善。assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+          <t>模型装配v021；动作v033；专项通过；其他长枪支撑差异、脚底锁地、蓄力近战待完善。assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
         </is>
       </c>
     </row>
@@ -21120,7 +21386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="87" min="1" max="1"/>
@@ -21850,6 +22116,43 @@
         </is>
       </c>
     </row>
+    <row r="24" ht="60" customHeight="1" s="88">
+      <c r="A24" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.18</t>
+        </is>
+      </c>
+      <c r="B24" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C24" s="98" t="inlineStr">
+        <is>
+          <t>三类换弹与实际时长同步</t>
+        </is>
+      </c>
+      <c r="D24" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E24" s="98" t="inlineStr">
+        <is>
+          <t>v033动作库91条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F24" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；蓄力近战/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G24" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M13" s="116" t="inlineStr">
         <is>
-          <t>v033</t>
+          <t>v037</t>
         </is>
       </c>
       <c r="N13" s="117" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T13" s="116" t="inlineStr">
         <is>
-          <t>c991ad2f8a65e796184684344b898672c2a67d4509d0a1cac37644ebe7987535</t>
+          <t>6924b230d48d0e70404dedc91a23e2c21ea5074707d9a1690fa3c2242e6c348c</t>
         </is>
       </c>
       <c r="U13" s="116" t="inlineStr">
@@ -3585,7 +3585,7 @@
 2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。
 2026-09-29：v021 模型及原12动作保持不变；新增 v022 Blender 坐姿滑行循环 seated，Player3D 九态状态机与 99F 两把可驾驶椅接入；verify_pushable_base_chairs 通过。
 2026-09-29：v023 Blender 坐姿源将双脚向座面前方伸出；角色乘坐时可正常射击，相机补偿座面抬升，离座恢复世界碰撞。
-2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。；v033新增三类独立换弹，按WeaponModel3D真实progress同步播放；保留88条原剪辑。0.4/1.5/4秒、移动/取消/换槽打断专项174检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v033.md。</t>
+2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。；v033新增三类独立换弹，按WeaponModel3D真实progress同步播放；保留88条原剪辑。0.4/1.5/4秒、移动/取消/换槽打断专项174检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v033.md。；v034增强长枪机枪换弹枪体抬起、倾斜、沉降回弹与压紧回位；短枪及其余89条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项178检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v034.md。；v035机枪枪口转向前下方并抬高枪尾换弹操作位；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项184检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v035.md。；v036机枪枪口向前下方约45度，握点不前伸，近身抬高枪尾换弹；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v036.md。；v037机枪顶视斜向左前45度、枪口上抬；握点近身不前伸；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v037.md。</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="L61" s="127" t="inlineStr">
         <is>
-          <t>v033 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="L62" s="127" t="inlineStr">
         <is>
-          <t>v033 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="L63" s="127" t="inlineStr">
         <is>
-          <t>v033 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="L64" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="L65" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="L66" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="L67" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="L68" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="L69" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="L70" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="L71" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L72" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="L73" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="L74" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="L75" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="L76" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="L77" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="L78" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="L79" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="L80" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13368,7 +13368,7 @@
       </c>
       <c r="L81" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="L82" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="L83" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="L84" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="L85" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13678,7 @@
       </c>
       <c r="L86" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="L87" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="L88" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="L89" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="L90" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="L91" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="L92" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="L93" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="L94" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14236,7 +14236,7 @@
       </c>
       <c r="L95" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="L96" s="127" t="inlineStr">
         <is>
-          <t>v033 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="L97" s="127" t="inlineStr">
         <is>
-          <t>v033 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="L98" s="127" t="inlineStr">
         <is>
-          <t>v033 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="L99" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="L100" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14608,7 +14608,7 @@
       </c>
       <c r="L101" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="L102" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
       </c>
       <c r="L103" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="L104" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="L105" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="L106" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="L107" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="L108" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="L109" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="L110" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="L111" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="L112" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="L113" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="L114" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="L115" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="L116" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="L117" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="L118" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="L119" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="L120" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="L121" s="127" t="inlineStr">
         <is>
-          <t>v033 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="L122" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="L123" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="L124" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="L125" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="L126" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="L127" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="L128" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="L129" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="L130" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="L131" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="L132" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="L133" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16654,7 +16654,7 @@
       </c>
       <c r="L134" s="127" t="inlineStr">
         <is>
-          <t>v033 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="L135" s="127" t="inlineStr">
         <is>
-          <t>v033 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="L136" s="127" t="inlineStr">
         <is>
-          <t>v033 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="L137" s="127" t="inlineStr">
         <is>
-          <t>v033 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -17524,7 +17524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.1" customWidth="1" style="87" min="1" max="1"/>
@@ -20176,6 +20176,326 @@
         </is>
       </c>
       <c r="D133" s="91" t="n">
+        <v>1769716</v>
+      </c>
+    </row>
+    <row r="134" ht="64.5" customHeight="1" s="88">
+      <c r="A134" s="91" t="inlineStr">
+        <is>
+          <t>v034动作源</t>
+        </is>
+      </c>
+      <c r="B134" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend</t>
+        </is>
+      </c>
+      <c r="C134" s="150" t="inlineStr">
+        <is>
+          <t>5e2f0c08537a82c08b8710ebd53a4273bdb3c0b6606942370a91988241c7cc06</t>
+        </is>
+      </c>
+      <c r="D134" s="91" t="n">
+        <v>287419695</v>
+      </c>
+    </row>
+    <row r="135" ht="64.5" customHeight="1" s="88">
+      <c r="A135" s="91" t="inlineStr">
+        <is>
+          <t>v034正式中转</t>
+        </is>
+      </c>
+      <c r="B135" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C135" s="150" t="inlineStr">
+        <is>
+          <t>6e0fc75ad4311ea2e381c526b12b5036e75528f103b706d0b0d83e5c5531df6a</t>
+        </is>
+      </c>
+      <c r="D135" s="91" t="n">
+        <v>17796</v>
+      </c>
+    </row>
+    <row r="136" ht="64.5" customHeight="1" s="88">
+      <c r="A136" s="91" t="inlineStr">
+        <is>
+          <t>v034运行采样库</t>
+        </is>
+      </c>
+      <c r="B136" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C136" s="150" t="inlineStr">
+        <is>
+          <t>017e4de58f4cd45b5b61bc2bb62fe16682359529877026f42cae991b86ed69a2</t>
+        </is>
+      </c>
+      <c r="D136" s="91" t="n">
+        <v>13796253</v>
+      </c>
+    </row>
+    <row r="137" ht="64.5" customHeight="1" s="88">
+      <c r="A137" s="91" t="inlineStr">
+        <is>
+          <t>v034标准GLB</t>
+        </is>
+      </c>
+      <c r="B137" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C137" s="150" t="inlineStr">
+        <is>
+          <t>7077f8399b2dbc66692ecfc5ba5a9684ab80ff5b1a596f49f720b19633dcc4b2</t>
+        </is>
+      </c>
+      <c r="D137" s="91" t="n">
+        <v>1769716</v>
+      </c>
+    </row>
+    <row r="138" ht="64.5" customHeight="1" s="88">
+      <c r="A138" s="91" t="inlineStr">
+        <is>
+          <t>v035动作源</t>
+        </is>
+      </c>
+      <c r="B138" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend</t>
+        </is>
+      </c>
+      <c r="C138" s="150" t="inlineStr">
+        <is>
+          <t>005a05e6908d76ac2b400bf9b56d3a0a96a7cf555bc260f230407538e362b750</t>
+        </is>
+      </c>
+      <c r="D138" s="91" t="n">
+        <v>292827976</v>
+      </c>
+    </row>
+    <row r="139" ht="64.5" customHeight="1" s="88">
+      <c r="A139" s="91" t="inlineStr">
+        <is>
+          <t>v035正式中转</t>
+        </is>
+      </c>
+      <c r="B139" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C139" s="150" t="inlineStr">
+        <is>
+          <t>5b47a2a37493564fe84dd7266cd9f1948b549059490cf3186cbd20622a588384</t>
+        </is>
+      </c>
+      <c r="D139" s="91" t="n">
+        <v>17797</v>
+      </c>
+    </row>
+    <row r="140" ht="64.5" customHeight="1" s="88">
+      <c r="A140" s="91" t="inlineStr">
+        <is>
+          <t>v035运行采样库</t>
+        </is>
+      </c>
+      <c r="B140" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C140" s="150" t="inlineStr">
+        <is>
+          <t>0c33df914fd559d151593174811bb956b89a2796fffc4cc7cbc3e1c07f171d1b</t>
+        </is>
+      </c>
+      <c r="D140" s="91" t="n">
+        <v>13795873</v>
+      </c>
+    </row>
+    <row r="141" ht="64.5" customHeight="1" s="88">
+      <c r="A141" s="91" t="inlineStr">
+        <is>
+          <t>v035标准GLB</t>
+        </is>
+      </c>
+      <c r="B141" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C141" s="150" t="inlineStr">
+        <is>
+          <t>3021994f6bb5813f52b33a1cb0eccb68ce791b7f0d07bf23025ec9a30cbaec11</t>
+        </is>
+      </c>
+      <c r="D141" s="91" t="n">
+        <v>1769716</v>
+      </c>
+    </row>
+    <row r="142" ht="64.5" customHeight="1" s="88">
+      <c r="A142" s="91" t="inlineStr">
+        <is>
+          <t>v036动作源</t>
+        </is>
+      </c>
+      <c r="B142" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend</t>
+        </is>
+      </c>
+      <c r="C142" s="150" t="inlineStr">
+        <is>
+          <t>9cd887054392257a5f0af8f102babfad321b0de11bd0f2e4dbb2a382c6da65dd</t>
+        </is>
+      </c>
+      <c r="D142" s="91" t="n">
+        <v>298235761</v>
+      </c>
+    </row>
+    <row r="143" ht="64.5" customHeight="1" s="88">
+      <c r="A143" s="91" t="inlineStr">
+        <is>
+          <t>v036正式中转</t>
+        </is>
+      </c>
+      <c r="B143" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C143" s="150" t="inlineStr">
+        <is>
+          <t>7743ddb5de24670a94e7bac2f051c2519cfb6d2fb199d169ab6e5deb988d3183</t>
+        </is>
+      </c>
+      <c r="D143" s="91" t="n">
+        <v>17797</v>
+      </c>
+    </row>
+    <row r="144" ht="64.5" customHeight="1" s="88">
+      <c r="A144" s="91" t="inlineStr">
+        <is>
+          <t>v036运行采样库</t>
+        </is>
+      </c>
+      <c r="B144" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C144" s="150" t="inlineStr">
+        <is>
+          <t>e9139e81f5b97c11a1b514540737051118d99c7712d7980fe75cb0177341d754</t>
+        </is>
+      </c>
+      <c r="D144" s="91" t="n">
+        <v>13796396</v>
+      </c>
+    </row>
+    <row r="145" ht="64.5" customHeight="1" s="88">
+      <c r="A145" s="91" t="inlineStr">
+        <is>
+          <t>v036标准GLB</t>
+        </is>
+      </c>
+      <c r="B145" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C145" s="150" t="inlineStr">
+        <is>
+          <t>22880bb4b477ba0741e8cb2e2b95d7c483eac9529de52a44352f3f46b2152e10</t>
+        </is>
+      </c>
+      <c r="D145" s="91" t="n">
+        <v>1769716</v>
+      </c>
+    </row>
+    <row r="146" ht="64.5" customHeight="1" s="88">
+      <c r="A146" s="91" t="inlineStr">
+        <is>
+          <t>v037动作源</t>
+        </is>
+      </c>
+      <c r="B146" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend</t>
+        </is>
+      </c>
+      <c r="C146" s="150" t="inlineStr">
+        <is>
+          <t>65723230d26c8bce2ec06f63d4a35b66f0984582316953492d275069d635d38e</t>
+        </is>
+      </c>
+      <c r="D146" s="91" t="n">
+        <v>303643546</v>
+      </c>
+    </row>
+    <row r="147" ht="64.5" customHeight="1" s="88">
+      <c r="A147" s="91" t="inlineStr">
+        <is>
+          <t>v037正式中转</t>
+        </is>
+      </c>
+      <c r="B147" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C147" s="150" t="inlineStr">
+        <is>
+          <t>ae650c8a44fb3655780cf18487529044c2238d3b8f92008a11444697981b3f0d</t>
+        </is>
+      </c>
+      <c r="D147" s="91" t="n">
+        <v>17797</v>
+      </c>
+    </row>
+    <row r="148" ht="64.5" customHeight="1" s="88">
+      <c r="A148" s="91" t="inlineStr">
+        <is>
+          <t>v037运行采样库</t>
+        </is>
+      </c>
+      <c r="B148" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C148" s="150" t="inlineStr">
+        <is>
+          <t>c82599925724f4fc48a3291f0a0da08b820bb8f364f67eb56ae47130a7b97470</t>
+        </is>
+      </c>
+      <c r="D148" s="91" t="n">
+        <v>13795797</v>
+      </c>
+    </row>
+    <row r="149" ht="64.5" customHeight="1" s="88">
+      <c r="A149" s="91" t="inlineStr">
+        <is>
+          <t>v037标准GLB</t>
+        </is>
+      </c>
+      <c r="B149" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C149" s="150" t="inlineStr">
+        <is>
+          <t>867b083e10aab5401489609c90c8efbb7621b3de910ab1bd9240a91e55b2720c</t>
+        </is>
+      </c>
+      <c r="D149" s="91" t="n">
         <v>1769716</v>
       </c>
     </row>
@@ -20410,7 +20730,7 @@
       </c>
       <c r="E6" s="162" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend；模型保持v021</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；模型保持v021</t>
         </is>
       </c>
       <c r="F6" s="162" t="inlineStr">
@@ -20460,12 +20780,12 @@
       </c>
       <c r="O6" s="163" t="inlineStr">
         <is>
-          <t>v033</t>
+          <t>v037</t>
         </is>
       </c>
       <c r="P6" s="164" t="inlineStr">
         <is>
-          <t>模型装配v021；动作v033；专项通过；其他长枪支撑差异、脚底锁地、蓄力近战待完善。assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+          <t>模型装配v021；动作v037；专项通过；其他长枪支撑差异、脚底锁地、蓄力近战待完善。assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
         </is>
       </c>
     </row>
@@ -21386,7 +21706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="87" min="1" max="1"/>
@@ -22153,6 +22473,154 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="60" customHeight="1" s="88">
+      <c r="A25" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.19</t>
+        </is>
+      </c>
+      <c r="B25" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C25" s="98" t="inlineStr">
+        <is>
+          <t>长枪机枪换弹枪体动态增强</t>
+        </is>
+      </c>
+      <c r="D25" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E25" s="98" t="inlineStr">
+        <is>
+          <t>v034动作库91条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F25" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；蓄力近战/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G25" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" s="88">
+      <c r="A26" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.20</t>
+        </is>
+      </c>
+      <c r="B26" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C26" s="98" t="inlineStr">
+        <is>
+          <t>机枪换弹顶视可读性修订</t>
+        </is>
+      </c>
+      <c r="D26" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E26" s="98" t="inlineStr">
+        <is>
+          <t>v035动作库91条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F26" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；蓄力近战/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G26" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1" s="88">
+      <c r="A27" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.21</t>
+        </is>
+      </c>
+      <c r="B27" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C27" s="98" t="inlineStr">
+        <is>
+          <t>机枪换弹45度近身修订</t>
+        </is>
+      </c>
+      <c r="D27" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E27" s="98" t="inlineStr">
+        <is>
+          <t>v036动作库91条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F27" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；蓄力近战/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G27" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" s="88">
+      <c r="A28" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.22</t>
+        </is>
+      </c>
+      <c r="B28" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C28" s="98" t="inlineStr">
+        <is>
+          <t>机枪换弹左前斜向枪口上抬</t>
+        </is>
+      </c>
+      <c r="D28" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E28" s="98" t="inlineStr">
+        <is>
+          <t>v037动作库91条；保持v021模型装配和碰撞；掌心挂点与源枪朝向。</t>
+        </is>
+      </c>
+      <c r="F28" s="98" t="inlineStr">
+        <is>
+          <t>专项通过；蓄力近战/逐枪支撑/锁地待完善。</t>
+        </is>
+      </c>
+      <c r="G28" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -2123,6 +2123,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -2715,7 +2716,7 @@
       </c>
       <c r="P6" s="105" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json</t>
         </is>
       </c>
       <c r="Q6" s="98" t="inlineStr">
@@ -3532,7 +3533,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3667,7 +3668,7 @@
       </c>
       <c r="P14" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q14" s="117" t="inlineStr">
@@ -3795,7 +3796,7 @@
       </c>
       <c r="P15" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q15" s="117" t="inlineStr">
@@ -3923,7 +3924,7 @@
       </c>
       <c r="P16" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q16" s="117" t="inlineStr">
@@ -4051,7 +4052,7 @@
       </c>
       <c r="P17" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q17" s="117" t="inlineStr">
@@ -4182,7 +4183,7 @@
       </c>
       <c r="P18" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q18" s="117" t="inlineStr">
@@ -4310,7 +4311,7 @@
       </c>
       <c r="P19" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q19" s="117" t="inlineStr">
@@ -4563,7 +4564,7 @@
       </c>
       <c r="P21" s="122" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q21" s="122" t="inlineStr">
@@ -6053,6 +6054,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -16897,6 +16899,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -17240,6 +17243,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="31.5" customHeight="1" s="88">
       <c r="A15" s="107" t="inlineStr">
         <is>
@@ -17450,6 +17454,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="88">
       <c r="A21" s="141" t="inlineStr">
         <is>
@@ -17457,6 +17462,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="88">
       <c r="A23" s="142" t="inlineStr">
         <is>
@@ -17485,6 +17491,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="33.75" customHeight="1" s="88">
       <c r="A28" s="145" t="inlineStr">
         <is>
@@ -17607,7 +17614,7 @@
       </c>
       <c r="B5" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend</t>
         </is>
       </c>
       <c r="C5" s="150" t="inlineStr">
@@ -17867,7 +17874,7 @@
       </c>
       <c r="B18" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v002.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v002.blend</t>
         </is>
       </c>
       <c r="C18" s="150" t="inlineStr">
@@ -17887,7 +17894,7 @@
       </c>
       <c r="B19" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v002.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v002.blend</t>
         </is>
       </c>
       <c r="C19" s="150" t="inlineStr">
@@ -18007,7 +18014,7 @@
       </c>
       <c r="B25" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v003.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v003.blend</t>
         </is>
       </c>
       <c r="C25" s="150" t="inlineStr">
@@ -18027,7 +18034,7 @@
       </c>
       <c r="B26" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v003.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v003.blend</t>
         </is>
       </c>
       <c r="C26" s="150" t="inlineStr">
@@ -18547,7 +18554,7 @@
       </c>
       <c r="B52" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v004.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v004.blend</t>
         </is>
       </c>
       <c r="C52" s="150" t="inlineStr">
@@ -18567,7 +18574,7 @@
       </c>
       <c r="B53" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v004.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v004.blend</t>
         </is>
       </c>
       <c r="C53" s="150" t="inlineStr">
@@ -19627,7 +19634,7 @@
       </c>
       <c r="B106" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
         </is>
       </c>
       <c r="C106" s="150" t="inlineStr">
@@ -19667,7 +19674,7 @@
       </c>
       <c r="B108" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend</t>
         </is>
       </c>
       <c r="C108" s="150" t="inlineStr">
@@ -19707,7 +19714,7 @@
       </c>
       <c r="B110" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend</t>
         </is>
       </c>
       <c r="C110" s="150" t="inlineStr">
@@ -19747,7 +19754,7 @@
       </c>
       <c r="B112" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend</t>
         </is>
       </c>
       <c r="C112" s="150" t="inlineStr">
@@ -19787,7 +19794,7 @@
       </c>
       <c r="B114" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend</t>
         </is>
       </c>
       <c r="C114" s="150" t="inlineStr">
@@ -19867,7 +19874,7 @@
       </c>
       <c r="B118" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend</t>
         </is>
       </c>
       <c r="C118" s="150" t="inlineStr">
@@ -19947,7 +19954,7 @@
       </c>
       <c r="B122" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend</t>
         </is>
       </c>
       <c r="C122" s="150" t="inlineStr">
@@ -20027,7 +20034,7 @@
       </c>
       <c r="B126" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend</t>
         </is>
       </c>
       <c r="C126" s="150" t="inlineStr">
@@ -20107,7 +20114,7 @@
       </c>
       <c r="B130" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend</t>
         </is>
       </c>
       <c r="C130" s="150" t="inlineStr">
@@ -20187,7 +20194,7 @@
       </c>
       <c r="B134" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend</t>
         </is>
       </c>
       <c r="C134" s="150" t="inlineStr">
@@ -20267,7 +20274,7 @@
       </c>
       <c r="B138" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend</t>
         </is>
       </c>
       <c r="C138" s="150" t="inlineStr">
@@ -20347,7 +20354,7 @@
       </c>
       <c r="B142" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend</t>
         </is>
       </c>
       <c r="C142" s="150" t="inlineStr">
@@ -21733,6 +21740,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -2123,7 +2123,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -3686,7 +3685,7 @@
       </c>
       <c r="T14" s="116" t="inlineStr">
         <is>
-          <t>861c7d454e510d7d50c0459dc9fa5b052af56c473896333a68ab6940ae981b49</t>
+          <t>120a25fd63abc29f5e9e04f13b207b86c77207abca6cb8a82c120177535dd45b</t>
         </is>
       </c>
       <c r="U14" s="116" t="inlineStr">
@@ -3814,7 +3813,7 @@
       </c>
       <c r="T15" s="116" t="inlineStr">
         <is>
-          <t>f654754b8a52cbd173597bd5f1e390a900bd0c2b0ed4ba357a8060542d51fda5</t>
+          <t>ff6d106a59068101e87692a73818f0cf0bf94319732d9bbda366f2febe5aaca9</t>
         </is>
       </c>
       <c r="U15" s="116" t="inlineStr">
@@ -4201,7 +4200,7 @@
       </c>
       <c r="T18" s="116" t="inlineStr">
         <is>
-          <t>60617a88b9659d9c4dba5884ed68314ff1e503a80df0ff5b35d63f8578b6b60a</t>
+          <t>055de14fc0840b5e218b0db8f26b496bc080cede6a43bf131a9bed9cf163ac9e</t>
         </is>
       </c>
       <c r="U18" s="116" t="inlineStr">
@@ -4329,7 +4328,7 @@
       </c>
       <c r="T19" s="116" t="inlineStr">
         <is>
-          <t>8509a8e959a7d427b4ee168d8585fb2d09ca01cbbf8c83601d8d5c46fe22e7a7</t>
+          <t>bf9ddff69d423f1beb60c84d091bf6c86bfdf01a85a0a517202faaf635338813</t>
         </is>
       </c>
       <c r="U19" s="116" t="inlineStr">
@@ -17639,7 +17638,7 @@
       </c>
       <c r="C6" s="150" t="inlineStr">
         <is>
-          <t>ded83dc49be4790aec4f6164f9de8b82dde125700a5eea5f323512f0f181bd0f</t>
+          <t>8229c948a6930ca5ef20f8b57162f2cf79c112a4822d6ce0a3f8e432f4ff5406</t>
         </is>
       </c>
       <c r="D6" s="91" t="n">
@@ -17699,7 +17698,7 @@
       </c>
       <c r="C9" s="150" t="inlineStr">
         <is>
-          <t>861c7d454e510d7d50c0459dc9fa5b052af56c473896333a68ab6940ae981b49</t>
+          <t>120a25fd63abc29f5e9e04f13b207b86c77207abca6cb8a82c120177535dd45b</t>
         </is>
       </c>
       <c r="D9" s="91" t="n">
@@ -17719,7 +17718,7 @@
       </c>
       <c r="C10" s="150" t="inlineStr">
         <is>
-          <t>f654754b8a52cbd173597bd5f1e390a900bd0c2b0ed4ba357a8060542d51fda5</t>
+          <t>ff6d106a59068101e87692a73818f0cf0bf94319732d9bbda366f2febe5aaca9</t>
         </is>
       </c>
       <c r="D10" s="91" t="n">
@@ -17739,7 +17738,7 @@
       </c>
       <c r="C11" s="150" t="inlineStr">
         <is>
-          <t>d83d016304df67eeff0f1222e3f4be19baef05437e7cbdca6f60a4842b26f5ec</t>
+          <t>e887924d711e490453e0fa51bd0589a4b95ffb1a03be0102ddffc5b3da55c7ed</t>
         </is>
       </c>
       <c r="D11" s="91" t="n">
@@ -17799,7 +17798,7 @@
       </c>
       <c r="C14" s="150" t="inlineStr">
         <is>
-          <t>60617a88b9659d9c4dba5884ed68314ff1e503a80df0ff5b35d63f8578b6b60a</t>
+          <t>055de14fc0840b5e218b0db8f26b496bc080cede6a43bf131a9bed9cf163ac9e</t>
         </is>
       </c>
       <c r="D14" s="91" t="n">
@@ -17819,7 +17818,7 @@
       </c>
       <c r="C15" s="150" t="inlineStr">
         <is>
-          <t>8509a8e959a7d427b4ee168d8585fb2d09ca01cbbf8c83601d8d5c46fe22e7a7</t>
+          <t>bf9ddff69d423f1beb60c84d091bf6c86bfdf01a85a0a517202faaf635338813</t>
         </is>
       </c>
       <c r="D15" s="91" t="n">
@@ -17839,7 +17838,7 @@
       </c>
       <c r="C16" s="150" t="inlineStr">
         <is>
-          <t>0936a7e3212554eddf48af62704649b6a6c98a67b56b180ed2e802bc97a1fc7c</t>
+          <t>c7dc667575d0fab32e8c66f489e7c9994798caa50ddcccf30d56c00fcaac5acf</t>
         </is>
       </c>
       <c r="D16" s="91" t="n">
@@ -17859,7 +17858,7 @@
       </c>
       <c r="C17" s="150" t="inlineStr">
         <is>
-          <t>7719ba73dec977951da3edf997752ba5afcf4a1c9f8b2bc8dd5ad8a78381b208</t>
+          <t>66ab8722d31333344f66c44abd132217e71d47a8ed23fa15832fdf01d0bad266</t>
         </is>
       </c>
       <c r="D17" s="91" t="n">
@@ -21740,7 +21739,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -2123,6 +2123,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -2715,7 +2716,7 @@
       </c>
       <c r="P6" s="105" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json</t>
         </is>
       </c>
       <c r="Q6" s="98" t="inlineStr">
@@ -3532,7 +3533,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3667,7 +3668,7 @@
       </c>
       <c r="P14" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q14" s="117" t="inlineStr">
@@ -3709,7 +3710,7 @@
       <c r="Y14" s="116" t="inlineStr">
         <is>
           <t>v0.1 v006：身体网格与底部中心原点保持不变；BodyJoint新增LowerBodySocket local=(0,0.14,0)，用于裙摆/腰甲/下摆并继承全部身体程序动画。
-2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
+2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
 2026-09-09：双Blend共享骨架 v009；新导出分件骨局部原点，八态Blender动作库接入；玩法层级/碰撞不变。
 2026-09-09：v010 腰胸/上下臂/指链/大小腿新骨架，模型未改；待机、移动、持枪待机、持枪移动重新制作并接入。用户要求跳过验收，未验证；其他状态沿用v009。
 2026-09-10：v011 +Y到Godot -Z统一朝向；原位直链绑定、腰胸归位、四基础动作无骨链拉伸。验收结果见中转JSON。
@@ -3795,7 +3796,7 @@
       </c>
       <c r="P15" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q15" s="117" t="inlineStr">
@@ -3837,7 +3838,7 @@
       <c r="Y15" s="116" t="inlineStr">
         <is>
           <t>v0.1 v006：头部与下沿中心原点真实1.5倍；不含耳头顶1.103390m，完整双耳顶部1.500m。
-2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
+2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
 2026-09-09：双Blend共享骨架 v009；新导出分件骨局部原点，八态Blender动作库接入；玩法层级/碰撞不变。
 2026-09-09：v010 腰胸/上下臂/指链/大小腿新骨架，模型未改；待机、移动、持枪待机、持枪移动重新制作并接入。用户要求跳过验收，未验证；其他状态沿用v009。
 2026-09-10：v011 +Y到Godot -Z统一朝向；原位直链绑定、腰胸归位、四基础动作无骨链拉伸。验收结果见中转JSON。
@@ -3923,7 +3924,7 @@
       </c>
       <c r="P16" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q16" s="117" t="inlineStr">
@@ -3965,7 +3966,7 @@
       <c r="Y16" s="116" t="inlineStr">
         <is>
           <t>v0.1 v006：耳朵网格与耳根原点真实1.5倍；左右挂点复用单资产，装配后最高点严格1.500m。
-2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
+2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
 2026-09-09：双Blend共享骨架 v009；新导出分件骨局部原点，八态Blender动作库接入；玩法层级/碰撞不变。
 2026-09-09：v010 腰胸/上下臂/指链/大小腿新骨架，模型未改；待机、移动、持枪待机、持枪移动重新制作并接入。用户要求跳过验收，未验证；其他状态沿用v009。
 2026-09-10：v011 +Y到Godot -Z统一朝向；原位直链绑定、腰胸归位、四基础动作无骨链拉伸。验收结果见中转JSON。
@@ -4051,7 +4052,7 @@
       </c>
       <c r="P17" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q17" s="117" t="inlineStr">
@@ -4096,7 +4097,7 @@
 2026-08-21：右手收紧到GripSocket；手枪待机自由左手前伸胸前，枪口下俯并向角色外侧偏转，正面与三分之四近景保持面部净空。
 2026-08-21：HandJointR/Model使用局部枢轴校正(-0.135996,0.038999,0.018441)，持枪状态每帧按真实GripSocket换算到HandRoot局部空间，三点偏差0mm。
 2026-08-21：右手掌球仍与HandJointR/GripSocket保持0mm；吹风机Prefab另将可见握把中心校正到该同一坐标，未改角色GLB。
-2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v006.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v007.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
+2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v006.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v007.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
 2026-09-09：双Blend共享骨架 v009；新导出分件骨局部原点，八态Blender动作库接入；玩法层级/碰撞不变。
 2026-09-09：v010 腰胸/上下臂/指链/大小腿新骨架，模型未改；待机、移动、持枪待机、持枪移动重新制作并接入。用户要求跳过验收，未验证；其他状态沿用v009。
 2026-09-10：v011 +Y到Godot -Z统一朝向；原位直链绑定、腰胸归位、四基础动作无骨链拉伸。验收结果见中转JSON。
@@ -4182,7 +4183,7 @@
       </c>
       <c r="P18" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q18" s="117" t="inlineStr">
@@ -4224,7 +4225,7 @@
       <c r="Y18" s="116" t="inlineStr">
         <is>
           <t>v0.1：v006网格与AssetID不变；FootJointL除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。
-2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
+2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
 2026-09-09：双Blend共享骨架 v009；新导出分件骨局部原点，八态Blender动作库接入；玩法层级/碰撞不变。
 2026-09-09：v010 腰胸/上下臂/指链/大小腿新骨架，模型未改；待机、移动、持枪待机、持枪移动重新制作并接入。用户要求跳过验收，未验证；其他状态沿用v009。
 2026-09-10：v011 +Y到Godot -Z统一朝向；原位直链绑定、腰胸归位、四基础动作无骨链拉伸。验收结果见中转JSON。
@@ -4310,7 +4311,7 @@
       </c>
       <c r="P19" s="116" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q19" s="117" t="inlineStr">
@@ -4352,7 +4353,7 @@
       <c r="Y19" s="116" t="inlineStr">
         <is>
           <t>v0.1：v006网格与AssetID不变；FootJointR除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。
-2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
+2026-08-30 AST-04：Bunny v008 包装层实际消费 v007 组件；登记路径 assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v006.glb → assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v007.glb；稳定组件 AssetID 不变；源母版为 art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v008.blend；验收角色节点/尺寸/姿势/换装契约。
 2026-09-09：双Blend共享骨架 v009；新导出分件骨局部原点，八态Blender动作库接入；玩法层级/碰撞不变。
 2026-09-09：v010 腰胸/上下臂/指链/大小腿新骨架，模型未改；待机、移动、持枪待机、持枪移动重新制作并接入。用户要求跳过验收，未验证；其他状态沿用v009。
 2026-09-10：v011 +Y到Godot -Z统一朝向；原位直链绑定、腰胸归位、四基础动作无骨链拉伸。验收结果见中转JSON。
@@ -4433,7 +4434,7 @@
       </c>
       <c r="O20" s="120" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_avatar_template_3d/source/chr_player_avatar_template_source_v001.blend</t>
+          <t>art_source/characters/player/chr_player_avatar_template_3d/source/chr_player_avatar_template_source_v001.blend</t>
         </is>
       </c>
       <c r="P20" s="120" t="inlineStr">
@@ -4563,7 +4564,7 @@
       </c>
       <c r="P21" s="122" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json</t>
         </is>
       </c>
       <c r="Q21" s="122" t="inlineStr">
@@ -12129,7 +12130,7 @@
       </c>
       <c r="L61" s="127" t="inlineStr">
         <is>
-          <t>v037 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；3.20秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12192,7 @@
       </c>
       <c r="L62" s="127" t="inlineStr">
         <is>
-          <t>v037 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；3.60秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12253,7 +12254,7 @@
       </c>
       <c r="L63" s="127" t="inlineStr">
         <is>
-          <t>v037 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；4.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12315,7 +12316,7 @@
       </c>
       <c r="L64" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12378,7 @@
       </c>
       <c r="L65" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12439,7 +12440,7 @@
       </c>
       <c r="L66" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12501,7 +12502,7 @@
       </c>
       <c r="L67" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12563,7 +12564,7 @@
       </c>
       <c r="L68" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12626,7 @@
       </c>
       <c r="L69" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12688,7 @@
       </c>
       <c r="L70" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12750,7 @@
       </c>
       <c r="L71" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12811,7 +12812,7 @@
       </c>
       <c r="L72" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12874,7 @@
       </c>
       <c r="L73" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12935,7 +12936,7 @@
       </c>
       <c r="L74" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12998,7 @@
       </c>
       <c r="L75" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13060,7 @@
       </c>
       <c r="L76" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13122,7 @@
       </c>
       <c r="L77" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13184,7 @@
       </c>
       <c r="L78" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13245,7 +13246,7 @@
       </c>
       <c r="L79" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13308,7 @@
       </c>
       <c r="L80" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13370,7 @@
       </c>
       <c r="L81" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13432,7 @@
       </c>
       <c r="L82" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13493,7 +13494,7 @@
       </c>
       <c r="L83" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13556,7 @@
       </c>
       <c r="L84" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13618,7 @@
       </c>
       <c r="L85" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13679,7 +13680,7 @@
       </c>
       <c r="L86" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13741,7 +13742,7 @@
       </c>
       <c r="L87" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13804,7 @@
       </c>
       <c r="L88" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13865,7 +13866,7 @@
       </c>
       <c r="L89" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13928,7 @@
       </c>
       <c r="L90" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -13989,7 +13990,7 @@
       </c>
       <c r="L91" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14052,7 @@
       </c>
       <c r="L92" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14114,7 @@
       </c>
       <c r="L93" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14175,7 +14176,7 @@
       </c>
       <c r="L94" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14237,7 +14238,7 @@
       </c>
       <c r="L95" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14299,7 +14300,7 @@
       </c>
       <c r="L96" s="127" t="inlineStr">
         <is>
-          <t>v037 active；3.20秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；3.20秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14362,7 @@
       </c>
       <c r="L97" s="127" t="inlineStr">
         <is>
-          <t>v037 active；3.60秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；3.60秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14423,7 +14424,7 @@
       </c>
       <c r="L98" s="127" t="inlineStr">
         <is>
-          <t>v037 active；4.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；4.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14485,7 +14486,7 @@
       </c>
       <c r="L99" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14548,7 @@
       </c>
       <c r="L100" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14610,7 @@
       </c>
       <c r="L101" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14671,7 +14672,7 @@
       </c>
       <c r="L102" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14733,7 +14734,7 @@
       </c>
       <c r="L103" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14795,7 +14796,7 @@
       </c>
       <c r="L104" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14858,7 @@
       </c>
       <c r="L105" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14919,7 +14920,7 @@
       </c>
       <c r="L106" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -14981,7 +14982,7 @@
       </c>
       <c r="L107" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15043,7 +15044,7 @@
       </c>
       <c r="L108" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15106,7 @@
       </c>
       <c r="L109" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15168,7 @@
       </c>
       <c r="L110" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15230,7 @@
       </c>
       <c r="L111" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15291,7 +15292,7 @@
       </c>
       <c r="L112" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15354,7 @@
       </c>
       <c r="L113" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15416,7 @@
       </c>
       <c r="L114" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15478,7 @@
       </c>
       <c r="L115" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15539,7 +15540,7 @@
       </c>
       <c r="L116" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15602,7 @@
       </c>
       <c r="L117" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15663,7 +15664,7 @@
       </c>
       <c r="L118" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15726,7 @@
       </c>
       <c r="L119" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15787,7 +15788,7 @@
       </c>
       <c r="L120" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15850,7 @@
       </c>
       <c r="L121" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15912,7 @@
       </c>
       <c r="L122" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -15973,7 +15974,7 @@
       </c>
       <c r="L123" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16035,7 +16036,7 @@
       </c>
       <c r="L124" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16098,7 @@
       </c>
       <c r="L125" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16160,7 @@
       </c>
       <c r="L126" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16222,7 @@
       </c>
       <c r="L127" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16284,7 @@
       </c>
       <c r="L128" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16345,7 +16346,7 @@
       </c>
       <c r="L129" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16407,7 +16408,7 @@
       </c>
       <c r="L130" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16469,7 +16470,7 @@
       </c>
       <c r="L131" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16531,7 +16532,7 @@
       </c>
       <c r="L132" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16593,7 +16594,7 @@
       </c>
       <c r="L133" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16655,7 +16656,7 @@
       </c>
       <c r="L134" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；0.45秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16717,7 +16718,7 @@
       </c>
       <c r="L135" s="127" t="inlineStr">
         <is>
-          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16779,7 +16780,7 @@
       </c>
       <c r="L136" s="127" t="inlineStr">
         <is>
-          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16842,7 @@
       </c>
       <c r="L137" s="127" t="inlineStr">
         <is>
-          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
         </is>
       </c>
     </row>
@@ -17593,7 +17594,7 @@
       </c>
       <c r="B4" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend</t>
         </is>
       </c>
       <c r="C4" s="150" t="inlineStr">
@@ -17613,7 +17614,7 @@
       </c>
       <c r="B5" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend</t>
         </is>
       </c>
       <c r="C5" s="150" t="inlineStr">
@@ -17873,7 +17874,7 @@
       </c>
       <c r="B18" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v002.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v002.blend</t>
         </is>
       </c>
       <c r="C18" s="150" t="inlineStr">
@@ -17893,7 +17894,7 @@
       </c>
       <c r="B19" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v002.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v002.blend</t>
         </is>
       </c>
       <c r="C19" s="150" t="inlineStr">
@@ -18013,7 +18014,7 @@
       </c>
       <c r="B25" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v003.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v003.blend</t>
         </is>
       </c>
       <c r="C25" s="150" t="inlineStr">
@@ -18033,7 +18034,7 @@
       </c>
       <c r="B26" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v003.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v003.blend</t>
         </is>
       </c>
       <c r="C26" s="150" t="inlineStr">
@@ -18553,7 +18554,7 @@
       </c>
       <c r="B52" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v004.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v004.blend</t>
         </is>
       </c>
       <c r="C52" s="150" t="inlineStr">
@@ -18573,7 +18574,7 @@
       </c>
       <c r="B53" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v004.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v004.blend</t>
         </is>
       </c>
       <c r="C53" s="150" t="inlineStr">
@@ -19093,7 +19094,7 @@
       </c>
       <c r="B79" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="C79" s="150" t="inlineStr">
@@ -19113,7 +19114,7 @@
       </c>
       <c r="B80" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_animation_v005.blend</t>
         </is>
       </c>
       <c r="C80" s="150" t="inlineStr">
@@ -19633,7 +19634,7 @@
       </c>
       <c r="B106" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend</t>
         </is>
       </c>
       <c r="C106" s="150" t="inlineStr">
@@ -19653,7 +19654,7 @@
       </c>
       <c r="B107" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json</t>
         </is>
       </c>
       <c r="C107" s="150" t="inlineStr">
@@ -19673,7 +19674,7 @@
       </c>
       <c r="B108" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend</t>
         </is>
       </c>
       <c r="C108" s="150" t="inlineStr">
@@ -19693,7 +19694,7 @@
       </c>
       <c r="B109" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json</t>
         </is>
       </c>
       <c r="C109" s="150" t="inlineStr">
@@ -19713,7 +19714,7 @@
       </c>
       <c r="B110" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend</t>
         </is>
       </c>
       <c r="C110" s="150" t="inlineStr">
@@ -19733,7 +19734,7 @@
       </c>
       <c r="B111" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json</t>
         </is>
       </c>
       <c r="C111" s="150" t="inlineStr">
@@ -19753,7 +19754,7 @@
       </c>
       <c r="B112" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend</t>
         </is>
       </c>
       <c r="C112" s="150" t="inlineStr">
@@ -19773,7 +19774,7 @@
       </c>
       <c r="B113" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json</t>
         </is>
       </c>
       <c r="C113" s="150" t="inlineStr">
@@ -19793,7 +19794,7 @@
       </c>
       <c r="B114" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend</t>
         </is>
       </c>
       <c r="C114" s="150" t="inlineStr">
@@ -19873,7 +19874,7 @@
       </c>
       <c r="B118" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend</t>
         </is>
       </c>
       <c r="C118" s="150" t="inlineStr">
@@ -19953,7 +19954,7 @@
       </c>
       <c r="B122" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend</t>
         </is>
       </c>
       <c r="C122" s="150" t="inlineStr">
@@ -20033,7 +20034,7 @@
       </c>
       <c r="B126" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend</t>
         </is>
       </c>
       <c r="C126" s="150" t="inlineStr">
@@ -20113,7 +20114,7 @@
       </c>
       <c r="B130" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend</t>
         </is>
       </c>
       <c r="C130" s="150" t="inlineStr">
@@ -20193,7 +20194,7 @@
       </c>
       <c r="B134" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend</t>
         </is>
       </c>
       <c r="C134" s="150" t="inlineStr">
@@ -20273,7 +20274,7 @@
       </c>
       <c r="B138" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend</t>
         </is>
       </c>
       <c r="C138" s="150" t="inlineStr">
@@ -20353,7 +20354,7 @@
       </c>
       <c r="B142" s="150" t="inlineStr">
         <is>
-          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend</t>
+          <t>../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend</t>
         </is>
       </c>
       <c r="C142" s="150" t="inlineStr">
@@ -20433,7 +20434,7 @@
       </c>
       <c r="B146" s="150" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend</t>
         </is>
       </c>
       <c r="C146" s="150" t="inlineStr">
@@ -20736,7 +20737,7 @@
       </c>
       <c r="E6" s="162" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；模型保持v021</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；模型保持v021</t>
         </is>
       </c>
       <c r="F6" s="162" t="inlineStr">
@@ -20884,7 +20885,7 @@
       <c r="D8" s="120" t="n"/>
       <c r="E8" s="120" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_avatar_template_3d/source/chr_player_avatar_template_source_v001.blend</t>
+          <t>art_source/characters/player/chr_player_avatar_template_3d/source/chr_player_avatar_template_source_v001.blend</t>
         </is>
       </c>
       <c r="F8" s="91" t="inlineStr">
@@ -20966,7 +20967,7 @@
       </c>
       <c r="E9" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F9" s="158" t="inlineStr">
@@ -21048,7 +21049,7 @@
       </c>
       <c r="E10" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F10" s="158" t="inlineStr">
@@ -21130,7 +21131,7 @@
       </c>
       <c r="E11" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F11" s="158" t="inlineStr">
@@ -21212,7 +21213,7 @@
       </c>
       <c r="E12" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F12" s="158" t="inlineStr">
@@ -21294,7 +21295,7 @@
       </c>
       <c r="E13" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F13" s="158" t="inlineStr">
@@ -21376,7 +21377,7 @@
       </c>
       <c r="E14" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F14" s="158" t="inlineStr">
@@ -21458,7 +21459,7 @@
       </c>
       <c r="E15" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F15" s="158" t="inlineStr">
@@ -21540,7 +21541,7 @@
       </c>
       <c r="E16" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F16" s="158" t="inlineStr">
@@ -21622,7 +21623,7 @@
       </c>
       <c r="E17" s="159" t="inlineStr">
         <is>
-          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/components/face/electronic_mask/source/chr_bunny01_electronic_mask_model_v005.blend</t>
         </is>
       </c>
       <c r="F17" s="158" t="inlineStr">
@@ -21739,6 +21740,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -2123,7 +2123,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -3498,7 +3497,7 @@
       </c>
       <c r="I13" s="116" t="inlineStr">
         <is>
-          <t>10 existing states / 3 family reload overlays / gameplay progress sampling</t>
+          <t>10 existing states / 56 directional loops / 7 expressive idles / reload and switch overlays</t>
         </is>
       </c>
       <c r="J13" s="116" t="inlineStr">
@@ -3518,7 +3517,7 @@
       </c>
       <c r="M13" s="116" t="inlineStr">
         <is>
-          <t>v037</t>
+          <t>v039</t>
         </is>
       </c>
       <c r="N13" s="117" t="inlineStr">
@@ -3533,7 +3532,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3551,7 +3550,7 @@
       </c>
       <c r="T13" s="116" t="inlineStr">
         <is>
-          <t>6924b230d48d0e70404dedc91a23e2c21ea5074707d9a1690fa3c2242e6c348c</t>
+          <t>5db5eb5a1e03d9e0f3fee9dc595509f86b0e15d2c7e5664d2241521b5b5104cb</t>
         </is>
       </c>
       <c r="U13" s="116" t="inlineStr">
@@ -3560,7 +3559,7 @@
         </is>
       </c>
       <c r="V13" s="118" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="W13" s="119" t="inlineStr">
         <is>
@@ -3586,7 +3585,7 @@
 2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。
 2026-09-29：v021 模型及原12动作保持不变；新增 v022 Blender 坐姿滑行循环 seated，Player3D 九态状态机与 99F 两把可驾驶椅接入；verify_pushable_base_chairs 通过。
 2026-09-29：v023 Blender 坐姿源将双脚向座面前方伸出；角色乘坐时可正常射击，相机补偿座面抬升，离座恢复世界碰撞。
-2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。；v033新增三类独立换弹，按WeaponModel3D真实progress同步播放；保留88条原剪辑。0.4/1.5/4秒、移动/取消/换槽打断专项174检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v033.md。；v034增强长枪机枪换弹枪体抬起、倾斜、沉降回弹与压紧回位；短枪及其余89条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项178检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v034.md。；v035机枪枪口转向前下方并抬高枪尾换弹操作位；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项184检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v035.md。；v036机枪枪口向前下方约45度，握点不前伸，近身抬高枪尾换弹；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v036.md。；v037机枪顶视斜向左前45度、枪口上抬；握点近身不前伸；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v037.md。</t>
+2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。；v033新增三类独立换弹，按WeaponModel3D真实progress同步播放；保留88条原剪辑。0.4/1.5/4秒、移动/取消/换槽打断专项174检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v033.md。；v034增强长枪机枪换弹枪体抬起、倾斜、沉降回弹与压紧回位；短枪及其余89条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项178检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v034.md。；v035机枪枪口转向前下方并抬高枪尾换弹操作位；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项184检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v035.md。；v036机枪枪口向前下方约45度，握点不前伸，近身抬高枪尾换弹；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v036.md。；v037机枪顶视斜向左前45度、枪口上抬；握点近身不前伸；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v037.md。；2026-10-15 v039：63条四方向慢走/跑步/移动射击及7待机增强头部起伏与躯干扭转；双手随动、射击稳枪。28条非目标剪辑保持，下肢/根差异&lt;0.000001；源63条及15项导入/运行/真实渲染检查通过。完整项目与移动端未验，历史头像哈希/命名债务另列。</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6053,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -9335,27 +9333,27 @@
       </c>
       <c r="F6" s="128" t="inlineStr">
         <is>
-          <t>v021：纯Blender 3.2秒循环待机；持枪使用armed_idle，禁用玩家程序姿势。</t>
+          <t>v039：无枪idle源2.4秒；三枪型使用独立sidearm_idle/longgun_idle/machinegun_idle；全局1.25倍率。</t>
         </is>
       </c>
       <c r="G6" s="127" t="inlineStr">
         <is>
-          <t>刚性头部，不缩放；低幅反向滞后保持重量感。</t>
+          <t>头部起伏与延迟跟随，耳部错相摆动；不缩放头部。</t>
         </is>
       </c>
       <c r="H6" s="127" t="inlineStr">
         <is>
-          <t>手枪自由左手前伸胸前警戒；长枪左手保持托举</t>
+          <t>双手随源躯干扭转；单手短枪及双手长枪/机枪分别制作。</t>
         </is>
       </c>
       <c r="I6" s="127" t="inlineStr">
         <is>
-          <t>手枪/长枪右手掌球中心、HandJointR与GripSocket三点重合；手枪WeaponSocket待机右前下移，枪管local -Z保持瞄准同向</t>
+          <t>右掌对齐源WeaponSocket，支撑手同枪体随动；射击使用独立稳枪动作，不启用程序手部覆盖。</t>
         </is>
       </c>
       <c r="J6" s="127" t="inlineStr">
         <is>
-          <t>低频错相轻摆</t>
+          <t>脚部支撑保持；身体重心转移与竖轴扭转。</t>
         </is>
       </c>
       <c r="K6" s="128" t="inlineStr">
@@ -9365,7 +9363,7 @@
       </c>
       <c r="L6" s="127" t="inlineStr">
         <is>
-          <t>八态StateMachine的idle唯一驱动；sidearm_hold保持低位警戒与面部净空，但取消整枪俯仰/偏航/侧滚；右手刚性追随GripSocket且掌球中心0mm对齐，左手前伸但不计第二握持。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11125,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44" ht="12.65" customHeight="1" s="88">
       <c r="A44" s="122" t="inlineStr">
         <is>
@@ -12130,7 +12127,7 @@
       </c>
       <c r="L61" s="127" t="inlineStr">
         <is>
-          <t>v037 active；3.20秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12189,7 @@
       </c>
       <c r="L62" s="127" t="inlineStr">
         <is>
-          <t>v037 active；3.60秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12251,7 @@
       </c>
       <c r="L63" s="127" t="inlineStr">
         <is>
-          <t>v037 active；4.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12313,7 @@
       </c>
       <c r="L64" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12375,7 @@
       </c>
       <c r="L65" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12437,7 @@
       </c>
       <c r="L66" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12499,7 @@
       </c>
       <c r="L67" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12561,7 @@
       </c>
       <c r="L68" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12623,7 @@
       </c>
       <c r="L69" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12685,7 @@
       </c>
       <c r="L70" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12747,7 @@
       </c>
       <c r="L71" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12809,7 @@
       </c>
       <c r="L72" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12871,7 @@
       </c>
       <c r="L73" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12933,7 @@
       </c>
       <c r="L74" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12995,7 @@
       </c>
       <c r="L75" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13057,7 @@
       </c>
       <c r="L76" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13119,7 @@
       </c>
       <c r="L77" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13181,7 @@
       </c>
       <c r="L78" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13243,7 @@
       </c>
       <c r="L79" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13305,7 @@
       </c>
       <c r="L80" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13367,7 @@
       </c>
       <c r="L81" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13429,7 @@
       </c>
       <c r="L82" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13491,7 @@
       </c>
       <c r="L83" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13553,7 @@
       </c>
       <c r="L84" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13615,7 @@
       </c>
       <c r="L85" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13677,7 @@
       </c>
       <c r="L86" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13739,7 @@
       </c>
       <c r="L87" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13801,7 @@
       </c>
       <c r="L88" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13863,7 @@
       </c>
       <c r="L89" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13925,7 @@
       </c>
       <c r="L90" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13987,7 @@
       </c>
       <c r="L91" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14049,7 @@
       </c>
       <c r="L92" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14111,7 @@
       </c>
       <c r="L93" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14173,7 @@
       </c>
       <c r="L94" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14235,7 @@
       </c>
       <c r="L95" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14297,7 @@
       </c>
       <c r="L96" s="127" t="inlineStr">
         <is>
-          <t>v037 active；3.20秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14359,7 @@
       </c>
       <c r="L97" s="127" t="inlineStr">
         <is>
-          <t>v037 active；3.60秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14421,7 @@
       </c>
       <c r="L98" s="127" t="inlineStr">
         <is>
-          <t>v037 active；4.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14483,7 @@
       </c>
       <c r="L99" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14545,7 @@
       </c>
       <c r="L100" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14607,7 @@
       </c>
       <c r="L101" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14669,7 @@
       </c>
       <c r="L102" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14731,7 @@
       </c>
       <c r="L103" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14793,7 @@
       </c>
       <c r="L104" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14855,7 @@
       </c>
       <c r="L105" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14917,7 @@
       </c>
       <c r="L106" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14979,7 @@
       </c>
       <c r="L107" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15041,7 @@
       </c>
       <c r="L108" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15103,7 @@
       </c>
       <c r="L109" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15165,7 @@
       </c>
       <c r="L110" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15227,7 @@
       </c>
       <c r="L111" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15289,7 @@
       </c>
       <c r="L112" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15351,7 @@
       </c>
       <c r="L113" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15413,7 @@
       </c>
       <c r="L114" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15475,7 @@
       </c>
       <c r="L115" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15537,7 @@
       </c>
       <c r="L116" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15599,7 @@
       </c>
       <c r="L117" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15661,7 @@
       </c>
       <c r="L118" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15726,7 +15723,7 @@
       </c>
       <c r="L119" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15785,7 @@
       </c>
       <c r="L120" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15847,7 @@
       </c>
       <c r="L121" s="127" t="inlineStr">
         <is>
-          <t>v037 active；1.00秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -15912,7 +15909,7 @@
       </c>
       <c r="L122" s="127" t="inlineStr">
         <is>
-          <t>v037 active；0.80秒循环；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+          <t>v039 active；头部起伏/前进前探/躯干竖轴扭转；移动射击保持枪口朝向。art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；63循环源检查及运行方向/待机/关联专项通过。</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16896,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -17243,7 +17239,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="31.5" customHeight="1" s="88">
       <c r="A15" s="107" t="inlineStr">
         <is>
@@ -17454,7 +17449,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="88">
       <c r="A21" s="141" t="inlineStr">
         <is>
@@ -17462,7 +17456,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="88">
       <c r="A23" s="142" t="inlineStr">
         <is>
@@ -17491,7 +17484,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="33.75" customHeight="1" s="88">
       <c r="A28" s="145" t="inlineStr">
         <is>
@@ -17531,7 +17523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.1" customWidth="1" style="87" min="1" max="1"/>
@@ -20504,6 +20496,86 @@
       </c>
       <c r="D149" s="91" t="n">
         <v>1769716</v>
+      </c>
+    </row>
+    <row r="150" ht="64.5" customHeight="1" s="88">
+      <c r="A150" s="91" t="inlineStr">
+        <is>
+          <t>v039动作源</t>
+        </is>
+      </c>
+      <c r="B150" s="150" t="inlineStr">
+        <is>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend</t>
+        </is>
+      </c>
+      <c r="C150" s="150" t="inlineStr">
+        <is>
+          <t>6062e0d92bdf4f79eb6981110c762cf5d9c4415b5dcf426d84254c3cc35e76ce</t>
+        </is>
+      </c>
+      <c r="D150" s="91" t="n">
+        <v>487698271</v>
+      </c>
+    </row>
+    <row r="151" ht="64.5" customHeight="1" s="88">
+      <c r="A151" s="91" t="inlineStr">
+        <is>
+          <t>v039正式中转</t>
+        </is>
+      </c>
+      <c r="B151" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C151" s="150" t="inlineStr">
+        <is>
+          <t>59f79d15ea62c03b17a0752a2671b27be7821040b5c27390ddd4b1b777287924</t>
+        </is>
+      </c>
+      <c r="D151" s="91" t="n">
+        <v>23673</v>
+      </c>
+    </row>
+    <row r="152" ht="64.5" customHeight="1" s="88">
+      <c r="A152" s="91" t="inlineStr">
+        <is>
+          <t>v039运行采样库</t>
+        </is>
+      </c>
+      <c r="B152" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C152" s="150" t="inlineStr">
+        <is>
+          <t>cb8ba5522f96e753a7e6cc93ee231c3354bd0e9f339a9933516483378dc08ed5</t>
+        </is>
+      </c>
+      <c r="D152" s="91" t="n">
+        <v>13891665</v>
+      </c>
+    </row>
+    <row r="153" ht="64.5" customHeight="1" s="88">
+      <c r="A153" s="91" t="inlineStr">
+        <is>
+          <t>v039标准GLB</t>
+        </is>
+      </c>
+      <c r="B153" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C153" s="150" t="inlineStr">
+        <is>
+          <t>b6be0a726966e69ef03df13e1bc6dc802fe1dabff129cf254082b33b174538a0</t>
+        </is>
+      </c>
+      <c r="D153" s="91" t="n">
+        <v>2426500</v>
       </c>
     </row>
   </sheetData>
@@ -20557,7 +20629,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="88">
       <c r="A4" s="153" t="inlineStr">
         <is>
@@ -20737,7 +20808,7 @@
       </c>
       <c r="E6" s="162" t="inlineStr">
         <is>
-          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；模型保持v021</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；模型保持v021</t>
         </is>
       </c>
       <c r="F6" s="162" t="inlineStr">
@@ -20787,12 +20858,12 @@
       </c>
       <c r="O6" s="163" t="inlineStr">
         <is>
-          <t>v037</t>
+          <t>v039</t>
         </is>
       </c>
       <c r="P6" s="164" t="inlineStr">
         <is>
-          <t>模型装配v021；动作v037；专项通过；其他长枪支撑差异、脚底锁地、蓄力近战待完善。assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+          <t>模型v021；动作v039，四方向跑步与7待机加强，保留全局1.25倍率。15项导入/角色专项/真实渲染通过；历史未完项不变。assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
         </is>
       </c>
     </row>
@@ -21713,7 +21784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="87" min="1" max="1"/>
@@ -21740,7 +21811,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -22624,6 +22694,43 @@
         </is>
       </c>
       <c r="G28" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1" s="88">
+      <c r="A29" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.24</t>
+        </is>
+      </c>
+      <c r="B29" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C29" s="98" t="inlineStr">
+        <is>
+          <t>跑步与待机加强 v039</t>
+        </is>
+      </c>
+      <c r="D29" s="98" t="inlineStr">
+        <is>
+          <t>角色 / Bunny01</t>
+        </is>
+      </c>
+      <c r="E29" s="98" t="inlineStr">
+        <is>
+          <t>63条动作起伏与扭转加强；三类移动射击稳枪；v021模型、91条总库保持。</t>
+        </is>
+      </c>
+      <c r="F29" s="98" t="inlineStr">
+        <is>
+          <t>源及角色专项通过；全工程/移动端未验。</t>
+        </is>
+      </c>
+      <c r="G29" s="98" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色中转记录" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="角色组件" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="动画与状态" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="原型角色" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="角色中转记录" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3D-角色" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="域变更日志" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$30</definedName>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T13" s="116" t="inlineStr">
         <is>
-          <t>5db5eb5a1e03d9e0f3fee9dc595509f86b0e15d2c7e5664d2241521b5b5104cb</t>
+          <t>ed60a72aea33e94b8535f3d80b5e89ba982415dbc2a54bd4ae2ab52a2c520e91</t>
         </is>
       </c>
       <c r="U13" s="116" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="T21" s="122" t="inlineStr">
         <is>
-          <t>09dac92ea794b1c42c9c4c1e23db83d3d057216f2ac11fa53624a6951bc1e284</t>
+          <t>7f01db18d3f93d33567589bdf93f3b966930df9221a571dea8cf99d0ca005d9c</t>
         </is>
       </c>
       <c r="U21" s="87" t="inlineStr">

--- a/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="角色组件" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="动画与状态" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="原型角色" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="角色中转记录" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="3D-角色" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="域变更日志" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色中转记录" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$30</definedName>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I13" s="116" t="inlineStr">
         <is>
-          <t>10 existing states / 56 directional loops / 7 expressive idles / reload and switch overlays</t>
+          <t>128 clips / 37 distinct melee actions / six melee phases</t>
         </is>
       </c>
       <c r="J13" s="116" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M13" s="116" t="inlineStr">
         <is>
-          <t>v039</t>
+          <t>v042</t>
         </is>
       </c>
       <c r="N13" s="117" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P13" s="116" t="inlineStr">
         <is>
-          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/model/chr_bunny01_model_v021.blend; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/source/animation/chr_bunny01_animation_v021.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v021/character_transfer_ledger_v021.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/source/animation/chr_bunny01_animation_v022.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v023/character_transfer_ledger_v022.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/source/animation/chr_bunny01_animation_v024.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/production/v024/character_transfer_ledger_v024.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v025.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v025.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v026.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_weapon_idles_v026.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v027.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v027.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v028.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_directional_v028.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v029.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v030.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v031.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v032.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v033.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v034.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v035.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; ../ShellStorm2-backup/2026-10-11_slimming/original_tree/art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v036.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/asset_manifest.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend; art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
         </is>
       </c>
       <c r="Q13" s="117" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T13" s="116" t="inlineStr">
         <is>
-          <t>ed60a72aea33e94b8535f3d80b5e89ba982415dbc2a54bd4ae2ab52a2c520e91</t>
+          <t>50861d4bc1ff5fc16ac2851288a4e4cbbb0018078aee848e63e570b0066c8306</t>
         </is>
       </c>
       <c r="U13" s="116" t="inlineStr">
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="V13" s="118" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="W13" s="119" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
 2026-09-10：v021 完整12动作库接入；八个玩法基础状态与慢走/单手持枪变体均来自新版Blender，body读取chest，右手使用掌心握点。仅替换表现层，碰撞与功能层级不变。
 2026-09-29：v021 模型及原12动作保持不变；新增 v022 Blender 坐姿滑行循环 seated，Player3D 九态状态机与 99F 两把可驾驶椅接入；verify_pushable_base_chairs 通过。
 2026-09-29：v023 Blender 坐姿源将双脚向座面前方伸出；角色乘坐时可正常射击，相机补偿座面抬升，离座恢复世界碰撞。
-2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。；v033新增三类独立换弹，按WeaponModel3D真实progress同步播放；保留88条原剪辑。0.4/1.5/4秒、移动/取消/换槽打断专项174检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v033.md。；v034增强长枪机枪换弹枪体抬起、倾斜、沉降回弹与压紧回位；短枪及其余89条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项178检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v034.md。；v035机枪枪口转向前下方并抬高枪尾换弹操作位；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项184检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v035.md。；v036机枪枪口向前下方约45度，握点不前伸，近身抬高枪尾换弹；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v036.md。；v037机枪顶视斜向左前45度、枪口上抬；握点近身不前伸；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v037.md。；2026-10-15 v039：63条四方向慢走/跑步/移动射击及7待机增强头部起伏与躯干扭转；双手随动、射击稳枪。28条非目标剪辑保持，下肢/根差异&lt;0.000001；源63条及15项导入/运行/真实渲染检查通过。完整项目与移动端未验，历史头像哈希/命名债务另列。</t>
+2026-09-29：v024原角色动画母版新增climbing交替手脚攀爬循环，映射到Player3D climbing状态。；2026-10-07新增v025站立持枪待机sidearm_idle/longgun_idle/machinegun_idle，源级authored，待导出接线；保留原14条动作、模型与骨架，四方向移动另待制作。运行路径/版本/状态保持，不代表新动作已启用。；v026按用户正侧参考调整短枪前上倾、三枪前移，握点同步；源级待导入，v025保留。；v027按v026持枪姿态新增三枪型×慢走/正常移动×左移/右移/后退18循环，源级authored，待导入；前进另待制作。；v028为v027的18移动循环补耳朵反方向拖曳/回弹，其余曲线保持，源级authored待导入。；v029正式接入35新剪辑并保留14旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、专用战斗动作待完善。见2026-10-07_player_motion_runtime_v029.md。；v030正式接入27举枪射击剪辑并保留49旧剪辑，机枪独立族、四方向/两速度、耳朵跟随、掌心与枪朝向采样。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_firing_v030.md。；v031正式接入18条长枪机枪斜持修订并保留58条其他剪辑，长枪机枪小幅斜持、机枪收近3.5cm创作尺寸；身体脚步耳朵、短枪和射击不变。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-07_player_motion_carry_v031.md。；v032修订4条无枪前后摆臂，新增12条三枪型双背槽收取枪；其余72条保持。1/2重复当前槽收枪、双枪背负，切换先收后取；弹药与实例保留。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、换弹蓄力近战待完善。见2026-10-08_player_motion_switch_v032.md。；v033新增三类独立换弹，按WeaponModel3D真实progress同步播放；保留88条原剪辑。0.4/1.5/4秒、移动/取消/换槽打断专项174检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v033.md。；v034增强长枪机枪换弹枪体抬起、倾斜、沉降回弹与压紧回位；短枪及其余89条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项178检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v034.md。；v035机枪枪口转向前下方并抬高枪尾换弹操作位；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项184检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v035.md。；v036机枪枪口向前下方约45度，握点不前伸，近身抬高枪尾换弹；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v036.md。；v037机枪顶视斜向左前45度、枪口上抬；握点近身不前伸；短枪、长枪及其余90条剪辑逐值保持，实际progress同步不变。0.4/1.5/4秒、移动/取消/换槽打断专项225检查通过；无新增弹匣物件。专项通过，命名/文档全局既有红项保留；其他长枪支撑差异和世界滑步、蓄力近战待完善。见2026-10-08_player_motion_reload_v037.md。；2026-10-15 v039：63条四方向慢走/跑步/移动射击及7待机增强头部起伏与躯干扭转；双手随动、射击稳枪。28条非目标剪辑保持，下肢/根差异&lt;0.000001；源63条及15项导入/运行/真实渲染检查通过。完整项目与移动端未验，历史头像哈希/命名债务另列。；v041：棍普通挥击、斧慢速下劈与蓄力击退、剑交替横扫与持续旋风。37段Blender近战动作、91条旧动作保真；专项与真实渲染通过，详见docs/v0.1/development/2026-10-16_melee_styles_v041.md；v042修正斧子握持：绕柄轴-90°，刃面进入下劈平面、银刃领先；14斧动作仅WeaponSocket旋转改变，其余114动作逐值不变；docs/v0.1/development/2026-10-17_axe_edge_v042.md</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.94" customWidth="1" style="87" min="1" max="1"/>
@@ -11125,6 +11125,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44" ht="12.65" customHeight="1" s="88">
       <c r="A44" s="122" t="inlineStr">
         <is>
@@ -16840,6 +16841,2300 @@
       <c r="L137" s="127" t="inlineStr">
         <is>
           <t>v037 active；2.00秒单次；CharacterMotionLibrary3D采样；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v037.blend；蓄力近战/锁地待完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="70" customHeight="1" s="88">
+      <c r="A138" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B138" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_1_active</t>
+        </is>
+      </c>
+      <c r="C138" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_1_active</t>
+        </is>
+      </c>
+      <c r="D138" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E138" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F138" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G138" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H138" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I138" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J138" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K138" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L138" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="70" customHeight="1" s="88">
+      <c r="A139" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B139" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_1_recovery</t>
+        </is>
+      </c>
+      <c r="C139" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_1_recovery</t>
+        </is>
+      </c>
+      <c r="D139" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E139" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F139" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G139" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H139" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I139" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J139" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K139" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L139" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="70" customHeight="1" s="88">
+      <c r="A140" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B140" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_1_windup</t>
+        </is>
+      </c>
+      <c r="C140" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_1_windup</t>
+        </is>
+      </c>
+      <c r="D140" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E140" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F140" s="128" t="inlineStr">
+        <is>
+          <t>0.48s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G140" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H140" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I140" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J140" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K140" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L140" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="70" customHeight="1" s="88">
+      <c r="A141" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B141" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_2_active</t>
+        </is>
+      </c>
+      <c r="C141" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_2_active</t>
+        </is>
+      </c>
+      <c r="D141" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E141" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F141" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G141" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H141" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I141" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J141" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K141" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L141" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="70" customHeight="1" s="88">
+      <c r="A142" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B142" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_2_recovery</t>
+        </is>
+      </c>
+      <c r="C142" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_2_recovery</t>
+        </is>
+      </c>
+      <c r="D142" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E142" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F142" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G142" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H142" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I142" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J142" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K142" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L142" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="70" customHeight="1" s="88">
+      <c r="A143" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B143" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_2_windup</t>
+        </is>
+      </c>
+      <c r="C143" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_2_windup</t>
+        </is>
+      </c>
+      <c r="D143" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E143" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F143" s="128" t="inlineStr">
+        <is>
+          <t>0.48s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G143" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H143" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I143" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J143" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K143" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L143" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="70" customHeight="1" s="88">
+      <c r="A144" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B144" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_3_active</t>
+        </is>
+      </c>
+      <c r="C144" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_3_active</t>
+        </is>
+      </c>
+      <c r="D144" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E144" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F144" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G144" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H144" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I144" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J144" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K144" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L144" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="70" customHeight="1" s="88">
+      <c r="A145" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B145" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_3_recovery</t>
+        </is>
+      </c>
+      <c r="C145" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_3_recovery</t>
+        </is>
+      </c>
+      <c r="D145" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E145" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F145" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G145" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H145" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I145" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J145" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K145" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L145" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="70" customHeight="1" s="88">
+      <c r="A146" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B146" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_3_windup</t>
+        </is>
+      </c>
+      <c r="C146" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_3_windup</t>
+        </is>
+      </c>
+      <c r="D146" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E146" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F146" s="128" t="inlineStr">
+        <is>
+          <t>0.48s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G146" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H146" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I146" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J146" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K146" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L146" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="70" customHeight="1" s="88">
+      <c r="A147" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B147" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_charge</t>
+        </is>
+      </c>
+      <c r="C147" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_charge</t>
+        </is>
+      </c>
+      <c r="D147" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E147" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F147" s="128" t="inlineStr">
+        <is>
+          <t>1.0s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G147" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H147" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I147" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J147" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K147" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L147" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="70" customHeight="1" s="88">
+      <c r="A148" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B148" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_charged_active</t>
+        </is>
+      </c>
+      <c r="C148" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_charged_active</t>
+        </is>
+      </c>
+      <c r="D148" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E148" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F148" s="128" t="inlineStr">
+        <is>
+          <t>0.18s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G148" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H148" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I148" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J148" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K148" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L148" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="70" customHeight="1" s="88">
+      <c r="A149" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B149" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_charged_recovery</t>
+        </is>
+      </c>
+      <c r="C149" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_charged_recovery</t>
+        </is>
+      </c>
+      <c r="D149" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E149" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F149" s="128" t="inlineStr">
+        <is>
+          <t>0.7s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G149" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H149" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I149" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J149" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K149" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L149" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="70" customHeight="1" s="88">
+      <c r="A150" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B150" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_charged_windup</t>
+        </is>
+      </c>
+      <c r="C150" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_charged_windup</t>
+        </is>
+      </c>
+      <c r="D150" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E150" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F150" s="128" t="inlineStr">
+        <is>
+          <t>0.08s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G150" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H150" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I150" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J150" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K150" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L150" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="70" customHeight="1" s="88">
+      <c r="A151" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B151" s="128" t="inlineStr">
+        <is>
+          <t>melee_axe_idle</t>
+        </is>
+      </c>
+      <c r="C151" s="127" t="inlineStr">
+        <is>
+          <t>melee_axe_idle</t>
+        </is>
+      </c>
+      <c r="D151" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E151" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F151" s="128" t="inlineStr">
+        <is>
+          <t>1.6s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G151" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H151" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I151" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J151" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K151" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L151" s="127" t="inlineStr">
+        <is>
+          <t>v042 active；源银刃-X/柄+Y，绕柄-90°使刃朝劈砍轨迹；接触拍刃朝下，双掌/阶段连续/真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="70" customHeight="1" s="88">
+      <c r="A152" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B152" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_1_active</t>
+        </is>
+      </c>
+      <c r="C152" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_1_active</t>
+        </is>
+      </c>
+      <c r="D152" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E152" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F152" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G152" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H152" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I152" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J152" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K152" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L152" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="70" customHeight="1" s="88">
+      <c r="A153" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B153" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_1_recovery</t>
+        </is>
+      </c>
+      <c r="C153" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_1_recovery</t>
+        </is>
+      </c>
+      <c r="D153" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E153" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F153" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G153" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H153" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I153" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J153" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K153" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L153" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="70" customHeight="1" s="88">
+      <c r="A154" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B154" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_1_windup</t>
+        </is>
+      </c>
+      <c r="C154" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_1_windup</t>
+        </is>
+      </c>
+      <c r="D154" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E154" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F154" s="128" t="inlineStr">
+        <is>
+          <t>0.2s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G154" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H154" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I154" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J154" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K154" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L154" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="70" customHeight="1" s="88">
+      <c r="A155" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B155" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_2_active</t>
+        </is>
+      </c>
+      <c r="C155" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_2_active</t>
+        </is>
+      </c>
+      <c r="D155" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E155" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F155" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G155" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H155" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I155" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J155" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K155" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L155" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="70" customHeight="1" s="88">
+      <c r="A156" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B156" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_2_recovery</t>
+        </is>
+      </c>
+      <c r="C156" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_2_recovery</t>
+        </is>
+      </c>
+      <c r="D156" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E156" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F156" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G156" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H156" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I156" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J156" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K156" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L156" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="70" customHeight="1" s="88">
+      <c r="A157" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B157" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_2_windup</t>
+        </is>
+      </c>
+      <c r="C157" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_2_windup</t>
+        </is>
+      </c>
+      <c r="D157" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E157" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F157" s="128" t="inlineStr">
+        <is>
+          <t>0.2s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G157" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H157" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I157" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J157" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K157" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L157" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="70" customHeight="1" s="88">
+      <c r="A158" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B158" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_3_active</t>
+        </is>
+      </c>
+      <c r="C158" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_3_active</t>
+        </is>
+      </c>
+      <c r="D158" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E158" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F158" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G158" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H158" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I158" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J158" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K158" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L158" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="70" customHeight="1" s="88">
+      <c r="A159" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B159" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_3_recovery</t>
+        </is>
+      </c>
+      <c r="C159" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_3_recovery</t>
+        </is>
+      </c>
+      <c r="D159" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E159" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F159" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G159" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H159" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I159" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J159" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K159" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L159" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="70" customHeight="1" s="88">
+      <c r="A160" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B160" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_3_windup</t>
+        </is>
+      </c>
+      <c r="C160" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_3_windup</t>
+        </is>
+      </c>
+      <c r="D160" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E160" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F160" s="128" t="inlineStr">
+        <is>
+          <t>0.2s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G160" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H160" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I160" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J160" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K160" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L160" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="70" customHeight="1" s="88">
+      <c r="A161" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B161" s="128" t="inlineStr">
+        <is>
+          <t>melee_bat_idle</t>
+        </is>
+      </c>
+      <c r="C161" s="127" t="inlineStr">
+        <is>
+          <t>melee_bat_idle</t>
+        </is>
+      </c>
+      <c r="D161" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E161" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F161" s="128" t="inlineStr">
+        <is>
+          <t>1.6s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G161" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H161" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I161" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J161" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K161" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L161" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="70" customHeight="1" s="88">
+      <c r="A162" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B162" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_1_active</t>
+        </is>
+      </c>
+      <c r="C162" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_1_active</t>
+        </is>
+      </c>
+      <c r="D162" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E162" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F162" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G162" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H162" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I162" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J162" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K162" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L162" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="70" customHeight="1" s="88">
+      <c r="A163" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B163" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_1_recovery</t>
+        </is>
+      </c>
+      <c r="C163" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_1_recovery</t>
+        </is>
+      </c>
+      <c r="D163" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E163" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F163" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G163" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H163" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I163" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J163" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K163" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L163" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="70" customHeight="1" s="88">
+      <c r="A164" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B164" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_1_windup</t>
+        </is>
+      </c>
+      <c r="C164" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_1_windup</t>
+        </is>
+      </c>
+      <c r="D164" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E164" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F164" s="128" t="inlineStr">
+        <is>
+          <t>0.2s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G164" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H164" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I164" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J164" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K164" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L164" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="70" customHeight="1" s="88">
+      <c r="A165" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B165" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_2_active</t>
+        </is>
+      </c>
+      <c r="C165" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_2_active</t>
+        </is>
+      </c>
+      <c r="D165" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E165" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F165" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G165" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H165" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I165" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J165" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K165" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L165" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="70" customHeight="1" s="88">
+      <c r="A166" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B166" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_2_recovery</t>
+        </is>
+      </c>
+      <c r="C166" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_2_recovery</t>
+        </is>
+      </c>
+      <c r="D166" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E166" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F166" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G166" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H166" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I166" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J166" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K166" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L166" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="70" customHeight="1" s="88">
+      <c r="A167" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B167" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_2_windup</t>
+        </is>
+      </c>
+      <c r="C167" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_2_windup</t>
+        </is>
+      </c>
+      <c r="D167" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E167" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F167" s="128" t="inlineStr">
+        <is>
+          <t>0.2s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G167" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H167" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I167" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J167" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K167" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L167" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="70" customHeight="1" s="88">
+      <c r="A168" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B168" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_3_active</t>
+        </is>
+      </c>
+      <c r="C168" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_3_active</t>
+        </is>
+      </c>
+      <c r="D168" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E168" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F168" s="128" t="inlineStr">
+        <is>
+          <t>0.14s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G168" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H168" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I168" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J168" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K168" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L168" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="70" customHeight="1" s="88">
+      <c r="A169" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B169" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_3_recovery</t>
+        </is>
+      </c>
+      <c r="C169" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_3_recovery</t>
+        </is>
+      </c>
+      <c r="D169" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E169" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F169" s="128" t="inlineStr">
+        <is>
+          <t>0.4s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G169" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H169" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I169" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J169" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K169" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L169" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="70" customHeight="1" s="88">
+      <c r="A170" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B170" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_3_windup</t>
+        </is>
+      </c>
+      <c r="C170" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_3_windup</t>
+        </is>
+      </c>
+      <c r="D170" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E170" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F170" s="128" t="inlineStr">
+        <is>
+          <t>0.2s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G170" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H170" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I170" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J170" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K170" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L170" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="70" customHeight="1" s="88">
+      <c r="A171" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B171" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_charge</t>
+        </is>
+      </c>
+      <c r="C171" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_charge</t>
+        </is>
+      </c>
+      <c r="D171" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E171" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F171" s="128" t="inlineStr">
+        <is>
+          <t>0.35s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G171" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H171" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I171" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J171" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K171" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L171" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="70" customHeight="1" s="88">
+      <c r="A172" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B172" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_idle</t>
+        </is>
+      </c>
+      <c r="C172" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_idle</t>
+        </is>
+      </c>
+      <c r="D172" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E172" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F172" s="128" t="inlineStr">
+        <is>
+          <t>1.6s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G172" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H172" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I172" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J172" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K172" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L172" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="70" customHeight="1" s="88">
+      <c r="A173" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B173" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_spin</t>
+        </is>
+      </c>
+      <c r="C173" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_spin</t>
+        </is>
+      </c>
+      <c r="D173" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E173" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F173" s="128" t="inlineStr">
+        <is>
+          <t>0.55s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G173" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H173" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I173" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J173" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K173" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L173" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="70" customHeight="1" s="88">
+      <c r="A174" s="127" t="inlineStr">
+        <is>
+          <t>近战表现（非移动顶层状态）</t>
+        </is>
+      </c>
+      <c r="B174" s="128" t="inlineStr">
+        <is>
+          <t>melee_blade_spin_recovery</t>
+        </is>
+      </c>
+      <c r="C174" s="127" t="inlineStr">
+        <is>
+          <t>melee_blade_spin_recovery</t>
+        </is>
+      </c>
+      <c r="D174" s="128" t="inlineStr">
+        <is>
+          <t>PlayerMeleeCombat3D phase/attack_mode/spin_progress</t>
+        </is>
+      </c>
+      <c r="E174" s="128" t="inlineStr">
+        <is>
+          <t>玩法状态机</t>
+        </is>
+      </c>
+      <c r="F174" s="128" t="inlineStr">
+        <is>
+          <t>0.3s；按真实进度采样</t>
+        </is>
+      </c>
+      <c r="G174" s="127" t="inlineStr">
+        <is>
+          <t>躯干发力、头部跟随；旋风整身转圈</t>
+        </is>
+      </c>
+      <c r="H174" s="127" t="inlineStr">
+        <is>
+          <t>左掌距握点0.18m</t>
+        </is>
+      </c>
+      <c r="I174" s="127" t="inlineStr">
+        <is>
+          <t>右掌对齐WeaponSocket</t>
+        </is>
+      </c>
+      <c r="J174" s="127" t="inlineStr">
+        <is>
+          <t>根静止/单位缩放/原碰撞</t>
+        </is>
+      </c>
+      <c r="K174" s="128" t="inlineStr">
+        <is>
+          <t>五种独立近战VFX；有效扣血局部停顿</t>
+        </is>
+      </c>
+      <c r="L174" s="127" t="inlineStr">
+        <is>
+          <t>v041 active；源与运行握点、阶段连续、真实渲染通过；art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
         </is>
       </c>
     </row>
@@ -17523,7 +19818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.1" customWidth="1" style="87" min="1" max="1"/>
@@ -20576,6 +22871,166 @@
       </c>
       <c r="D153" s="91" t="n">
         <v>2426500</v>
+      </c>
+    </row>
+    <row r="154" ht="70" customHeight="1" s="88">
+      <c r="A154" s="91" t="inlineStr">
+        <is>
+          <t>v041动作源</t>
+        </is>
+      </c>
+      <c r="B154" s="150" t="inlineStr">
+        <is>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v041.blend</t>
+        </is>
+      </c>
+      <c r="C154" s="150" t="inlineStr">
+        <is>
+          <t>20cfabac098819ea04ab9b79afaa17b0ddfc14ede6f6baab07c07e5cab4653ec</t>
+        </is>
+      </c>
+      <c r="D154" s="91" t="n">
+        <v>537526424</v>
+      </c>
+    </row>
+    <row r="155" ht="70" customHeight="1" s="88">
+      <c r="A155" s="91" t="inlineStr">
+        <is>
+          <t>v041中转</t>
+        </is>
+      </c>
+      <c r="B155" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C155" s="150" t="inlineStr">
+        <is>
+          <t>91f14611ce897fb890fc1f766bed9618c2290c2ee73ce14015114a902081fca4</t>
+        </is>
+      </c>
+      <c r="D155" s="91" t="n">
+        <v>27802</v>
+      </c>
+    </row>
+    <row r="156" ht="70" customHeight="1" s="88">
+      <c r="A156" s="91" t="inlineStr">
+        <is>
+          <t>v041运行采样库</t>
+        </is>
+      </c>
+      <c r="B156" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C156" s="150" t="inlineStr">
+        <is>
+          <t>88a5c75df4cb46d8af851d5ea90d4a789f858c9001a0b50291d8811dfa99ecf4</t>
+        </is>
+      </c>
+      <c r="D156" s="91" t="n">
+        <v>17461653</v>
+      </c>
+    </row>
+    <row r="157" ht="70" customHeight="1" s="88">
+      <c r="A157" s="91" t="inlineStr">
+        <is>
+          <t>v041近战增量GLB</t>
+        </is>
+      </c>
+      <c r="B157" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C157" s="150" t="inlineStr">
+        <is>
+          <t>34b22d18814290302760dff9b0558ee8894671ad8e9bfdb83e55c2cddcc730f4</t>
+        </is>
+      </c>
+      <c r="D157" s="91" t="n">
+        <v>793592</v>
+      </c>
+    </row>
+    <row r="158" ht="64.5" customHeight="1" s="88">
+      <c r="A158" s="91" t="inlineStr">
+        <is>
+          <t>v042斧握持修正源</t>
+        </is>
+      </c>
+      <c r="B158" s="150" t="inlineStr">
+        <is>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend</t>
+        </is>
+      </c>
+      <c r="C158" s="150" t="inlineStr">
+        <is>
+          <t>94774453e91c8c78e6738157964ea6d6b7e96d2f19bdca99496c2e01a3b6580d</t>
+        </is>
+      </c>
+      <c r="D158" s="91" t="n">
+        <v>537545424</v>
+      </c>
+    </row>
+    <row r="159" ht="64.5" customHeight="1" s="88">
+      <c r="A159" s="91" t="inlineStr">
+        <is>
+          <t>v042正式中转</t>
+        </is>
+      </c>
+      <c r="B159" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+        </is>
+      </c>
+      <c r="C159" s="150" t="inlineStr">
+        <is>
+          <t>0ba75f655b533a1461a45585d9b63ccdaf7189a3ff74e11c74b119b9e2fc3960</t>
+        </is>
+      </c>
+      <c r="D159" s="91" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="160" ht="64.5" customHeight="1" s="88">
+      <c r="A160" s="91" t="inlineStr">
+        <is>
+          <t>v042运行采样</t>
+        </is>
+      </c>
+      <c r="B160" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.json</t>
+        </is>
+      </c>
+      <c r="C160" s="150" t="inlineStr">
+        <is>
+          <t>ef8e6264e9156f0ff763138f5308604e9ec31ffbf4960a3f35a0fbd9466e6a32</t>
+        </is>
+      </c>
+      <c r="D160" s="91" t="n">
+        <v>17460416</v>
+      </c>
+    </row>
+    <row r="161" ht="64.5" customHeight="1" s="88">
+      <c r="A161" s="91" t="inlineStr">
+        <is>
+          <t>v042动画GLB</t>
+        </is>
+      </c>
+      <c r="B161" s="150" t="inlineStr">
+        <is>
+          <t>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_bunny01_motion/anim_bunny01_library.glb</t>
+        </is>
+      </c>
+      <c r="C161" s="150" t="inlineStr">
+        <is>
+          <t>34b22d18814290302760dff9b0558ee8894671ad8e9bfdb83e55c2cddcc730f4</t>
+        </is>
+      </c>
+      <c r="D161" s="91" t="n">
+        <v>793592</v>
       </c>
     </row>
   </sheetData>
@@ -20629,6 +23084,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="88">
       <c r="A4" s="153" t="inlineStr">
         <is>
@@ -20808,7 +23264,7 @@
       </c>
       <c r="E6" s="162" t="inlineStr">
         <is>
-          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v039.blend；模型保持v021</t>
+          <t>art_source/characters/player/chr_player_capsule01_3d/variants/bunny01/source/animation/chr_bunny01_animation_v042.blend；模型v021保持</t>
         </is>
       </c>
       <c r="F6" s="162" t="inlineStr">
@@ -20858,12 +23314,12 @@
       </c>
       <c r="O6" s="163" t="inlineStr">
         <is>
-          <t>v039</t>
+          <t>v042</t>
         </is>
       </c>
       <c r="P6" s="164" t="inlineStr">
         <is>
-          <t>模型v021；动作v039，四方向跑步与7待机加强，保留全局1.25倍率。15项导入/角色专项/真实渲染通过；历史未完项不变。assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/character_transfer_ledger.json</t>
+          <t>128动作保持；仅斧14动作握持绕柄-90°校正；docs/v0.1/development/2026-10-17_axe_edge_v042.md</t>
         </is>
       </c>
     </row>
@@ -21784,7 +24240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="87" min="1" max="1"/>
@@ -21811,6 +24267,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="88">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -22731,6 +25188,80 @@
         </is>
       </c>
       <c r="G29" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="70" customHeight="1" s="88">
+      <c r="A30" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.25</t>
+        </is>
+      </c>
+      <c r="B30" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C30" s="98" t="inlineStr">
+        <is>
+          <t>三类近战37动作与命中反馈</t>
+        </is>
+      </c>
+      <c r="D30" s="98" t="inlineStr">
+        <is>
+          <t>近战差异 v041</t>
+        </is>
+      </c>
+      <c r="E30" s="98" t="inlineStr">
+        <is>
+          <t>三类攻击差异、敌方硬直、玩家局部1/2/4帧停顿；模型与移动动作保持。</t>
+        </is>
+      </c>
+      <c r="F30" s="98" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-16_melee_styles_v041.md</t>
+        </is>
+      </c>
+      <c r="G30" s="98" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1" s="88">
+      <c r="A31" s="105" t="inlineStr">
+        <is>
+          <t>v0.1.26</t>
+        </is>
+      </c>
+      <c r="B31" s="105" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C31" s="98" t="inlineStr">
+        <is>
+          <t>斧子刃口朝向修正v042</t>
+        </is>
+      </c>
+      <c r="D31" s="98" t="inlineStr">
+        <is>
+          <t>角色握持角度</t>
+        </is>
+      </c>
+      <c r="E31" s="98" t="inlineStr">
+        <is>
+          <t>银刃沿竖向下劈方向领先；源、GLB、运行采样与真实渲染一致。</t>
+        </is>
+      </c>
+      <c r="F31" s="98" t="inlineStr">
+        <is>
+          <t>docs/v0.1/development/2026-10-17_axe_edge_v042.md</t>
+        </is>
+      </c>
+      <c r="G31" s="98" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>
